--- a/public/data/review-export.xlsx
+++ b/public/data/review-export.xlsx
@@ -8,14 +8,14 @@
     <sheet name="review-export" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review-export'!$A$1:$AP$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review-export'!$A$1:$AP$79</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="785">
   <si>
     <t>ReviewId</t>
   </si>
@@ -143,33 +143,123 @@
     <t>Distribution</t>
   </si>
   <si>
+    <t>ORREV116477897</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
+  </si>
+  <si>
+    <t>Kaila H</t>
+  </si>
+  <si>
+    <t>Mar 2026</t>
+  </si>
+  <si>
+    <t>Perfect stay!</t>
+  </si>
+  <si>
+    <t>My daughter left her air pods, did anyone find them?</t>
+  </si>
+  <si>
+    <t>Thank you Kaila, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORP458447</t>
+  </si>
+  <si>
+    <t>Bluff Haven Retreat</t>
+  </si>
+  <si>
+    <t>ORB16870867</t>
+  </si>
+  <si>
+    <t>ORG621252108</t>
+  </si>
+  <si>
+    <t>Kaila</t>
+  </si>
+  <si>
+    <t>Haboush</t>
+  </si>
+  <si>
+    <t>haboushkaila@gmail.com</t>
+  </si>
+  <si>
+    <t>Ineligible</t>
+  </si>
+  <si>
+    <t>ORREV116475507</t>
+  </si>
+  <si>
+    <t>Johanna S</t>
+  </si>
+  <si>
+    <t>I’ve been staying in Gatlinburg 3 times a year for 6 years now, a lot of air bnb’s I have stayed in and this was by far the best! The cabin is beautiful! They were amazing and very responsive with any of our questions! We left our work laptop and they went out of the way to meet us after check out and bring it to to us! Can’t leave a better review an can’t stay at a better place!</t>
+  </si>
+  <si>
+    <t>Thank you Johanna, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB16789356</t>
+  </si>
+  <si>
+    <t>ORG621166954</t>
+  </si>
+  <si>
+    <t>Johanna</t>
+  </si>
+  <si>
+    <t>Sandheinrich</t>
+  </si>
+  <si>
+    <t>daniellejs2323@yahoo.com</t>
+  </si>
+  <si>
+    <t>ORREV116474301</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Grace P</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Thank you Grace, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB16745308</t>
+  </si>
+  <si>
+    <t>ORG621120064</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>gschelinski@gmail.com</t>
+  </si>
+  <si>
     <t>ORREV116444769</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
     <t>LaShumbie C</t>
   </si>
   <si>
-    <t>Mar 2026</t>
-  </si>
-  <si>
     <t>Beautiful cabin &amp; view! Host was easy to communicate with 😊</t>
   </si>
   <si>
     <t>Thank you LaShumbie, Welcome back anytime!!</t>
   </si>
   <si>
-    <t>ORP458447</t>
-  </si>
-  <si>
-    <t>Bluff Haven Retreat</t>
-  </si>
-  <si>
     <t>ORB17026699</t>
   </si>
   <si>
@@ -183,9 +273,6 @@
   </si>
   <si>
     <t>shumbie1986@gmail.com</t>
-  </si>
-  <si>
-    <t>Ineligible</t>
   </si>
   <si>
     <t>ORREV116381662</t>
@@ -888,9 +975,6 @@
     <t>ORREV115845564</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Alex M</t>
   </si>
   <si>
@@ -900,7 +984,7 @@
     <t>We did notice some of the furniture &amp; dishes/glassware were dirty but no major concerns. Some special touches like coffee provided for the coffee station are what would make this a 5 star stay for us! But overall we really enjoyed the stay and appreciate your having us.</t>
   </si>
   <si>
-    <t>Thank you, Alex. Welcome back anytime!!</t>
+    <t>Thank you so much for staying at Bluff Haven Retreat and for taking the time to share your experience! 🏔️ We're so glad the location worked perfectly for your Pigeon Forge adventures and that everything went smoothly. It means the world to us that you would recommend us to others. We hope to welcome you back to the Smokies again soon! 🔥</t>
   </si>
   <si>
     <t>ORB15343331</t>
@@ -1108,10 +1192,7 @@
     <t>Thank you for your help when our car got stuck. Danny was great. If I had the heads up to park at the bottom if there were a ton of leaves I wouldn't have had a problem moving them with a rake. Also I'd recommend leaving more items like soaps and paper products sponges etc. They make a nice impact on guests. Also it would be worth getting a refrigerator with filtered water and ice. The patio furniture is cheap and uncomfortable. These few changes will make guests feel way more comfortable and would make the place feel more high end.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thank you for your feedback and for noting our responsiveness. We're glad we could help quickly with the driveway situation.
-We professionally clean and change all linens between stays, and we'll review our cleaning process. As shown in our listing, the refrigerator doesn't have a water hookup but includes ice cube trays. We stock extra supplies in the cabinets and would have been happy to direct you to them had you reached out during your stay.
-We're always available to address any concerns immediately when guests contact us, just as we did with the driveway. It seems some expectations may not have aligned with what's described in our listing
-We'd also note that these concerns are isolated to this review our other guests have consistently had positive experiences with the cleanliness, appliances, and overall stay. We appreciate your feedback and hope you were still able to enjoy your time at our property!</t>
+    <t>Thank you Jason for staying at Bluff Haven Retreat and for your kind words about our responsiveness! 🏔️ We're glad we could assist quickly when your car got stuck in the driveway. We do wish you had mentioned the other concerns during your 3-night stay, as we were available around the clock and would have gladly resolved everything immediately, just as we did with the driveway situation. We always provide freshly laundered linens, fully stocked supplies, and take great pride in our cleanliness standards. Your feedback has been noted, and we continue to improve with every stay. We hope you'll give us another chance to show you the 5-star experience we deliver for our guests! 🌟</t>
   </si>
   <si>
     <t>ORB15390909</t>
@@ -2380,7 +2461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP76"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.3060188293457" customWidth="1"/>
@@ -2563,7 +2644,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="2">
-        <v>46111</v>
+        <v>46117</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>44</v>
@@ -2575,7 +2656,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="2">
-        <v>46111.839397338</v>
+        <v>46117.4916690046</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -2589,35 +2670,38 @@
       <c r="L2" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="M2" s="0" t="s">
+        <v>48</v>
+      </c>
       <c r="N2" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R2" s="2">
-        <v>46105</v>
+        <v>46110</v>
       </c>
       <c r="S2" s="2">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W2" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X2" s="0">
         <v>5</v>
@@ -2638,30 +2722,30 @@
         <v>5</v>
       </c>
       <c r="AP2" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="2">
-        <v>46102</v>
+        <v>46116</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="2">
-        <v>46102.6623598032</v>
+        <v>46116.7064720255</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -2673,28 +2757,25 @@
         <v>5</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="0" t="s">
         <v>60</v>
       </c>
       <c r="N3" s="0" t="s">
         <v>61</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>62</v>
       </c>
       <c r="R3" s="2">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="S3" s="2">
-        <v>46102</v>
+        <v>46105</v>
       </c>
       <c r="T3" s="0" t="s">
         <v>63</v>
@@ -2727,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="AP3" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -2735,55 +2816,52 @@
         <v>67</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2">
-        <v>46100</v>
+        <v>46116</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G4" s="2">
-        <v>46100.7350191667</v>
+        <v>46116.6444062153</v>
       </c>
       <c r="H4" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="0">
         <v>5</v>
       </c>
       <c r="J4" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="M4" s="0" t="s">
         <v>70</v>
       </c>
       <c r="N4" s="0" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q4" s="0" t="s">
         <v>72</v>
       </c>
       <c r="R4" s="2">
-        <v>46096</v>
+        <v>46112</v>
       </c>
       <c r="S4" s="2">
-        <v>46100</v>
+        <v>46116</v>
       </c>
       <c r="T4" s="0" t="s">
         <v>73</v>
@@ -2804,19 +2882,19 @@
         <v>5</v>
       </c>
       <c r="AA4" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="0">
         <v>5</v>
       </c>
       <c r="AC4" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD4" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP4" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -2827,7 +2905,7 @@
         <v>43</v>
       </c>
       <c r="C5" s="2">
-        <v>46096</v>
+        <v>46111</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>44</v>
@@ -2839,7 +2917,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2">
-        <v>46096.7874516898</v>
+        <v>46111.839397338</v>
       </c>
       <c r="H5" s="0">
         <v>5</v>
@@ -2853,39 +2931,36 @@
       <c r="L5" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="N5" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="O5" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P5" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="O5" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="0" t="s">
+      <c r="R5" s="2">
+        <v>46105</v>
+      </c>
+      <c r="S5" s="2">
+        <v>46108</v>
+      </c>
+      <c r="T5" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="R5" s="2">
-        <v>46093</v>
-      </c>
-      <c r="S5" s="2">
-        <v>46096</v>
-      </c>
-      <c r="T5" s="0" t="s">
+      <c r="U5" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="U5" s="0" t="s">
+      <c r="V5" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="V5" s="0" t="s">
+      <c r="W5" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="W5" s="0" t="s">
-        <v>86</v>
-      </c>
       <c r="X5" s="0">
         <v>5</v>
       </c>
@@ -2905,30 +2980,30 @@
         <v>5</v>
       </c>
       <c r="AP5" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="2">
-        <v>46093</v>
+        <v>46102</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G6" s="2">
-        <v>46093.5347989931</v>
+        <v>46102.6623598032</v>
       </c>
       <c r="H6" s="0">
         <v>5</v>
@@ -2940,41 +3015,41 @@
         <v>5</v>
       </c>
       <c r="L6" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="N6" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="O6" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P6" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q6" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="O6" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="0" t="s">
+      <c r="R6" s="2">
+        <v>46100</v>
+      </c>
+      <c r="S6" s="2">
+        <v>46102</v>
+      </c>
+      <c r="T6" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="R6" s="2">
-        <v>46089</v>
-      </c>
-      <c r="S6" s="2">
-        <v>46092</v>
-      </c>
-      <c r="T6" s="0" t="s">
+      <c r="U6" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="U6" s="0" t="s">
+      <c r="V6" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="V6" s="0" t="s">
+      <c r="W6" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="W6" s="0" t="s">
-        <v>96</v>
-      </c>
       <c r="X6" s="0">
         <v>5</v>
       </c>
@@ -2994,30 +3069,30 @@
         <v>5</v>
       </c>
       <c r="AP6" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="2">
-        <v>46089</v>
+        <v>46100</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G7" s="2">
-        <v>46089.7169537731</v>
+        <v>46100.7350191667</v>
       </c>
       <c r="H7" s="0">
         <v>5</v>
@@ -3029,41 +3104,41 @@
         <v>5</v>
       </c>
       <c r="L7" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="M7" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="M7" s="0" t="s">
+      <c r="N7" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="O7" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="O7" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P7" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q7" s="0" t="s">
+      <c r="R7" s="2">
+        <v>46096</v>
+      </c>
+      <c r="S7" s="2">
+        <v>46100</v>
+      </c>
+      <c r="T7" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="R7" s="2">
-        <v>46085</v>
-      </c>
-      <c r="S7" s="2">
-        <v>46089</v>
-      </c>
-      <c r="T7" s="0" t="s">
+      <c r="U7" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="U7" s="0" t="s">
+      <c r="V7" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="V7" s="0" t="s">
+      <c r="W7" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="W7" s="0" t="s">
-        <v>106</v>
-      </c>
       <c r="X7" s="0">
         <v>5</v>
       </c>
@@ -3083,30 +3158,30 @@
         <v>5</v>
       </c>
       <c r="AP7" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="2">
-        <v>46085</v>
+        <v>46096</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G8" s="2">
-        <v>46085.7193587963</v>
+        <v>46096.7874516898</v>
       </c>
       <c r="H8" s="0">
         <v>5</v>
@@ -3118,41 +3193,41 @@
         <v>5</v>
       </c>
       <c r="L8" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="M8" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="M8" s="0" t="s">
+      <c r="N8" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="O8" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P8" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="O8" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P8" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="0" t="s">
+      <c r="R8" s="2">
+        <v>46093</v>
+      </c>
+      <c r="S8" s="2">
+        <v>46096</v>
+      </c>
+      <c r="T8" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="R8" s="2">
-        <v>46082</v>
-      </c>
-      <c r="S8" s="2">
-        <v>46085</v>
-      </c>
-      <c r="T8" s="0" t="s">
+      <c r="U8" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="U8" s="0" t="s">
+      <c r="V8" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="V8" s="0" t="s">
+      <c r="W8" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="W8" s="0" t="s">
-        <v>116</v>
-      </c>
       <c r="X8" s="0">
         <v>5</v>
       </c>
@@ -3172,76 +3247,76 @@
         <v>5</v>
       </c>
       <c r="AP8" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46093.5347989931</v>
+      </c>
+      <c r="H9" s="0">
+        <v>5</v>
+      </c>
+      <c r="I9" s="0">
+        <v>5</v>
+      </c>
+      <c r="J9" s="0">
+        <v>5</v>
+      </c>
+      <c r="L9" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="M9" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="2">
-        <v>46078.6396170949</v>
-      </c>
-      <c r="H9" s="0">
-        <v>5</v>
-      </c>
-      <c r="I9" s="0">
-        <v>5</v>
-      </c>
-      <c r="J9" s="0">
-        <v>5</v>
-      </c>
-      <c r="L9" s="0" t="s">
+      <c r="N9" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="O9" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P9" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q9" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="R9" s="2">
+        <v>46089</v>
+      </c>
+      <c r="S9" s="2">
+        <v>46092</v>
+      </c>
+      <c r="T9" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="O9" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P9" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="0" t="s">
+      <c r="U9" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="R9" s="2">
-        <v>46075</v>
-      </c>
-      <c r="S9" s="2">
-        <v>46078</v>
-      </c>
-      <c r="T9" s="0" t="s">
+      <c r="V9" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="U9" s="0" t="s">
+      <c r="W9" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="V9" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="W9" s="0" t="s">
-        <v>127</v>
-      </c>
       <c r="X9" s="0">
         <v>5</v>
       </c>
@@ -3261,76 +3336,76 @@
         <v>5</v>
       </c>
       <c r="AP9" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="2">
-        <v>46075</v>
+        <v>46089</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46089.7169537731</v>
+      </c>
+      <c r="H10" s="0">
+        <v>5</v>
+      </c>
+      <c r="I10" s="0">
+        <v>5</v>
+      </c>
+      <c r="J10" s="0">
+        <v>5</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="G10" s="2">
-        <v>46075.7313287847</v>
-      </c>
-      <c r="H10" s="0">
-        <v>5</v>
-      </c>
-      <c r="I10" s="0">
-        <v>5</v>
-      </c>
-      <c r="J10" s="0">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="N10" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="M10" s="0" t="s">
+      <c r="O10" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P10" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="0" t="s">
+      <c r="R10" s="2">
+        <v>46085</v>
+      </c>
+      <c r="S10" s="2">
+        <v>46089</v>
+      </c>
+      <c r="T10" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="O10" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P10" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q10" s="0" t="s">
+      <c r="U10" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="R10" s="2">
-        <v>46073</v>
-      </c>
-      <c r="S10" s="2">
-        <v>46075</v>
-      </c>
-      <c r="T10" s="0" t="s">
+      <c r="V10" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="U10" s="0" t="s">
+      <c r="W10" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="V10" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="W10" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="X10" s="0">
         <v>5</v>
       </c>
@@ -3350,73 +3425,76 @@
         <v>5</v>
       </c>
       <c r="AP10" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="2">
-        <v>46072</v>
+        <v>46085</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="2">
+        <v>46085.7193587963</v>
+      </c>
+      <c r="H11" s="0">
+        <v>5</v>
+      </c>
+      <c r="I11" s="0">
+        <v>5</v>
+      </c>
+      <c r="J11" s="0">
+        <v>5</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="M11" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" s="2">
-        <v>46072.546856875</v>
-      </c>
-      <c r="H11" s="0">
-        <v>5</v>
-      </c>
-      <c r="I11" s="0">
-        <v>5</v>
-      </c>
-      <c r="J11" s="0">
-        <v>5</v>
-      </c>
-      <c r="L11" s="0" t="s">
+      <c r="N11" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="O11" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P11" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q11" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="O11" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q11" s="0" t="s">
+      <c r="R11" s="2">
+        <v>46082</v>
+      </c>
+      <c r="S11" s="2">
+        <v>46085</v>
+      </c>
+      <c r="T11" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="R11" s="2">
-        <v>46067</v>
-      </c>
-      <c r="S11" s="2">
-        <v>46071</v>
-      </c>
-      <c r="T11" s="0" t="s">
+      <c r="U11" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="U11" s="0" t="s">
+      <c r="V11" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="V11" s="0" t="s">
+      <c r="W11" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="W11" s="0" t="s">
-        <v>146</v>
-      </c>
       <c r="X11" s="0">
         <v>5</v>
       </c>
@@ -3436,30 +3514,30 @@
         <v>5</v>
       </c>
       <c r="AP11" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="2">
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>119</v>
-      </c>
       <c r="G12" s="2">
-        <v>46071.6485774074</v>
+        <v>46078.6396170949</v>
       </c>
       <c r="H12" s="0">
         <v>5</v>
@@ -3473,35 +3551,38 @@
       <c r="L12" s="0" t="s">
         <v>149</v>
       </c>
+      <c r="M12" s="0" t="s">
+        <v>150</v>
+      </c>
       <c r="N12" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q12" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R12" s="2">
-        <v>46065</v>
+        <v>46075</v>
       </c>
       <c r="S12" s="2">
-        <v>46067</v>
+        <v>46078</v>
       </c>
       <c r="T12" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="W12" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="X12" s="0">
         <v>5</v>
@@ -3522,30 +3603,30 @@
         <v>5</v>
       </c>
       <c r="AP12" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="2">
-        <v>46062</v>
+        <v>46075</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="G13" s="2">
-        <v>46062.6577711111</v>
+        <v>46075.7313287847</v>
       </c>
       <c r="H13" s="0">
         <v>5</v>
@@ -3556,38 +3637,41 @@
       <c r="J13" s="0">
         <v>5</v>
       </c>
-      <c r="L13" s="0" t="s">
-        <v>157</v>
+      <c r="L13" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>160</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="R13" s="2">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="S13" s="2">
-        <v>46062</v>
+        <v>46075</v>
       </c>
       <c r="T13" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="W13" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="X13" s="0">
         <v>5</v>
@@ -3608,30 +3692,30 @@
         <v>5</v>
       </c>
       <c r="AP13" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="2">
-        <v>46057</v>
+        <v>46072</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G14" s="2">
-        <v>46057.6514546875</v>
+        <v>46072.546856875</v>
       </c>
       <c r="H14" s="0">
         <v>5</v>
@@ -3643,37 +3727,37 @@
         <v>5</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q14" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="R14" s="2">
-        <v>46052</v>
+        <v>46067</v>
       </c>
       <c r="S14" s="2">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="T14" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="W14" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="X14" s="0">
         <v>5</v>
@@ -3694,30 +3778,30 @@
         <v>5</v>
       </c>
       <c r="AP14" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="2">
-        <v>46046</v>
+        <v>46071</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G15" s="2">
-        <v>46046.6863551157</v>
+        <v>46071.6485774074</v>
       </c>
       <c r="H15" s="0">
         <v>5</v>
@@ -3729,37 +3813,37 @@
         <v>5</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q15" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R15" s="2">
-        <v>46043</v>
+        <v>46065</v>
       </c>
       <c r="S15" s="2">
-        <v>46046</v>
+        <v>46067</v>
       </c>
       <c r="T15" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X15" s="0">
         <v>5</v>
@@ -3780,30 +3864,30 @@
         <v>5</v>
       </c>
       <c r="AP15" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2">
-        <v>46044</v>
+        <v>46062</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G16" s="2">
-        <v>46044.5556409607</v>
+        <v>46062.6577711111</v>
       </c>
       <c r="H16" s="0">
         <v>5</v>
@@ -3815,37 +3899,37 @@
         <v>5</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q16" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R16" s="2">
-        <v>46038</v>
+        <v>46059</v>
       </c>
       <c r="S16" s="2">
-        <v>46042</v>
+        <v>46062</v>
       </c>
       <c r="T16" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V16" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="W16" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="X16" s="0">
         <v>5</v>
@@ -3866,30 +3950,30 @@
         <v>5</v>
       </c>
       <c r="AP16" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="2">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G17" s="2">
-        <v>46044.5534156597</v>
+        <v>46057.6514546875</v>
       </c>
       <c r="H17" s="0">
         <v>5</v>
@@ -3901,37 +3985,37 @@
         <v>5</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P17" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R17" s="2">
-        <v>46034</v>
+        <v>46052</v>
       </c>
       <c r="S17" s="2">
-        <v>46037</v>
+        <v>46057</v>
       </c>
       <c r="T17" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U17" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="V17" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="W17" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="X17" s="0">
         <v>5</v>
@@ -3952,30 +4036,30 @@
         <v>5</v>
       </c>
       <c r="AP17" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="2">
-        <v>46033</v>
+        <v>46046</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G18" s="2">
-        <v>46033.7481770718</v>
+        <v>46046.6863551157</v>
       </c>
       <c r="H18" s="0">
         <v>5</v>
@@ -3987,40 +4071,37 @@
         <v>5</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N18" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P18" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q18" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R18" s="2">
-        <v>46030</v>
+        <v>46043</v>
       </c>
       <c r="S18" s="2">
-        <v>46033</v>
+        <v>46046</v>
       </c>
       <c r="T18" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W18" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X18" s="0">
         <v>5</v>
@@ -4041,30 +4122,30 @@
         <v>5</v>
       </c>
       <c r="AP18" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="2">
-        <v>46030</v>
+        <v>46044</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G19" s="2">
-        <v>46030.801171713</v>
+        <v>46044.5556409607</v>
       </c>
       <c r="H19" s="0">
         <v>5</v>
@@ -4076,28 +4157,25 @@
         <v>5</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="M19" s="0" t="s">
         <v>214</v>
       </c>
       <c r="N19" s="0" t="s">
         <v>215</v>
       </c>
       <c r="O19" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q19" s="0" t="s">
         <v>216</v>
       </c>
       <c r="R19" s="2">
-        <v>46027</v>
+        <v>46038</v>
       </c>
       <c r="S19" s="2">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="T19" s="0" t="s">
         <v>217</v>
@@ -4130,7 +4208,7 @@
         <v>5</v>
       </c>
       <c r="AP19" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -4141,7 +4219,7 @@
         <v>43</v>
       </c>
       <c r="C20" s="2">
-        <v>46026</v>
+        <v>46044</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>44</v>
@@ -4150,10 +4228,10 @@
         <v>222</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G20" s="2">
-        <v>46026.8843540856</v>
+        <v>46044.5534156597</v>
       </c>
       <c r="H20" s="0">
         <v>5</v>
@@ -4167,39 +4245,36 @@
       <c r="L20" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="M20" s="0" t="s">
+      <c r="N20" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="N20" s="0" t="s">
+      <c r="O20" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P20" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q20" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="O20" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P20" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q20" s="0" t="s">
+      <c r="R20" s="2">
+        <v>46034</v>
+      </c>
+      <c r="S20" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T20" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="R20" s="2">
-        <v>46025</v>
-      </c>
-      <c r="S20" s="2">
-        <v>46026</v>
-      </c>
-      <c r="T20" s="0" t="s">
+      <c r="U20" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="U20" s="0" t="s">
+      <c r="V20" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="V20" s="0" t="s">
+      <c r="W20" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="W20" s="0" t="s">
-        <v>230</v>
-      </c>
       <c r="X20" s="0">
         <v>5</v>
       </c>
@@ -4219,73 +4294,76 @@
         <v>5</v>
       </c>
       <c r="AP20" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="2">
-        <v>46025</v>
+        <v>46033</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E21" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="G21" s="2">
+        <v>46033.7481770718</v>
+      </c>
+      <c r="H21" s="0">
+        <v>5</v>
+      </c>
+      <c r="I21" s="0">
+        <v>5</v>
+      </c>
+      <c r="J21" s="0">
+        <v>5</v>
+      </c>
+      <c r="L21" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="M21" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G21" s="2">
-        <v>46025.9183283912</v>
-      </c>
-      <c r="H21" s="0">
-        <v>5</v>
-      </c>
-      <c r="I21" s="0">
-        <v>5</v>
-      </c>
-      <c r="J21" s="0">
-        <v>5</v>
-      </c>
-      <c r="L21" s="0" t="s">
+      <c r="N21" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="N21" s="0" t="s">
+      <c r="O21" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P21" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q21" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="O21" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P21" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q21" s="0" t="s">
+      <c r="R21" s="2">
+        <v>46030</v>
+      </c>
+      <c r="S21" s="2">
+        <v>46033</v>
+      </c>
+      <c r="T21" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="R21" s="2">
-        <v>46018</v>
-      </c>
-      <c r="S21" s="2">
-        <v>46025</v>
-      </c>
-      <c r="T21" s="0" t="s">
+      <c r="U21" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="U21" s="0" t="s">
+      <c r="V21" s="0" t="s">
         <v>238</v>
       </c>
-      <c r="V21" s="0" t="s">
+      <c r="W21" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="W21" s="0" t="s">
-        <v>240</v>
-      </c>
       <c r="X21" s="0">
         <v>5</v>
       </c>
@@ -4305,60 +4383,63 @@
         <v>5</v>
       </c>
       <c r="AP21" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="2">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E22" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="G22" s="2">
+        <v>46030.801171713</v>
+      </c>
+      <c r="H22" s="0">
+        <v>5</v>
+      </c>
+      <c r="I22" s="0">
+        <v>5</v>
+      </c>
+      <c r="J22" s="0">
+        <v>5</v>
+      </c>
+      <c r="L22" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="F22" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="G22" s="2">
-        <v>46024.2781152662</v>
-      </c>
-      <c r="H22" s="0">
-        <v>5</v>
-      </c>
-      <c r="I22" s="0">
-        <v>5</v>
-      </c>
-      <c r="J22" s="0">
-        <v>5</v>
-      </c>
-      <c r="L22" s="0" t="s">
+      <c r="M22" s="0" t="s">
         <v>243</v>
       </c>
       <c r="N22" s="0" t="s">
         <v>244</v>
       </c>
       <c r="O22" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P22" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q22" s="0" t="s">
         <v>245</v>
       </c>
       <c r="R22" s="2">
-        <v>46017</v>
+        <v>46027</v>
       </c>
       <c r="S22" s="2">
-        <v>46018</v>
+        <v>46030</v>
       </c>
       <c r="T22" s="0" t="s">
         <v>246</v>
@@ -4391,7 +4472,7 @@
         <v>5</v>
       </c>
       <c r="AP22" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
@@ -4402,7 +4483,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>44</v>
@@ -4411,10 +4492,10 @@
         <v>251</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="G23" s="2">
-        <v>46023.7304273495</v>
+        <v>46026.8843540856</v>
       </c>
       <c r="H23" s="0">
         <v>5</v>
@@ -4428,35 +4509,38 @@
       <c r="L23" s="0" t="s">
         <v>252</v>
       </c>
+      <c r="M23" s="0" t="s">
+        <v>253</v>
+      </c>
       <c r="N23" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O23" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R23" s="2">
-        <v>46010</v>
+        <v>46025</v>
       </c>
       <c r="S23" s="2">
-        <v>46012</v>
+        <v>46026</v>
       </c>
       <c r="T23" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="V23" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="W23" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="X23" s="0">
         <v>5</v>
@@ -4474,33 +4558,33 @@
         <v>5</v>
       </c>
       <c r="AD23" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP23" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="2">
-        <v>46018</v>
+        <v>46025</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G24" s="2">
-        <v>46018.4146147801</v>
+        <v>46025.9183283912</v>
       </c>
       <c r="H24" s="0">
         <v>5</v>
@@ -4512,40 +4596,37 @@
         <v>5</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="M24" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O24" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q24" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R24" s="2">
-        <v>46013</v>
+        <v>46018</v>
       </c>
       <c r="S24" s="2">
-        <v>46017</v>
+        <v>46025</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W24" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="X24" s="0">
         <v>5</v>
@@ -4566,30 +4647,30 @@
         <v>5</v>
       </c>
       <c r="AP24" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="2">
-        <v>46011</v>
+        <v>46024</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G25" s="2">
-        <v>46011.6063615046</v>
+        <v>46024.2781152662</v>
       </c>
       <c r="H25" s="0">
         <v>5</v>
@@ -4601,37 +4682,37 @@
         <v>5</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O25" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q25" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R25" s="2">
-        <v>46006</v>
+        <v>46017</v>
       </c>
       <c r="S25" s="2">
-        <v>46010</v>
+        <v>46018</v>
       </c>
       <c r="T25" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="W25" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="X25" s="0">
         <v>5</v>
@@ -4652,30 +4733,30 @@
         <v>5</v>
       </c>
       <c r="AP25" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="2">
-        <v>46005</v>
+        <v>46023</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G26" s="2">
-        <v>46005.7644445486</v>
+        <v>46023.7304273495</v>
       </c>
       <c r="H26" s="0">
         <v>5</v>
@@ -4687,37 +4768,37 @@
         <v>5</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O26" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q26" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R26" s="2">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="S26" s="2">
-        <v>46005</v>
+        <v>46012</v>
       </c>
       <c r="T26" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="W26" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="X26" s="0">
         <v>5</v>
@@ -4735,21 +4816,21 @@
         <v>5</v>
       </c>
       <c r="AD26" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP26" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2">
-        <v>46003</v>
+        <v>46018</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>44</v>
@@ -4758,19 +4839,19 @@
         <v>289</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G27" s="2">
-        <v>46003.8492650926</v>
+        <v>46018.4146147801</v>
       </c>
       <c r="H27" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="0">
         <v>5</v>
       </c>
       <c r="J27" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="0" t="s">
         <v>290</v>
@@ -4782,19 +4863,19 @@
         <v>292</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P27" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q27" s="0" t="s">
         <v>293</v>
       </c>
       <c r="R27" s="2">
-        <v>45996</v>
+        <v>46013</v>
       </c>
       <c r="S27" s="2">
-        <v>45998</v>
+        <v>46017</v>
       </c>
       <c r="T27" s="0" t="s">
         <v>294</v>
@@ -4809,7 +4890,7 @@
         <v>297</v>
       </c>
       <c r="X27" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y27" s="0">
         <v>5</v>
@@ -4824,10 +4905,10 @@
         <v>5</v>
       </c>
       <c r="AD27" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP27" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -4838,7 +4919,7 @@
         <v>43</v>
       </c>
       <c r="C28" s="2">
-        <v>46001</v>
+        <v>46011</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>44</v>
@@ -4847,10 +4928,10 @@
         <v>299</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G28" s="2">
-        <v>46001.7156633218</v>
+        <v>46011.6063615046</v>
       </c>
       <c r="H28" s="0">
         <v>5</v>
@@ -4868,19 +4949,19 @@
         <v>301</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P28" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q28" s="0" t="s">
         <v>302</v>
       </c>
       <c r="R28" s="2">
-        <v>45998</v>
+        <v>46006</v>
       </c>
       <c r="S28" s="2">
-        <v>46001</v>
+        <v>46010</v>
       </c>
       <c r="T28" s="0" t="s">
         <v>303</v>
@@ -4913,7 +4994,7 @@
         <v>5</v>
       </c>
       <c r="AP28" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
@@ -4924,7 +5005,7 @@
         <v>43</v>
       </c>
       <c r="C29" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>44</v>
@@ -4933,10 +5014,10 @@
         <v>308</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G29" s="2">
-        <v>45999.39383875</v>
+        <v>46005.7644445486</v>
       </c>
       <c r="H29" s="0">
         <v>5</v>
@@ -4954,19 +5035,19 @@
         <v>310</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P29" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q29" s="0" t="s">
         <v>311</v>
       </c>
       <c r="R29" s="2">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="S29" s="2">
-        <v>45994</v>
+        <v>46005</v>
       </c>
       <c r="T29" s="0" t="s">
         <v>312</v>
@@ -4999,7 +5080,7 @@
         <v>5</v>
       </c>
       <c r="AP29" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -5007,10 +5088,10 @@
         <v>316</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>45997</v>
+        <v>46003</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>44</v>
@@ -5019,19 +5100,19 @@
         <v>317</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="G30" s="2">
-        <v>45997.7247070486</v>
+        <v>46003.8492650926</v>
       </c>
       <c r="H30" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" s="0">
         <v>5</v>
       </c>
       <c r="J30" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30" s="0" t="s">
         <v>318</v>
@@ -5043,19 +5124,19 @@
         <v>320</v>
       </c>
       <c r="O30" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q30" s="0" t="s">
         <v>321</v>
       </c>
       <c r="R30" s="2">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="S30" s="2">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="T30" s="0" t="s">
         <v>322</v>
@@ -5070,7 +5151,7 @@
         <v>325</v>
       </c>
       <c r="X30" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y30" s="0">
         <v>5</v>
@@ -5085,10 +5166,10 @@
         <v>5</v>
       </c>
       <c r="AD30" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP30" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
@@ -5099,7 +5180,7 @@
         <v>43</v>
       </c>
       <c r="C31" s="2">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>44</v>
@@ -5108,53 +5189,53 @@
         <v>327</v>
       </c>
       <c r="F31" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="G31" s="2">
+        <v>46001.7156633218</v>
+      </c>
+      <c r="H31" s="0">
+        <v>5</v>
+      </c>
+      <c r="I31" s="0">
+        <v>5</v>
+      </c>
+      <c r="J31" s="0">
+        <v>5</v>
+      </c>
+      <c r="L31" s="0" t="s">
         <v>328</v>
       </c>
-      <c r="G31" s="2">
-        <v>45993.7333972569</v>
-      </c>
-      <c r="H31" s="0">
-        <v>5</v>
-      </c>
-      <c r="I31" s="0">
-        <v>5</v>
-      </c>
-      <c r="J31" s="0">
-        <v>5</v>
-      </c>
-      <c r="L31" s="0" t="s">
+      <c r="N31" s="0" t="s">
         <v>329</v>
       </c>
-      <c r="N31" s="0" t="s">
+      <c r="O31" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P31" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q31" s="0" t="s">
         <v>330</v>
       </c>
-      <c r="O31" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P31" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q31" s="0" t="s">
+      <c r="R31" s="2">
+        <v>45998</v>
+      </c>
+      <c r="S31" s="2">
+        <v>46001</v>
+      </c>
+      <c r="T31" s="0" t="s">
         <v>331</v>
       </c>
-      <c r="R31" s="2">
-        <v>45990</v>
-      </c>
-      <c r="S31" s="2">
-        <v>45993</v>
-      </c>
-      <c r="T31" s="0" t="s">
+      <c r="U31" s="0" t="s">
         <v>332</v>
       </c>
-      <c r="U31" s="0" t="s">
+      <c r="V31" s="0" t="s">
         <v>333</v>
       </c>
-      <c r="V31" s="0" t="s">
+      <c r="W31" s="0" t="s">
         <v>334</v>
       </c>
-      <c r="W31" s="0" t="s">
-        <v>335</v>
-      </c>
       <c r="X31" s="0">
         <v>5</v>
       </c>
@@ -5174,76 +5255,73 @@
         <v>5</v>
       </c>
       <c r="AP31" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="2">
-        <v>45990</v>
+        <v>45999</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="G32" s="2">
+        <v>45999.39383875</v>
+      </c>
+      <c r="H32" s="0">
+        <v>5</v>
+      </c>
+      <c r="I32" s="0">
+        <v>5</v>
+      </c>
+      <c r="J32" s="0">
+        <v>5</v>
+      </c>
+      <c r="L32" s="0" t="s">
         <v>337</v>
       </c>
-      <c r="F32" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="G32" s="2">
-        <v>45990.6230057292</v>
-      </c>
-      <c r="H32" s="0">
-        <v>5</v>
-      </c>
-      <c r="I32" s="0">
-        <v>5</v>
-      </c>
-      <c r="J32" s="0">
-        <v>5</v>
-      </c>
-      <c r="L32" s="0" t="s">
+      <c r="N32" s="0" t="s">
         <v>338</v>
       </c>
-      <c r="M32" s="0" t="s">
+      <c r="O32" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P32" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q32" s="0" t="s">
         <v>339</v>
       </c>
-      <c r="N32" s="0" t="s">
+      <c r="R32" s="2">
+        <v>45993</v>
+      </c>
+      <c r="S32" s="2">
+        <v>45994</v>
+      </c>
+      <c r="T32" s="0" t="s">
         <v>340</v>
       </c>
-      <c r="O32" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P32" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q32" s="0" t="s">
+      <c r="U32" s="0" t="s">
         <v>341</v>
       </c>
-      <c r="R32" s="2">
-        <v>45986</v>
-      </c>
-      <c r="S32" s="2">
-        <v>45990</v>
-      </c>
-      <c r="T32" s="0" t="s">
+      <c r="V32" s="0" t="s">
         <v>342</v>
       </c>
-      <c r="U32" s="0" t="s">
+      <c r="W32" s="0" t="s">
         <v>343</v>
       </c>
-      <c r="V32" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="W32" s="0" t="s">
-        <v>345</v>
-      </c>
       <c r="X32" s="0">
         <v>5</v>
       </c>
@@ -5263,76 +5341,76 @@
         <v>5</v>
       </c>
       <c r="AP32" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="2">
-        <v>45986</v>
+        <v>45997</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="G33" s="2">
+        <v>45997.7247070486</v>
+      </c>
+      <c r="H33" s="0">
+        <v>5</v>
+      </c>
+      <c r="I33" s="0">
+        <v>5</v>
+      </c>
+      <c r="J33" s="0">
+        <v>5</v>
+      </c>
+      <c r="L33" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="M33" s="0" t="s">
         <v>347</v>
       </c>
-      <c r="F33" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="G33" s="2">
-        <v>45986.7385835995</v>
-      </c>
-      <c r="H33" s="0">
-        <v>5</v>
-      </c>
-      <c r="I33" s="0">
-        <v>5</v>
-      </c>
-      <c r="J33" s="0">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3" t="s">
+      <c r="N33" s="0" t="s">
         <v>348</v>
       </c>
-      <c r="M33" s="3" t="s">
+      <c r="O33" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P33" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q33" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="N33" s="0" t="s">
+      <c r="R33" s="2">
+        <v>45994</v>
+      </c>
+      <c r="S33" s="2">
+        <v>45996</v>
+      </c>
+      <c r="T33" s="0" t="s">
         <v>350</v>
       </c>
-      <c r="O33" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P33" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q33" s="0" t="s">
+      <c r="U33" s="0" t="s">
         <v>351</v>
       </c>
-      <c r="R33" s="2">
-        <v>45977</v>
-      </c>
-      <c r="S33" s="2">
-        <v>45983</v>
-      </c>
-      <c r="T33" s="0" t="s">
+      <c r="V33" s="0" t="s">
         <v>352</v>
       </c>
-      <c r="U33" s="0" t="s">
+      <c r="W33" s="0" t="s">
         <v>353</v>
       </c>
-      <c r="V33" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="W33" s="0" t="s">
-        <v>354</v>
-      </c>
       <c r="X33" s="0">
         <v>5</v>
       </c>
@@ -5352,78 +5430,75 @@
         <v>5</v>
       </c>
       <c r="AP33" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="F34" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="F34" s="0" t="s">
-        <v>328</v>
-      </c>
       <c r="G34" s="2">
-        <v>45986.574325081</v>
+        <v>45993.7333972569</v>
       </c>
       <c r="H34" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I34" s="0">
         <v>5</v>
       </c>
       <c r="J34" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L34" s="0" t="s">
         <v>357</v>
       </c>
-      <c r="M34" s="0" t="s">
+      <c r="N34" s="0" t="s">
         <v>358</v>
       </c>
-      <c r="N34" s="3" t="s">
+      <c r="O34" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P34" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q34" s="0" t="s">
         <v>359</v>
       </c>
-      <c r="O34" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P34" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q34" s="0" t="s">
+      <c r="R34" s="2">
+        <v>45990</v>
+      </c>
+      <c r="S34" s="2">
+        <v>45993</v>
+      </c>
+      <c r="T34" s="0" t="s">
         <v>360</v>
       </c>
-      <c r="R34" s="2">
-        <v>45983</v>
-      </c>
-      <c r="S34" s="2">
-        <v>45986</v>
-      </c>
-      <c r="T34" s="0" t="s">
+      <c r="U34" s="0" t="s">
         <v>361</v>
       </c>
-      <c r="U34" s="0" t="s">
+      <c r="V34" s="0" t="s">
         <v>362</v>
       </c>
-      <c r="V34" s="0" t="s">
+      <c r="W34" s="0" t="s">
         <v>363</v>
       </c>
-      <c r="W34" s="0" t="s">
-        <v>364</v>
-      </c>
       <c r="X34" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y34" s="0">
         <v>5</v>
@@ -5432,85 +5507,85 @@
         <v>5</v>
       </c>
       <c r="AB34" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC34" s="0">
         <v>5</v>
       </c>
       <c r="AD34" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP34" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="2">
-        <v>45981</v>
+        <v>45990</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45990.6230057292</v>
+      </c>
+      <c r="H35" s="0">
+        <v>5</v>
+      </c>
+      <c r="I35" s="0">
+        <v>5</v>
+      </c>
+      <c r="J35" s="0">
+        <v>5</v>
+      </c>
+      <c r="L35" s="0" t="s">
         <v>366</v>
       </c>
-      <c r="F35" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45981.6819216319</v>
-      </c>
-      <c r="H35" s="0">
-        <v>5</v>
-      </c>
-      <c r="I35" s="0">
-        <v>5</v>
-      </c>
-      <c r="J35" s="0">
-        <v>5</v>
-      </c>
-      <c r="L35" s="0" t="s">
+      <c r="M35" s="0" t="s">
         <v>367</v>
       </c>
-      <c r="M35" s="0" t="s">
+      <c r="N35" s="0" t="s">
         <v>368</v>
       </c>
-      <c r="N35" s="0" t="s">
+      <c r="O35" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P35" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q35" s="0" t="s">
         <v>369</v>
       </c>
-      <c r="O35" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P35" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q35" s="0" t="s">
+      <c r="R35" s="2">
+        <v>45986</v>
+      </c>
+      <c r="S35" s="2">
+        <v>45990</v>
+      </c>
+      <c r="T35" s="0" t="s">
         <v>370</v>
       </c>
-      <c r="R35" s="2">
-        <v>45970</v>
-      </c>
-      <c r="S35" s="2">
-        <v>45977</v>
-      </c>
-      <c r="T35" s="0" t="s">
+      <c r="U35" s="0" t="s">
         <v>371</v>
       </c>
-      <c r="U35" s="0" t="s">
+      <c r="V35" s="0" t="s">
         <v>372</v>
       </c>
-      <c r="V35" s="0" t="s">
+      <c r="W35" s="0" t="s">
         <v>373</v>
       </c>
-      <c r="W35" s="0" t="s">
-        <v>374</v>
-      </c>
       <c r="X35" s="0">
         <v>5</v>
       </c>
@@ -5530,60 +5605,63 @@
         <v>5</v>
       </c>
       <c r="AP35" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="2">
-        <v>45970</v>
+        <v>45986</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45986.7385835995</v>
+      </c>
+      <c r="H36" s="0">
+        <v>5</v>
+      </c>
+      <c r="I36" s="0">
+        <v>5</v>
+      </c>
+      <c r="J36" s="0">
+        <v>5</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="F36" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45970.7607620602</v>
-      </c>
-      <c r="H36" s="0">
-        <v>5</v>
-      </c>
-      <c r="I36" s="0">
-        <v>5</v>
-      </c>
-      <c r="J36" s="0">
-        <v>5</v>
-      </c>
-      <c r="L36" s="0" t="s">
+      <c r="M36" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="N36" s="0" t="s">
         <v>378</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q36" s="0" t="s">
         <v>379</v>
       </c>
       <c r="R36" s="2">
-        <v>45969</v>
+        <v>45977</v>
       </c>
       <c r="S36" s="2">
-        <v>45970</v>
+        <v>45983</v>
       </c>
       <c r="T36" s="0" t="s">
         <v>380</v>
@@ -5592,11 +5670,11 @@
         <v>381</v>
       </c>
       <c r="V36" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="W36" s="0" t="s">
         <v>382</v>
       </c>
-      <c r="W36" s="0" t="s">
-        <v>383</v>
-      </c>
       <c r="X36" s="0">
         <v>5</v>
       </c>
@@ -5616,78 +5694,78 @@
         <v>5</v>
       </c>
       <c r="AP36" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C37" s="2">
-        <v>45970</v>
+        <v>45986</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45986.574325081</v>
+      </c>
+      <c r="H37" s="0">
+        <v>3</v>
+      </c>
+      <c r="I37" s="0">
+        <v>5</v>
+      </c>
+      <c r="J37" s="0">
+        <v>3</v>
+      </c>
+      <c r="L37" s="0" t="s">
         <v>385</v>
       </c>
-      <c r="F37" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45970.4829323264</v>
-      </c>
-      <c r="H37" s="0">
-        <v>5</v>
-      </c>
-      <c r="I37" s="0">
-        <v>5</v>
-      </c>
-      <c r="J37" s="0">
-        <v>5</v>
-      </c>
-      <c r="L37" s="0" t="s">
+      <c r="M37" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="M37" s="0" t="s">
+      <c r="N37" s="0" t="s">
         <v>387</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="O37" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P37" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q37" s="0" t="s">
         <v>388</v>
       </c>
-      <c r="O37" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P37" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q37" s="0" t="s">
+      <c r="R37" s="2">
+        <v>45983</v>
+      </c>
+      <c r="S37" s="2">
+        <v>45986</v>
+      </c>
+      <c r="T37" s="0" t="s">
         <v>389</v>
       </c>
-      <c r="R37" s="2">
-        <v>45967</v>
-      </c>
-      <c r="S37" s="2">
-        <v>45969</v>
-      </c>
-      <c r="T37" s="0" t="s">
+      <c r="U37" s="0" t="s">
         <v>390</v>
       </c>
-      <c r="U37" s="0" t="s">
+      <c r="V37" s="0" t="s">
         <v>391</v>
       </c>
-      <c r="V37" s="0" t="s">
+      <c r="W37" s="0" t="s">
         <v>392</v>
       </c>
-      <c r="W37" s="0" t="s">
-        <v>393</v>
-      </c>
       <c r="X37" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y37" s="0">
         <v>5</v>
@@ -5696,69 +5774,72 @@
         <v>5</v>
       </c>
       <c r="AB37" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC37" s="0">
         <v>5</v>
       </c>
       <c r="AD37" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP37" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="2">
-        <v>45965</v>
+        <v>45981</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45981.6819216319</v>
+      </c>
+      <c r="H38" s="0">
+        <v>5</v>
+      </c>
+      <c r="I38" s="0">
+        <v>5</v>
+      </c>
+      <c r="J38" s="0">
+        <v>5</v>
+      </c>
+      <c r="L38" s="0" t="s">
         <v>395</v>
       </c>
-      <c r="F38" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45965.8421596644</v>
-      </c>
-      <c r="H38" s="0">
-        <v>5</v>
-      </c>
-      <c r="I38" s="0">
-        <v>5</v>
-      </c>
-      <c r="J38" s="0">
-        <v>5</v>
-      </c>
-      <c r="L38" s="0" t="s">
+      <c r="M38" s="0" t="s">
         <v>396</v>
       </c>
       <c r="N38" s="0" t="s">
         <v>397</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P38" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q38" s="0" t="s">
         <v>398</v>
       </c>
       <c r="R38" s="2">
-        <v>45962</v>
+        <v>45970</v>
       </c>
       <c r="S38" s="2">
-        <v>45965</v>
+        <v>45977</v>
       </c>
       <c r="T38" s="0" t="s">
         <v>399</v>
@@ -5791,7 +5872,7 @@
         <v>5</v>
       </c>
       <c r="AP38" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
@@ -5802,7 +5883,7 @@
         <v>43</v>
       </c>
       <c r="C39" s="2">
-        <v>45962</v>
+        <v>45970</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>44</v>
@@ -5811,56 +5892,53 @@
         <v>404</v>
       </c>
       <c r="F39" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45970.7607620602</v>
+      </c>
+      <c r="H39" s="0">
+        <v>5</v>
+      </c>
+      <c r="I39" s="0">
+        <v>5</v>
+      </c>
+      <c r="J39" s="0">
+        <v>5</v>
+      </c>
+      <c r="L39" s="0" t="s">
         <v>405</v>
       </c>
-      <c r="G39" s="2">
-        <v>45962.6437613773</v>
-      </c>
-      <c r="H39" s="0">
-        <v>5</v>
-      </c>
-      <c r="I39" s="0">
-        <v>5</v>
-      </c>
-      <c r="J39" s="0">
-        <v>5</v>
-      </c>
-      <c r="L39" s="0" t="s">
+      <c r="N39" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="M39" s="0" t="s">
+      <c r="O39" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P39" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q39" s="0" t="s">
         <v>407</v>
       </c>
-      <c r="N39" s="3" t="s">
+      <c r="R39" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S39" s="2">
+        <v>45970</v>
+      </c>
+      <c r="T39" s="0" t="s">
         <v>408</v>
       </c>
-      <c r="O39" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P39" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q39" s="0" t="s">
+      <c r="U39" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="R39" s="2">
-        <v>45959</v>
-      </c>
-      <c r="S39" s="2">
-        <v>45962</v>
-      </c>
-      <c r="T39" s="0" t="s">
+      <c r="V39" s="0" t="s">
         <v>410</v>
       </c>
-      <c r="U39" s="0" t="s">
+      <c r="W39" s="0" t="s">
         <v>411</v>
       </c>
-      <c r="V39" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="W39" s="0" t="s">
-        <v>413</v>
-      </c>
       <c r="X39" s="0">
         <v>5</v>
       </c>
@@ -5880,76 +5958,76 @@
         <v>5</v>
       </c>
       <c r="AP39" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="2">
-        <v>45959</v>
+        <v>45970</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45970.4829323264</v>
+      </c>
+      <c r="H40" s="0">
+        <v>5</v>
+      </c>
+      <c r="I40" s="0">
+        <v>5</v>
+      </c>
+      <c r="J40" s="0">
+        <v>5</v>
+      </c>
+      <c r="L40" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="M40" s="0" t="s">
         <v>415</v>
       </c>
-      <c r="F40" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45959.6416564352</v>
-      </c>
-      <c r="H40" s="0">
-        <v>5</v>
-      </c>
-      <c r="I40" s="0">
-        <v>5</v>
-      </c>
-      <c r="J40" s="0">
-        <v>5</v>
-      </c>
-      <c r="L40" s="0" t="s">
+      <c r="N40" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="M40" s="0" t="s">
+      <c r="O40" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P40" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q40" s="0" t="s">
         <v>417</v>
       </c>
-      <c r="N40" s="0" t="s">
+      <c r="R40" s="2">
+        <v>45967</v>
+      </c>
+      <c r="S40" s="2">
+        <v>45969</v>
+      </c>
+      <c r="T40" s="0" t="s">
         <v>418</v>
       </c>
-      <c r="O40" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P40" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q40" s="0" t="s">
+      <c r="U40" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="R40" s="2">
-        <v>45955</v>
-      </c>
-      <c r="S40" s="2">
-        <v>45959</v>
-      </c>
-      <c r="T40" s="0" t="s">
+      <c r="V40" s="0" t="s">
         <v>420</v>
       </c>
-      <c r="U40" s="0" t="s">
+      <c r="W40" s="0" t="s">
         <v>421</v>
       </c>
-      <c r="V40" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="W40" s="0" t="s">
-        <v>423</v>
-      </c>
       <c r="X40" s="0">
         <v>5</v>
       </c>
@@ -5957,7 +6035,7 @@
         <v>5</v>
       </c>
       <c r="AA40" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB40" s="0">
         <v>5</v>
@@ -5966,78 +6044,78 @@
         <v>5</v>
       </c>
       <c r="AD40" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP40" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="C41" s="2">
-        <v>45955</v>
+        <v>45965</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E41" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45965.8421596644</v>
+      </c>
+      <c r="H41" s="0">
+        <v>5</v>
+      </c>
+      <c r="I41" s="0">
+        <v>5</v>
+      </c>
+      <c r="J41" s="0">
+        <v>5</v>
+      </c>
+      <c r="L41" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="N41" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="F41" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45955.8044966319</v>
-      </c>
-      <c r="H41" s="0">
-        <v>4</v>
-      </c>
-      <c r="I41" s="0">
-        <v>5</v>
-      </c>
-      <c r="J41" s="0">
-        <v>4</v>
-      </c>
-      <c r="L41" s="0" t="s">
+      <c r="O41" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P41" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q41" s="0" t="s">
         <v>426</v>
       </c>
-      <c r="N41" s="0" t="s">
+      <c r="R41" s="2">
+        <v>45962</v>
+      </c>
+      <c r="S41" s="2">
+        <v>45965</v>
+      </c>
+      <c r="T41" s="0" t="s">
         <v>427</v>
       </c>
-      <c r="O41" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P41" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q41" s="0" t="s">
+      <c r="U41" s="0" t="s">
         <v>428</v>
       </c>
-      <c r="R41" s="2">
-        <v>45954</v>
-      </c>
-      <c r="S41" s="2">
-        <v>45955</v>
-      </c>
-      <c r="T41" s="0" t="s">
+      <c r="V41" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="U41" s="0" t="s">
+      <c r="W41" s="0" t="s">
         <v>430</v>
       </c>
-      <c r="V41" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="W41" s="0" t="s">
-        <v>432</v>
-      </c>
       <c r="X41" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y41" s="0">
         <v>5</v>
@@ -6049,66 +6127,69 @@
         <v>5</v>
       </c>
       <c r="AC41" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD41" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP41" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="2">
-        <v>45954</v>
+        <v>45962</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45962.6437613773</v>
+      </c>
+      <c r="H42" s="0">
+        <v>5</v>
+      </c>
+      <c r="I42" s="0">
+        <v>5</v>
+      </c>
+      <c r="J42" s="0">
+        <v>5</v>
+      </c>
+      <c r="L42" s="0" t="s">
         <v>434</v>
       </c>
-      <c r="F42" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="G42" s="2">
-        <v>45954.9526523148</v>
-      </c>
-      <c r="H42" s="0">
-        <v>5</v>
-      </c>
-      <c r="I42" s="0">
-        <v>5</v>
-      </c>
-      <c r="J42" s="0">
-        <v>5</v>
-      </c>
-      <c r="L42" s="0" t="s">
+      <c r="M42" s="0" t="s">
         <v>435</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>436</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q42" s="0" t="s">
         <v>437</v>
       </c>
       <c r="R42" s="2">
-        <v>45949</v>
+        <v>45959</v>
       </c>
       <c r="S42" s="2">
-        <v>45954</v>
+        <v>45962</v>
       </c>
       <c r="T42" s="0" t="s">
         <v>438</v>
@@ -6141,7 +6222,7 @@
         <v>5</v>
       </c>
       <c r="AP42" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -6152,7 +6233,7 @@
         <v>43</v>
       </c>
       <c r="C43" s="2">
-        <v>45949</v>
+        <v>45959</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>44</v>
@@ -6161,10 +6242,10 @@
         <v>443</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="G43" s="2">
-        <v>45949.8261354282</v>
+        <v>45959.6416564352</v>
       </c>
       <c r="H43" s="0">
         <v>5</v>
@@ -6178,35 +6259,38 @@
       <c r="L43" s="0" t="s">
         <v>444</v>
       </c>
+      <c r="M43" s="0" t="s">
+        <v>445</v>
+      </c>
       <c r="N43" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O43" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q43" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R43" s="2">
-        <v>45946</v>
+        <v>45955</v>
       </c>
       <c r="S43" s="2">
-        <v>45949</v>
+        <v>45959</v>
       </c>
       <c r="T43" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="U43" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="V43" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="W43" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="X43" s="0">
         <v>5</v>
@@ -6215,7 +6299,7 @@
         <v>5</v>
       </c>
       <c r="AA43" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB43" s="0">
         <v>5</v>
@@ -6224,66 +6308,63 @@
         <v>5</v>
       </c>
       <c r="AD43" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP43" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C44" s="2">
-        <v>45946</v>
+        <v>45955</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="G44" s="2">
-        <v>45946.8340835069</v>
+        <v>45955.8044966319</v>
       </c>
       <c r="H44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I44" s="0">
         <v>5</v>
       </c>
       <c r="J44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="M44" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="N44" s="0" t="s">
         <v>455</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P44" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q44" s="0" t="s">
         <v>456</v>
       </c>
       <c r="R44" s="2">
-        <v>45941</v>
+        <v>45954</v>
       </c>
       <c r="S44" s="2">
-        <v>45946</v>
+        <v>45955</v>
       </c>
       <c r="T44" s="0" t="s">
         <v>457</v>
@@ -6298,7 +6379,7 @@
         <v>460</v>
       </c>
       <c r="X44" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="0">
         <v>5</v>
@@ -6310,13 +6391,13 @@
         <v>5</v>
       </c>
       <c r="AC44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD44" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP44" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
@@ -6327,7 +6408,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="2">
-        <v>45938</v>
+        <v>45954</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>44</v>
@@ -6336,10 +6417,10 @@
         <v>462</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="G45" s="2">
-        <v>45938.7601655556</v>
+        <v>45954.9526523148</v>
       </c>
       <c r="H45" s="0">
         <v>5</v>
@@ -6357,19 +6438,19 @@
         <v>464</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q45" s="0" t="s">
         <v>465</v>
       </c>
       <c r="R45" s="2">
-        <v>45932</v>
+        <v>45949</v>
       </c>
       <c r="S45" s="2">
-        <v>45935</v>
+        <v>45954</v>
       </c>
       <c r="T45" s="0" t="s">
         <v>466</v>
@@ -6402,7 +6483,7 @@
         <v>5</v>
       </c>
       <c r="AP45" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
@@ -6413,7 +6494,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="2">
-        <v>45937</v>
+        <v>45949</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>44</v>
@@ -6422,10 +6503,10 @@
         <v>471</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="G46" s="2">
-        <v>45937.8034676042</v>
+        <v>45949.8261354282</v>
       </c>
       <c r="H46" s="0">
         <v>5</v>
@@ -6443,19 +6524,19 @@
         <v>473</v>
       </c>
       <c r="O46" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P46" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q46" s="0" t="s">
         <v>474</v>
       </c>
       <c r="R46" s="2">
-        <v>45935</v>
+        <v>45946</v>
       </c>
       <c r="S46" s="2">
-        <v>45937</v>
+        <v>45949</v>
       </c>
       <c r="T46" s="0" t="s">
         <v>475</v>
@@ -6485,10 +6566,10 @@
         <v>5</v>
       </c>
       <c r="AD46" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP46" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47">
@@ -6499,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="C47" s="2">
-        <v>45928</v>
+        <v>45946</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>44</v>
@@ -6508,56 +6589,56 @@
         <v>480</v>
       </c>
       <c r="F47" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45946.8340835069</v>
+      </c>
+      <c r="H47" s="0">
+        <v>5</v>
+      </c>
+      <c r="I47" s="0">
+        <v>5</v>
+      </c>
+      <c r="J47" s="0">
+        <v>5</v>
+      </c>
+      <c r="L47" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="G47" s="2">
-        <v>45928.7262096412</v>
-      </c>
-      <c r="H47" s="0">
-        <v>5</v>
-      </c>
-      <c r="I47" s="0">
-        <v>5</v>
-      </c>
-      <c r="J47" s="0">
-        <v>5</v>
-      </c>
-      <c r="L47" s="0" t="s">
+      <c r="M47" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="M47" s="0" t="s">
+      <c r="N47" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P47" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q47" s="0" t="s">
         <v>484</v>
       </c>
-      <c r="O47" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P47" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q47" s="0" t="s">
+      <c r="R47" s="2">
+        <v>45941</v>
+      </c>
+      <c r="S47" s="2">
+        <v>45946</v>
+      </c>
+      <c r="T47" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="R47" s="2">
-        <v>45925</v>
-      </c>
-      <c r="S47" s="2">
-        <v>45928</v>
-      </c>
-      <c r="T47" s="0" t="s">
+      <c r="U47" s="0" t="s">
         <v>486</v>
       </c>
-      <c r="U47" s="0" t="s">
+      <c r="V47" s="0" t="s">
         <v>487</v>
       </c>
-      <c r="V47" s="0" t="s">
+      <c r="W47" s="0" t="s">
         <v>488</v>
       </c>
-      <c r="W47" s="0" t="s">
-        <v>489</v>
-      </c>
       <c r="X47" s="0">
         <v>5</v>
       </c>
@@ -6577,73 +6658,73 @@
         <v>5</v>
       </c>
       <c r="AP47" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="2">
-        <v>45924</v>
+        <v>45938</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45938.7601655556</v>
+      </c>
+      <c r="H48" s="0">
+        <v>5</v>
+      </c>
+      <c r="I48" s="0">
+        <v>5</v>
+      </c>
+      <c r="J48" s="0">
+        <v>5</v>
+      </c>
+      <c r="L48" s="0" t="s">
         <v>491</v>
       </c>
-      <c r="F48" s="0" t="s">
-        <v>481</v>
-      </c>
-      <c r="G48" s="2">
-        <v>45924.6507670833</v>
-      </c>
-      <c r="H48" s="0">
-        <v>5</v>
-      </c>
-      <c r="I48" s="0">
-        <v>5</v>
-      </c>
-      <c r="J48" s="0">
-        <v>5</v>
-      </c>
-      <c r="L48" s="0" t="s">
+      <c r="N48" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="N48" s="0" t="s">
+      <c r="O48" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P48" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q48" s="0" t="s">
         <v>493</v>
       </c>
-      <c r="O48" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P48" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q48" s="0" t="s">
+      <c r="R48" s="2">
+        <v>45932</v>
+      </c>
+      <c r="S48" s="2">
+        <v>45935</v>
+      </c>
+      <c r="T48" s="0" t="s">
         <v>494</v>
       </c>
-      <c r="R48" s="2">
-        <v>45921</v>
-      </c>
-      <c r="S48" s="2">
-        <v>45924</v>
-      </c>
-      <c r="T48" s="0" t="s">
+      <c r="U48" s="0" t="s">
         <v>495</v>
       </c>
-      <c r="U48" s="0" t="s">
+      <c r="V48" s="0" t="s">
         <v>496</v>
       </c>
-      <c r="V48" s="0" t="s">
+      <c r="W48" s="0" t="s">
         <v>497</v>
       </c>
-      <c r="W48" s="0" t="s">
-        <v>498</v>
-      </c>
       <c r="X48" s="0">
         <v>5</v>
       </c>
@@ -6663,73 +6744,73 @@
         <v>5</v>
       </c>
       <c r="AP48" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="2">
-        <v>45923</v>
+        <v>45937</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45937.8034676042</v>
+      </c>
+      <c r="H49" s="0">
+        <v>5</v>
+      </c>
+      <c r="I49" s="0">
+        <v>5</v>
+      </c>
+      <c r="J49" s="0">
+        <v>5</v>
+      </c>
+      <c r="L49" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="F49" s="0" t="s">
-        <v>481</v>
-      </c>
-      <c r="G49" s="2">
-        <v>45923.3761746296</v>
-      </c>
-      <c r="H49" s="0">
-        <v>5</v>
-      </c>
-      <c r="I49" s="0">
-        <v>5</v>
-      </c>
-      <c r="J49" s="0">
-        <v>5</v>
-      </c>
-      <c r="L49" s="0" t="s">
+      <c r="N49" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="N49" s="0" t="s">
+      <c r="O49" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P49" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q49" s="0" t="s">
         <v>502</v>
       </c>
-      <c r="O49" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P49" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q49" s="0" t="s">
+      <c r="R49" s="2">
+        <v>45935</v>
+      </c>
+      <c r="S49" s="2">
+        <v>45937</v>
+      </c>
+      <c r="T49" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="R49" s="2">
-        <v>45918</v>
-      </c>
-      <c r="S49" s="2">
-        <v>45921</v>
-      </c>
-      <c r="T49" s="0" t="s">
+      <c r="U49" s="0" t="s">
         <v>504</v>
       </c>
-      <c r="U49" s="0" t="s">
+      <c r="V49" s="0" t="s">
         <v>505</v>
       </c>
-      <c r="V49" s="0" t="s">
+      <c r="W49" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="W49" s="0" t="s">
-        <v>507</v>
-      </c>
       <c r="X49" s="0">
         <v>5</v>
       </c>
@@ -6746,33 +6827,33 @@
         <v>5</v>
       </c>
       <c r="AD49" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP49" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="2">
-        <v>45922</v>
+        <v>45928</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="F50" s="0" t="s">
         <v>509</v>
       </c>
-      <c r="F50" s="0" t="s">
-        <v>481</v>
-      </c>
       <c r="G50" s="2">
-        <v>45922.4128161921</v>
+        <v>45928.7262096412</v>
       </c>
       <c r="H50" s="0">
         <v>5</v>
@@ -6786,35 +6867,38 @@
       <c r="L50" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="N50" s="0" t="s">
+      <c r="M50" s="0" t="s">
         <v>511</v>
       </c>
+      <c r="N50" s="3" t="s">
+        <v>512</v>
+      </c>
       <c r="O50" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q50" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="R50" s="2">
-        <v>45914</v>
+        <v>45925</v>
       </c>
       <c r="S50" s="2">
-        <v>45918</v>
+        <v>45928</v>
       </c>
       <c r="T50" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="U50" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="V50" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="W50" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="X50" s="0">
         <v>5</v>
@@ -6835,60 +6919,60 @@
         <v>5</v>
       </c>
       <c r="AP50" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="C51" s="2">
-        <v>45920</v>
+        <v>45924</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G51" s="2">
-        <v>45920.6962243171</v>
+        <v>45924.6507670833</v>
       </c>
       <c r="H51" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="0">
         <v>5</v>
       </c>
       <c r="J51" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L51" s="0" t="s">
         <v>520</v>
       </c>
-      <c r="M51" s="0" t="s">
+      <c r="N51" s="0" t="s">
         <v>521</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q51" s="0" t="s">
         <v>522</v>
       </c>
       <c r="R51" s="2">
-        <v>45900</v>
+        <v>45921</v>
       </c>
       <c r="S51" s="2">
-        <v>45906</v>
+        <v>45924</v>
       </c>
       <c r="T51" s="0" t="s">
         <v>523</v>
@@ -6915,13 +6999,13 @@
         <v>5</v>
       </c>
       <c r="AC51" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD51" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP51" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
@@ -6932,7 +7016,7 @@
         <v>43</v>
       </c>
       <c r="C52" s="2">
-        <v>45916</v>
+        <v>45923</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>44</v>
@@ -6941,10 +7025,10 @@
         <v>528</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="G52" s="2">
-        <v>45916.4699822917</v>
+        <v>45923.3761746296</v>
       </c>
       <c r="H52" s="0">
         <v>5</v>
@@ -6962,37 +7046,37 @@
         <v>530</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q52" s="0" t="s">
         <v>531</v>
       </c>
       <c r="R52" s="2">
-        <v>45913</v>
+        <v>45918</v>
       </c>
       <c r="S52" s="2">
-        <v>45914</v>
+        <v>45921</v>
       </c>
       <c r="T52" s="0" t="s">
         <v>532</v>
       </c>
       <c r="U52" s="0" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="V52" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="W52" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="X52" s="0">
         <v>5</v>
       </c>
       <c r="Y52" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA52" s="0">
         <v>5</v>
@@ -7007,30 +7091,30 @@
         <v>5</v>
       </c>
       <c r="AP52" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="2">
-        <v>45914</v>
+        <v>45922</v>
       </c>
       <c r="D53" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="G53" s="2">
-        <v>45914.5820426389</v>
+        <v>45922.4128161921</v>
       </c>
       <c r="H53" s="0">
         <v>5</v>
@@ -7042,37 +7126,37 @@
         <v>5</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N53" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q53" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R53" s="2">
-        <v>45907</v>
+        <v>45914</v>
       </c>
       <c r="S53" s="2">
-        <v>45913</v>
+        <v>45918</v>
       </c>
       <c r="T53" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="U53" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="V53" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="W53" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="X53" s="0">
         <v>5</v>
@@ -7093,72 +7177,72 @@
         <v>5</v>
       </c>
       <c r="AP53" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C54" s="2">
-        <v>45909</v>
+        <v>45920</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>481</v>
+        <v>547</v>
       </c>
       <c r="G54" s="2">
-        <v>45909.7231987963</v>
+        <v>45920.6962243171</v>
       </c>
       <c r="H54" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I54" s="0">
         <v>5</v>
       </c>
       <c r="J54" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>549</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P54" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q54" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="R54" s="2">
+        <v>45900</v>
+      </c>
+      <c r="S54" s="2">
         <v>45906</v>
       </c>
-      <c r="S54" s="2">
-        <v>45907</v>
-      </c>
       <c r="T54" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="U54" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="V54" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="W54" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="X54" s="0">
         <v>5</v>
@@ -7173,36 +7257,36 @@
         <v>5</v>
       </c>
       <c r="AC54" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD54" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP54" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="2">
-        <v>45900</v>
+        <v>45916</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G55" s="2">
-        <v>45900.6461770602</v>
+        <v>45916.4699822917</v>
       </c>
       <c r="H55" s="0">
         <v>5</v>
@@ -7214,43 +7298,43 @@
         <v>5</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>555</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
+      </c>
+      <c r="N55" s="0" t="s">
+        <v>558</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P55" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q55" s="0" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="R55" s="2">
-        <v>45897</v>
+        <v>45913</v>
       </c>
       <c r="S55" s="2">
-        <v>45900</v>
+        <v>45914</v>
       </c>
       <c r="T55" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="U55" s="0" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="V55" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="W55" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="X55" s="0">
         <v>5</v>
       </c>
       <c r="Y55" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA55" s="0">
         <v>5</v>
@@ -7265,30 +7349,30 @@
         <v>5</v>
       </c>
       <c r="AP55" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="2">
-        <v>45899</v>
+        <v>45914</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>563</v>
+        <v>44</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>564</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G56" s="2">
-        <v>45898.9353472222</v>
+        <v>45914.5820426389</v>
       </c>
       <c r="H56" s="0">
         <v>5</v>
@@ -7306,19 +7390,19 @@
         <v>566</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P56" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q56" s="0" t="s">
         <v>567</v>
       </c>
       <c r="R56" s="2">
-        <v>45893</v>
+        <v>45907</v>
       </c>
       <c r="S56" s="2">
-        <v>45896</v>
+        <v>45913</v>
       </c>
       <c r="T56" s="0" t="s">
         <v>568</v>
@@ -7332,6 +7416,9 @@
       <c r="W56" s="0" t="s">
         <v>571</v>
       </c>
+      <c r="X56" s="0">
+        <v>5</v>
+      </c>
       <c r="Y56" s="0">
         <v>5</v>
       </c>
@@ -7344,11 +7431,11 @@
       <c r="AC56" s="0">
         <v>5</v>
       </c>
-      <c r="AE56" s="0">
+      <c r="AD56" s="0">
         <v>5</v>
       </c>
       <c r="AP56" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57">
@@ -7359,7 +7446,7 @@
         <v>43</v>
       </c>
       <c r="C57" s="2">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>44</v>
@@ -7368,10 +7455,10 @@
         <v>573</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G57" s="2">
-        <v>45897.7557321412</v>
+        <v>45909.7231987963</v>
       </c>
       <c r="H57" s="0">
         <v>5</v>
@@ -7385,39 +7472,36 @@
       <c r="L57" s="0" t="s">
         <v>574</v>
       </c>
-      <c r="M57" s="0" t="s">
+      <c r="N57" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="N57" s="0" t="s">
+      <c r="O57" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P57" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q57" s="0" t="s">
         <v>576</v>
       </c>
-      <c r="O57" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P57" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q57" s="0" t="s">
+      <c r="R57" s="2">
+        <v>45906</v>
+      </c>
+      <c r="S57" s="2">
+        <v>45907</v>
+      </c>
+      <c r="T57" s="0" t="s">
         <v>577</v>
       </c>
-      <c r="R57" s="2">
-        <v>45896</v>
-      </c>
-      <c r="S57" s="2">
-        <v>45897</v>
-      </c>
-      <c r="T57" s="0" t="s">
+      <c r="U57" s="0" t="s">
         <v>578</v>
       </c>
-      <c r="U57" s="0" t="s">
+      <c r="V57" s="0" t="s">
         <v>579</v>
       </c>
-      <c r="V57" s="0" t="s">
+      <c r="W57" s="0" t="s">
         <v>580</v>
       </c>
-      <c r="W57" s="0" t="s">
-        <v>581</v>
-      </c>
       <c r="X57" s="0">
         <v>5</v>
       </c>
@@ -7437,60 +7521,60 @@
         <v>5</v>
       </c>
       <c r="AP57" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="2">
-        <v>45894</v>
+        <v>45900</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45900.6461770602</v>
+      </c>
+      <c r="H58" s="0">
+        <v>5</v>
+      </c>
+      <c r="I58" s="0">
+        <v>5</v>
+      </c>
+      <c r="J58" s="0">
+        <v>5</v>
+      </c>
+      <c r="L58" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="F58" s="0" t="s">
-        <v>519</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45894.8301493981</v>
-      </c>
-      <c r="H58" s="0">
-        <v>5</v>
-      </c>
-      <c r="I58" s="0">
-        <v>5</v>
-      </c>
-      <c r="J58" s="0">
-        <v>5</v>
-      </c>
-      <c r="L58" s="0" t="s">
+      <c r="N58" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="N58" s="0" t="s">
-        <v>576</v>
-      </c>
       <c r="O58" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P58" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q58" s="0" t="s">
         <v>585</v>
       </c>
       <c r="R58" s="2">
-        <v>45890</v>
+        <v>45897</v>
       </c>
       <c r="S58" s="2">
-        <v>45893</v>
+        <v>45900</v>
       </c>
       <c r="T58" s="0" t="s">
         <v>586</v>
@@ -7523,7 +7607,7 @@
         <v>5</v>
       </c>
       <c r="AP58" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -7534,19 +7618,19 @@
         <v>43</v>
       </c>
       <c r="C59" s="2">
-        <v>45889</v>
+        <v>45899</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>44</v>
+        <v>591</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G59" s="2">
-        <v>45889.6599939468</v>
+        <v>45898.9353472222</v>
       </c>
       <c r="H59" s="0">
         <v>5</v>
@@ -7558,28 +7642,25 @@
         <v>5</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>592</v>
-      </c>
-      <c r="M59" s="0" t="s">
         <v>593</v>
       </c>
       <c r="N59" s="0" t="s">
         <v>594</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q59" s="0" t="s">
         <v>595</v>
       </c>
       <c r="R59" s="2">
-        <v>45886</v>
+        <v>45893</v>
       </c>
       <c r="S59" s="2">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="T59" s="0" t="s">
         <v>596</v>
@@ -7593,9 +7674,6 @@
       <c r="W59" s="0" t="s">
         <v>599</v>
       </c>
-      <c r="X59" s="0">
-        <v>5</v>
-      </c>
       <c r="Y59" s="0">
         <v>5</v>
       </c>
@@ -7608,11 +7686,11 @@
       <c r="AC59" s="0">
         <v>5</v>
       </c>
-      <c r="AD59" s="0">
+      <c r="AE59" s="0">
         <v>5</v>
       </c>
       <c r="AP59" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -7623,7 +7701,7 @@
         <v>43</v>
       </c>
       <c r="C60" s="2">
-        <v>45888</v>
+        <v>45897</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>44</v>
@@ -7632,10 +7710,10 @@
         <v>601</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G60" s="2">
-        <v>45888.5413223148</v>
+        <v>45897.7557321412</v>
       </c>
       <c r="H60" s="0">
         <v>5</v>
@@ -7646,38 +7724,41 @@
       <c r="J60" s="0">
         <v>5</v>
       </c>
-      <c r="L60" s="3" t="s">
+      <c r="L60" s="0" t="s">
         <v>602</v>
       </c>
-      <c r="N60" s="3" t="s">
+      <c r="M60" s="0" t="s">
         <v>603</v>
       </c>
+      <c r="N60" s="0" t="s">
+        <v>604</v>
+      </c>
       <c r="O60" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q60" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R60" s="2">
-        <v>45883</v>
+        <v>45896</v>
       </c>
       <c r="S60" s="2">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="T60" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="U60" s="0" t="s">
-        <v>218</v>
+        <v>607</v>
       </c>
       <c r="V60" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="W60" s="0" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="X60" s="0">
         <v>5</v>
@@ -7698,30 +7779,30 @@
         <v>5</v>
       </c>
       <c r="AP60" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="2">
-        <v>45884</v>
+        <v>45894</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G61" s="2">
-        <v>45884.5080971296</v>
+        <v>45894.8301493981</v>
       </c>
       <c r="H61" s="0">
         <v>5</v>
@@ -7733,37 +7814,37 @@
         <v>5</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N61" s="0" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P61" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q61" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R61" s="2">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="S61" s="2">
-        <v>45883</v>
+        <v>45893</v>
       </c>
       <c r="T61" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="U61" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="V61" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="W61" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="X61" s="0">
         <v>5</v>
@@ -7784,30 +7865,30 @@
         <v>5</v>
       </c>
       <c r="AP61" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="2">
-        <v>45884</v>
+        <v>45889</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G62" s="2">
-        <v>45884.3282971181</v>
+        <v>45889.6599939468</v>
       </c>
       <c r="H62" s="0">
         <v>5</v>
@@ -7819,37 +7900,40 @@
         <v>5</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
+      </c>
+      <c r="M62" s="0" t="s">
+        <v>621</v>
       </c>
       <c r="N62" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q62" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="R62" s="2">
-        <v>45876</v>
+        <v>45886</v>
       </c>
       <c r="S62" s="2">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="T62" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="U62" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="V62" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="W62" s="0" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="X62" s="0">
         <v>5</v>
@@ -7870,30 +7954,30 @@
         <v>5</v>
       </c>
       <c r="AP62" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C63" s="2">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G63" s="2">
-        <v>45880.7327610417</v>
+        <v>45888.5413223148</v>
       </c>
       <c r="H63" s="0">
         <v>5</v>
@@ -7904,38 +7988,38 @@
       <c r="J63" s="0">
         <v>5</v>
       </c>
-      <c r="L63" s="0" t="s">
-        <v>628</v>
-      </c>
-      <c r="N63" s="0" t="s">
-        <v>629</v>
+      <c r="L63" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>631</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q63" s="0" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="R63" s="2">
-        <v>45877</v>
+        <v>45883</v>
       </c>
       <c r="S63" s="2">
-        <v>45880</v>
+        <v>45886</v>
       </c>
       <c r="T63" s="0" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="U63" s="0" t="s">
-        <v>632</v>
+        <v>247</v>
       </c>
       <c r="V63" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="W63" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="X63" s="0">
         <v>5</v>
@@ -7956,30 +8040,30 @@
         <v>5</v>
       </c>
       <c r="AP63" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="2">
-        <v>45877</v>
+        <v>45884</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G64" s="2">
-        <v>45877.4773553819</v>
+        <v>45884.5080971296</v>
       </c>
       <c r="H64" s="0">
         <v>5</v>
@@ -7991,37 +8075,37 @@
         <v>5</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q64" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R64" s="2">
-        <v>45873</v>
+        <v>45880</v>
       </c>
       <c r="S64" s="2">
-        <v>45876</v>
+        <v>45883</v>
       </c>
       <c r="T64" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="U64" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="V64" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="W64" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="X64" s="0">
         <v>5</v>
@@ -8042,30 +8126,30 @@
         <v>5</v>
       </c>
       <c r="AP64" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="2">
-        <v>45873</v>
+        <v>45884</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="G65" s="2">
-        <v>45873.7425913657</v>
+        <v>45884.3282971181</v>
       </c>
       <c r="H65" s="0">
         <v>5</v>
@@ -8076,38 +8160,38 @@
       <c r="J65" s="0">
         <v>5</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>646</v>
+      <c r="L65" s="0" t="s">
+        <v>647</v>
       </c>
       <c r="N65" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P65" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q65" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R65" s="2">
-        <v>45871</v>
+        <v>45876</v>
       </c>
       <c r="S65" s="2">
-        <v>45873</v>
+        <v>45877</v>
       </c>
       <c r="T65" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="U65" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="V65" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="W65" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="X65" s="0">
         <v>5</v>
@@ -8128,30 +8212,30 @@
         <v>5</v>
       </c>
       <c r="AP65" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C66" s="2">
-        <v>45871</v>
+        <v>45880</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>655</v>
+        <v>547</v>
       </c>
       <c r="G66" s="2">
-        <v>45871.6773271875</v>
+        <v>45880.7327610417</v>
       </c>
       <c r="H66" s="0">
         <v>5</v>
@@ -8169,19 +8253,19 @@
         <v>657</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q66" s="0" t="s">
         <v>658</v>
       </c>
       <c r="R66" s="2">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="S66" s="2">
-        <v>45871</v>
+        <v>45880</v>
       </c>
       <c r="T66" s="0" t="s">
         <v>659</v>
@@ -8214,7 +8298,7 @@
         <v>5</v>
       </c>
       <c r="AP66" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
@@ -8225,7 +8309,7 @@
         <v>43</v>
       </c>
       <c r="C67" s="2">
-        <v>45866</v>
+        <v>45877</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>44</v>
@@ -8234,10 +8318,10 @@
         <v>664</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>655</v>
+        <v>547</v>
       </c>
       <c r="G67" s="2">
-        <v>45866.5828246181</v>
+        <v>45877.4773553819</v>
       </c>
       <c r="H67" s="0">
         <v>5</v>
@@ -8251,39 +8335,36 @@
       <c r="L67" s="0" t="s">
         <v>665</v>
       </c>
-      <c r="M67" s="0" t="s">
+      <c r="N67" s="0" t="s">
         <v>666</v>
       </c>
-      <c r="N67" s="0" t="s">
+      <c r="O67" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P67" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q67" s="0" t="s">
         <v>667</v>
       </c>
-      <c r="O67" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P67" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q67" s="0" t="s">
+      <c r="R67" s="2">
+        <v>45873</v>
+      </c>
+      <c r="S67" s="2">
+        <v>45876</v>
+      </c>
+      <c r="T67" s="0" t="s">
         <v>668</v>
       </c>
-      <c r="R67" s="2">
-        <v>45863</v>
-      </c>
-      <c r="S67" s="2">
-        <v>45865</v>
-      </c>
-      <c r="T67" s="0" t="s">
+      <c r="U67" s="0" t="s">
         <v>669</v>
       </c>
-      <c r="U67" s="0" t="s">
+      <c r="V67" s="0" t="s">
         <v>670</v>
       </c>
-      <c r="V67" s="0" t="s">
+      <c r="W67" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="W67" s="0" t="s">
-        <v>672</v>
-      </c>
       <c r="X67" s="0">
         <v>5</v>
       </c>
@@ -8303,73 +8384,73 @@
         <v>5</v>
       </c>
       <c r="AP67" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="2">
-        <v>45865</v>
+        <v>45873</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E68" s="0" t="s">
+        <v>673</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45873.7425913657</v>
+      </c>
+      <c r="H68" s="0">
+        <v>5</v>
+      </c>
+      <c r="I68" s="0">
+        <v>5</v>
+      </c>
+      <c r="J68" s="0">
+        <v>5</v>
+      </c>
+      <c r="L68" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="F68" s="0" t="s">
-        <v>655</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45865.9243556134</v>
-      </c>
-      <c r="H68" s="0">
-        <v>5</v>
-      </c>
-      <c r="I68" s="0">
-        <v>5</v>
-      </c>
-      <c r="J68" s="0">
-        <v>5</v>
-      </c>
-      <c r="L68" s="0" t="s">
+      <c r="N68" s="0" t="s">
         <v>675</v>
       </c>
-      <c r="N68" s="0" t="s">
+      <c r="O68" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P68" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q68" s="0" t="s">
         <v>676</v>
       </c>
-      <c r="O68" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P68" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q68" s="0" t="s">
+      <c r="R68" s="2">
+        <v>45871</v>
+      </c>
+      <c r="S68" s="2">
+        <v>45873</v>
+      </c>
+      <c r="T68" s="0" t="s">
         <v>677</v>
       </c>
-      <c r="R68" s="2">
-        <v>45856</v>
-      </c>
-      <c r="S68" s="2">
-        <v>45863</v>
-      </c>
-      <c r="T68" s="0" t="s">
+      <c r="U68" s="0" t="s">
         <v>678</v>
       </c>
-      <c r="U68" s="0" t="s">
+      <c r="V68" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="V68" s="0" t="s">
+      <c r="W68" s="0" t="s">
         <v>680</v>
       </c>
-      <c r="W68" s="0" t="s">
-        <v>681</v>
-      </c>
       <c r="X68" s="0">
         <v>5</v>
       </c>
@@ -8389,30 +8470,30 @@
         <v>5</v>
       </c>
       <c r="AP68" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="2">
-        <v>45856</v>
+        <v>45871</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E69" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="F69" s="0" t="s">
         <v>683</v>
       </c>
-      <c r="F69" s="0" t="s">
-        <v>655</v>
-      </c>
       <c r="G69" s="2">
-        <v>45856.6443881597</v>
+        <v>45871.6773271875</v>
       </c>
       <c r="H69" s="0">
         <v>5</v>
@@ -8423,42 +8504,39 @@
       <c r="J69" s="0">
         <v>5</v>
       </c>
-      <c r="L69" s="3" t="s">
+      <c r="L69" s="0" t="s">
         <v>684</v>
       </c>
-      <c r="M69" s="0" t="s">
+      <c r="N69" s="0" t="s">
         <v>685</v>
       </c>
-      <c r="N69" s="0" t="s">
+      <c r="O69" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P69" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q69" s="0" t="s">
         <v>686</v>
       </c>
-      <c r="O69" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P69" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q69" s="0" t="s">
+      <c r="R69" s="2">
+        <v>45867</v>
+      </c>
+      <c r="S69" s="2">
+        <v>45871</v>
+      </c>
+      <c r="T69" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="R69" s="2">
-        <v>45852</v>
-      </c>
-      <c r="S69" s="2">
-        <v>45856</v>
-      </c>
-      <c r="T69" s="0" t="s">
+      <c r="U69" s="0" t="s">
         <v>688</v>
       </c>
-      <c r="U69" s="0" t="s">
+      <c r="V69" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="V69" s="0" t="s">
+      <c r="W69" s="0" t="s">
         <v>690</v>
       </c>
-      <c r="W69" s="0" t="s">
-        <v>691</v>
-      </c>
       <c r="X69" s="0">
         <v>5</v>
       </c>
@@ -8478,60 +8556,63 @@
         <v>5</v>
       </c>
       <c r="AP69" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C70" s="2">
-        <v>45852</v>
+        <v>45866</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E70" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45866.5828246181</v>
+      </c>
+      <c r="H70" s="0">
+        <v>5</v>
+      </c>
+      <c r="I70" s="0">
+        <v>5</v>
+      </c>
+      <c r="J70" s="0">
+        <v>5</v>
+      </c>
+      <c r="L70" s="0" t="s">
         <v>693</v>
       </c>
-      <c r="F70" s="0" t="s">
-        <v>655</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45852.7965359028</v>
-      </c>
-      <c r="H70" s="0">
-        <v>5</v>
-      </c>
-      <c r="I70" s="0">
-        <v>5</v>
-      </c>
-      <c r="J70" s="0">
-        <v>5</v>
-      </c>
-      <c r="L70" s="0" t="s">
+      <c r="M70" s="0" t="s">
         <v>694</v>
       </c>
       <c r="N70" s="0" t="s">
         <v>695</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P70" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q70" s="0" t="s">
         <v>696</v>
       </c>
       <c r="R70" s="2">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="S70" s="2">
-        <v>45852</v>
+        <v>45865</v>
       </c>
       <c r="T70" s="0" t="s">
         <v>697</v>
@@ -8564,7 +8645,7 @@
         <v>5</v>
       </c>
       <c r="AP70" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71">
@@ -8575,7 +8656,7 @@
         <v>43</v>
       </c>
       <c r="C71" s="2">
-        <v>45849</v>
+        <v>45865</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>44</v>
@@ -8584,10 +8665,10 @@
         <v>702</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="G71" s="2">
-        <v>45849.5684718982</v>
+        <v>45865.9243556134</v>
       </c>
       <c r="H71" s="0">
         <v>5</v>
@@ -8605,19 +8686,19 @@
         <v>704</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P71" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q71" s="0" t="s">
         <v>705</v>
       </c>
       <c r="R71" s="2">
-        <v>45844</v>
+        <v>45856</v>
       </c>
       <c r="S71" s="2">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="T71" s="0" t="s">
         <v>706</v>
@@ -8650,7 +8731,7 @@
         <v>5</v>
       </c>
       <c r="AP71" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72">
@@ -8661,7 +8742,7 @@
         <v>43</v>
       </c>
       <c r="C72" s="2">
-        <v>45848</v>
+        <v>45856</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>44</v>
@@ -8670,10 +8751,10 @@
         <v>711</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="G72" s="2">
-        <v>45848.4790960417</v>
+        <v>45856.6443881597</v>
       </c>
       <c r="H72" s="0">
         <v>5</v>
@@ -8684,7 +8765,7 @@
       <c r="J72" s="0">
         <v>5</v>
       </c>
-      <c r="L72" s="0" t="s">
+      <c r="L72" s="3" t="s">
         <v>712</v>
       </c>
       <c r="M72" s="0" t="s">
@@ -8694,19 +8775,19 @@
         <v>714</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q72" s="0" t="s">
         <v>715</v>
       </c>
       <c r="R72" s="2">
-        <v>45843</v>
+        <v>45852</v>
       </c>
       <c r="S72" s="2">
-        <v>45844</v>
+        <v>45856</v>
       </c>
       <c r="T72" s="0" t="s">
         <v>716</v>
@@ -8739,7 +8820,7 @@
         <v>5</v>
       </c>
       <c r="AP72" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
@@ -8750,7 +8831,7 @@
         <v>43</v>
       </c>
       <c r="C73" s="2">
-        <v>45845</v>
+        <v>45852</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>44</v>
@@ -8759,53 +8840,53 @@
         <v>721</v>
       </c>
       <c r="F73" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45852.7965359028</v>
+      </c>
+      <c r="H73" s="0">
+        <v>5</v>
+      </c>
+      <c r="I73" s="0">
+        <v>5</v>
+      </c>
+      <c r="J73" s="0">
+        <v>5</v>
+      </c>
+      <c r="L73" s="0" t="s">
         <v>722</v>
       </c>
-      <c r="G73" s="2">
-        <v>45845.9336395949</v>
-      </c>
-      <c r="H73" s="0">
-        <v>5</v>
-      </c>
-      <c r="I73" s="0">
-        <v>5</v>
-      </c>
-      <c r="J73" s="0">
-        <v>5</v>
-      </c>
-      <c r="L73" s="0" t="s">
+      <c r="N73" s="0" t="s">
         <v>723</v>
       </c>
-      <c r="N73" s="0" t="s">
+      <c r="O73" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P73" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q73" s="0" t="s">
         <v>724</v>
       </c>
-      <c r="O73" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P73" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q73" s="0" t="s">
+      <c r="R73" s="2">
+        <v>45849</v>
+      </c>
+      <c r="S73" s="2">
+        <v>45852</v>
+      </c>
+      <c r="T73" s="0" t="s">
         <v>725</v>
       </c>
-      <c r="R73" s="2">
-        <v>45838</v>
-      </c>
-      <c r="S73" s="2">
-        <v>45839</v>
-      </c>
-      <c r="T73" s="0" t="s">
+      <c r="U73" s="0" t="s">
         <v>726</v>
       </c>
-      <c r="U73" s="0" t="s">
+      <c r="V73" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="V73" s="0" t="s">
+      <c r="W73" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="W73" s="0" t="s">
-        <v>729</v>
-      </c>
       <c r="X73" s="0">
         <v>5</v>
       </c>
@@ -8822,76 +8903,76 @@
         <v>5</v>
       </c>
       <c r="AD73" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP73" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="2">
-        <v>45840</v>
+        <v>45849</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E74" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45849.5684718982</v>
+      </c>
+      <c r="H74" s="0">
+        <v>5</v>
+      </c>
+      <c r="I74" s="0">
+        <v>5</v>
+      </c>
+      <c r="J74" s="0">
+        <v>5</v>
+      </c>
+      <c r="L74" s="0" t="s">
         <v>731</v>
       </c>
-      <c r="F74" s="0" t="s">
-        <v>722</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45840.9692126389</v>
-      </c>
-      <c r="H74" s="0">
-        <v>5</v>
-      </c>
-      <c r="I74" s="0">
-        <v>5</v>
-      </c>
-      <c r="J74" s="0">
-        <v>5</v>
-      </c>
-      <c r="L74" s="0" t="s">
+      <c r="N74" s="0" t="s">
         <v>732</v>
       </c>
-      <c r="N74" s="0" t="s">
+      <c r="O74" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P74" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q74" s="0" t="s">
         <v>733</v>
       </c>
-      <c r="O74" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P74" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q74" s="0" t="s">
+      <c r="R74" s="2">
+        <v>45844</v>
+      </c>
+      <c r="S74" s="2">
+        <v>45849</v>
+      </c>
+      <c r="T74" s="0" t="s">
         <v>734</v>
       </c>
-      <c r="R74" s="2">
-        <v>45836</v>
-      </c>
-      <c r="S74" s="2">
-        <v>45838</v>
-      </c>
-      <c r="T74" s="0" t="s">
+      <c r="U74" s="0" t="s">
         <v>735</v>
       </c>
-      <c r="U74" s="0" t="s">
+      <c r="V74" s="0" t="s">
         <v>736</v>
       </c>
-      <c r="V74" s="0" t="s">
+      <c r="W74" s="0" t="s">
         <v>737</v>
       </c>
-      <c r="W74" s="0" t="s">
-        <v>738</v>
-      </c>
       <c r="X74" s="0">
         <v>5</v>
       </c>
@@ -8911,60 +8992,63 @@
         <v>5</v>
       </c>
       <c r="AP74" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C75" s="2">
-        <v>45834</v>
+        <v>45848</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E75" s="0" t="s">
+        <v>739</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45848.4790960417</v>
+      </c>
+      <c r="H75" s="0">
+        <v>5</v>
+      </c>
+      <c r="I75" s="0">
+        <v>5</v>
+      </c>
+      <c r="J75" s="0">
+        <v>5</v>
+      </c>
+      <c r="L75" s="0" t="s">
         <v>740</v>
       </c>
-      <c r="F75" s="0" t="s">
-        <v>722</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45834.7373021991</v>
-      </c>
-      <c r="H75" s="0">
-        <v>5</v>
-      </c>
-      <c r="I75" s="0">
-        <v>5</v>
-      </c>
-      <c r="J75" s="0">
-        <v>5</v>
-      </c>
-      <c r="L75" s="0" t="s">
+      <c r="M75" s="0" t="s">
         <v>741</v>
       </c>
       <c r="N75" s="0" t="s">
         <v>742</v>
       </c>
       <c r="O75" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P75" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q75" s="0" t="s">
         <v>743</v>
       </c>
       <c r="R75" s="2">
-        <v>45833</v>
+        <v>45843</v>
       </c>
       <c r="S75" s="2">
-        <v>45834</v>
+        <v>45844</v>
       </c>
       <c r="T75" s="0" t="s">
         <v>744</v>
@@ -8997,7 +9081,7 @@
         <v>5</v>
       </c>
       <c r="AP75" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76">
@@ -9008,7 +9092,7 @@
         <v>43</v>
       </c>
       <c r="C76" s="2">
-        <v>45831</v>
+        <v>45845</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>44</v>
@@ -9017,77 +9101,335 @@
         <v>749</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>722</v>
+        <v>750</v>
       </c>
       <c r="G76" s="2">
+        <v>45845.9336395949</v>
+      </c>
+      <c r="H76" s="0">
+        <v>5</v>
+      </c>
+      <c r="I76" s="0">
+        <v>5</v>
+      </c>
+      <c r="J76" s="0">
+        <v>5</v>
+      </c>
+      <c r="L76" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="N76" s="0" t="s">
+        <v>752</v>
+      </c>
+      <c r="O76" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P76" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q76" s="0" t="s">
+        <v>753</v>
+      </c>
+      <c r="R76" s="2">
+        <v>45838</v>
+      </c>
+      <c r="S76" s="2">
+        <v>45839</v>
+      </c>
+      <c r="T76" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="U76" s="0" t="s">
+        <v>755</v>
+      </c>
+      <c r="V76" s="0" t="s">
+        <v>756</v>
+      </c>
+      <c r="W76" s="0" t="s">
+        <v>757</v>
+      </c>
+      <c r="X76" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="0">
+        <v>4</v>
+      </c>
+      <c r="AP76" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" s="2">
+        <v>45840</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>759</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45840.9692126389</v>
+      </c>
+      <c r="H77" s="0">
+        <v>5</v>
+      </c>
+      <c r="I77" s="0">
+        <v>5</v>
+      </c>
+      <c r="J77" s="0">
+        <v>5</v>
+      </c>
+      <c r="L77" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="N77" s="0" t="s">
+        <v>761</v>
+      </c>
+      <c r="O77" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P77" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q77" s="0" t="s">
+        <v>762</v>
+      </c>
+      <c r="R77" s="2">
+        <v>45836</v>
+      </c>
+      <c r="S77" s="2">
+        <v>45838</v>
+      </c>
+      <c r="T77" s="0" t="s">
+        <v>763</v>
+      </c>
+      <c r="U77" s="0" t="s">
+        <v>764</v>
+      </c>
+      <c r="V77" s="0" t="s">
+        <v>765</v>
+      </c>
+      <c r="W77" s="0" t="s">
+        <v>766</v>
+      </c>
+      <c r="X77" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y77" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA77" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB77" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC77" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD77" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP77" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>767</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C78" s="2">
+        <v>45834</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>768</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45834.7373021991</v>
+      </c>
+      <c r="H78" s="0">
+        <v>5</v>
+      </c>
+      <c r="I78" s="0">
+        <v>5</v>
+      </c>
+      <c r="J78" s="0">
+        <v>5</v>
+      </c>
+      <c r="L78" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="N78" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="O78" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="P78" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q78" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="R78" s="2">
+        <v>45833</v>
+      </c>
+      <c r="S78" s="2">
+        <v>45834</v>
+      </c>
+      <c r="T78" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="U78" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="V78" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="W78" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="X78" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y78" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA78" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB78" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC78" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD78" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP78" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79" s="2">
+        <v>45831</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>777</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="G79" s="2">
         <v>45831.0369623843</v>
       </c>
-      <c r="H76" s="0">
-        <v>5</v>
-      </c>
-      <c r="I76" s="0">
-        <v>5</v>
-      </c>
-      <c r="J76" s="0">
-        <v>5</v>
-      </c>
-      <c r="L76" s="0" t="s">
-        <v>750</v>
-      </c>
-      <c r="N76" s="0" t="s">
-        <v>751</v>
-      </c>
-      <c r="O76" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="P76" s="0" t="s">
+      <c r="H79" s="0">
+        <v>5</v>
+      </c>
+      <c r="I79" s="0">
+        <v>5</v>
+      </c>
+      <c r="J79" s="0">
+        <v>5</v>
+      </c>
+      <c r="L79" s="0" t="s">
+        <v>778</v>
+      </c>
+      <c r="N79" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="O79" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="Q76" s="0" t="s">
-        <v>752</v>
-      </c>
-      <c r="R76" s="2">
+      <c r="P79" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q79" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="R79" s="2">
         <v>45828</v>
       </c>
-      <c r="S76" s="2">
+      <c r="S79" s="2">
         <v>45830</v>
       </c>
-      <c r="T76" s="0" t="s">
-        <v>753</v>
-      </c>
-      <c r="U76" s="0" t="s">
-        <v>754</v>
-      </c>
-      <c r="V76" s="0" t="s">
-        <v>755</v>
-      </c>
-      <c r="W76" s="0" t="s">
-        <v>756</v>
-      </c>
-      <c r="X76" s="0">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="0">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="0">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="0">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="0">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="0">
-        <v>5</v>
-      </c>
-      <c r="AP76" s="0" t="s">
-        <v>56</v>
+      <c r="T79" s="0" t="s">
+        <v>781</v>
+      </c>
+      <c r="U79" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="V79" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="W79" s="0" t="s">
+        <v>784</v>
+      </c>
+      <c r="X79" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP79" s="0" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP76"/>
+  <autoFilter ref="A1:AP79"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/public/data/review-export.xlsx
+++ b/public/data/review-export.xlsx
@@ -8,14 +8,14 @@
     <sheet name="review-export" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review-export'!$A$1:$AP$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review-export'!$A$1:$AP$88</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="874">
   <si>
     <t>ReviewId</t>
   </si>
@@ -143,21 +143,333 @@
     <t>Distribution</t>
   </si>
   <si>
+    <t>ORREV116809398</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
+  </si>
+  <si>
+    <t>Dip C</t>
+  </si>
+  <si>
+    <t>May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We had an amazing stay at this beautiful wooden cabin! The cabin was spotless, cozy, and surrounded by gorgeous mountain scenery. Everything felt peaceful and relaxing, especially sitting outside in the fresh air and enjoying the quiet atmosphere.
+The hosts were incredibly responsive and made check in super easy. The cabin had all the amenities we needed and truly felt like a home away from home. Perfect for a relaxing getaway with a classical vibe while still being comfortable and modern.
+We would absolutely stay here again and highly recommend it to anyone visiting the Smoky Mountains!</t>
+  </si>
+  <si>
+    <t>Thank you Dip, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORP458447</t>
+  </si>
+  <si>
+    <t>Bluff Haven Retreat</t>
+  </si>
+  <si>
+    <t>ORB17462323</t>
+  </si>
+  <si>
+    <t>ORG621883621</t>
+  </si>
+  <si>
+    <t>Dip</t>
+  </si>
+  <si>
+    <t>Chakravarty</t>
+  </si>
+  <si>
+    <t>dipto114@gmail.com</t>
+  </si>
+  <si>
+    <t>Ineligible</t>
+  </si>
+  <si>
+    <t>ORREV116781804</t>
+  </si>
+  <si>
+    <t>Kathleen Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beautiful home with great mountain views with wonderful space for hanging out and relaxing. 
+Anusha and Manesh were quick to respond to questions and with information.</t>
+  </si>
+  <si>
+    <t>Thank you, again, for getting us in early and for being so responsive and helpful.</t>
+  </si>
+  <si>
+    <t>Thank you Kathleen, welcome back anytime</t>
+  </si>
+  <si>
+    <t>ORB17303274</t>
+  </si>
+  <si>
+    <t>ORG621712747</t>
+  </si>
+  <si>
+    <t>Kathleen</t>
+  </si>
+  <si>
+    <t>Quinn</t>
+  </si>
+  <si>
+    <t>kfquinn61@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116779942</t>
+  </si>
+  <si>
+    <t>Zach M</t>
+  </si>
+  <si>
+    <t>Beautiful view, great mountain sunsets! The property was clean, spacious, and had a great aerial window view for natural light. We enjoyed this stay, had a great trip and they were great hosts. Thank you!</t>
+  </si>
+  <si>
+    <t>You might want to get an aerial view of the property or a mountain sunset picture on the porch. The view exceeded expectations. Based on the pictures I actually wasn't expecting much of a view. It looked nestled away in the trees from what I thought, so I was pleasantly surprised!</t>
+  </si>
+  <si>
+    <t>Thank you Zach, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17114082</t>
+  </si>
+  <si>
+    <t>ORG621521799</t>
+  </si>
+  <si>
+    <t>Zach</t>
+  </si>
+  <si>
+    <t>M.</t>
+  </si>
+  <si>
+    <t>zmarch95@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116758122</t>
+  </si>
+  <si>
+    <t>Rawan A</t>
+  </si>
+  <si>
+    <t>We had such an amazing stay here! Everything was beautiful, clean, and incredibly smooth from start to finish. One of my favorite touches was the guide link they provided. It had absolutely everything we needed, from the WiFi information to recommendations for restaurants, bars, and even nearby national parks. It made exploring the area so easy and stress-free. You can really tell the hosts put a lot of thought and care into creating a great experience for their guests. I would absolutely stay here again and highly recommend it to anyone visiting the area!</t>
+  </si>
+  <si>
+    <t>Thank you so much for such a wonderful stay. Everything was absolutely beautiful, and the whole experience felt so smooth and thoughtfully put together. We especially LOVED the guide link with all the information. Having the WiFi details, restaurant and bar recommendations, and national park suggestions all in one place made everything so easy and enjoyable. You can really tell how much care you put into hosting. We truly appreciated it and would love to stay again in the future!</t>
+  </si>
+  <si>
+    <t>Thank you Rawan, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17698840</t>
+  </si>
+  <si>
+    <t>ORG622141964</t>
+  </si>
+  <si>
+    <t>Rawan</t>
+  </si>
+  <si>
+    <t>Al-Shishani</t>
+  </si>
+  <si>
+    <t>noxchi6470@icloud.com</t>
+  </si>
+  <si>
+    <t>ORREV116700252</t>
+  </si>
+  <si>
+    <t>Kaenin W</t>
+  </si>
+  <si>
+    <t>5 stars Beautiful cabin in the Smokies with an amazing hot tub with an amazing view. Clean, comfortable, and has everything you need Great location for shopping and food! peaceful and private. Host was super friendly and very helpful. Highly recommend!</t>
+  </si>
+  <si>
+    <t>The place was so nice! Thank you so much for having us!</t>
+  </si>
+  <si>
+    <t>Thank you Kaenin, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB16941019</t>
+  </si>
+  <si>
+    <t>ORG621340787</t>
+  </si>
+  <si>
+    <t>Kaenin</t>
+  </si>
+  <si>
+    <t>Woolery</t>
+  </si>
+  <si>
+    <t>woolery223@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116628638</t>
+  </si>
+  <si>
+    <t>Alyse H</t>
+  </si>
+  <si>
+    <t>Apr 2026</t>
+  </si>
+  <si>
+    <t>What a view! Place was so peaceful and clean. We recommend everyone to book here! The drive to the hot spots was super easy too.</t>
+  </si>
+  <si>
+    <t>We loved this place! It was so hard to leave. It was so cute and clean, we can’t stop showing everyone our views. Thank you again for providing us your place to get away from the real world for a bit</t>
+  </si>
+  <si>
+    <t>Thank you Alyse, Welcome back anytime</t>
+  </si>
+  <si>
+    <t>ORB16249855</t>
+  </si>
+  <si>
+    <t>ORG620565484</t>
+  </si>
+  <si>
+    <t>Alyse</t>
+  </si>
+  <si>
+    <t>Hodgin</t>
+  </si>
+  <si>
+    <t>mark.krygowski@yahoo.com</t>
+  </si>
+  <si>
+    <t>ORREV116474301</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Grace P</t>
+  </si>
+  <si>
+    <t>Mar 2026</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Thank you Grace, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB16745308</t>
+  </si>
+  <si>
+    <t>ORG621120064</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>gschelinski@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116556834</t>
+  </si>
+  <si>
+    <t>Emily B</t>
+  </si>
+  <si>
+    <t>This place was awesome. The view was amazing and everything was so perfect and clean. There were so many amenities like the hot tub, games, and fully loaded kitchen that we enjoyed so much. We would definitely love to stay here again in the future. Thank you so much!</t>
+  </si>
+  <si>
+    <t>We had an amazing stay thank you so much. Did want to let you know that the sliding closet in the downstairs bedroom was missing one of the little knobs on the door so just a screw was poking out. Also we really enjoyed the pac man machine it was awesome! Thank you!</t>
+  </si>
+  <si>
+    <t>Thank you Emily, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17071388</t>
+  </si>
+  <si>
+    <t>ORG621479769</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>Breezley</t>
+  </si>
+  <si>
+    <t>emilybreezley2@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116520623</t>
+  </si>
+  <si>
+    <t>Chelsea S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This was by far the best home we’ve ever stayed in the Pigeon Forge area! It was extremely close to town but felt like you were on your slice of the mountain. The home was absolutely gorgeous, kitchen was very well stocked and all the small details were thought of. The beds were the most comfortable we’ve ever slept in! 
+The hosts were very proactive and responsive, their guide to staying was great. 
+We loved relaxing in the hot tub, the fire pit at night and enjoying the views from the porch. My daughter was delighted to find all the indoor and outdoor games. 
+Overall 10/10 recommend!</t>
+  </si>
+  <si>
+    <t>We really appreciated all the small details and how well the kitchen was stocked! It did not make a difference to us at all but thought you may want to know the left side of the toaster doesn’t work and the right 2 slots lean the toast too close to heat so they always burned even on the lowest setting. Also there are only 4 forks in the utensil drawer so we had to wash them often. But it did not take away from the stay at all, just something I’d want to know as an owner.</t>
+  </si>
+  <si>
+    <t>Thank you Chelsea, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB16857337</t>
+  </si>
+  <si>
+    <t>ORG621238139</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Simoneaux</t>
+  </si>
+  <si>
+    <t>chelseasimoneaux@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116489301</t>
+  </si>
+  <si>
+    <t>Chelsea R</t>
+  </si>
+  <si>
+    <t>We had a wonderful time at the cabin for my son’s first Easter! The cabin was so beautiful and comfortable, we will definitely be back!!</t>
+  </si>
+  <si>
+    <t>Thank you for everything your home is wonderful and we will be back!</t>
+  </si>
+  <si>
+    <t>ORB17179099</t>
+  </si>
+  <si>
+    <t>ORG621599784</t>
+  </si>
+  <si>
+    <t>Reeve</t>
+  </si>
+  <si>
+    <t>chelsea.helmle@gmail.com</t>
+  </si>
+  <si>
     <t>ORREV116477897</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
     <t>Kaila H</t>
   </si>
   <si>
-    <t>Mar 2026</t>
-  </si>
-  <si>
     <t>Perfect stay!</t>
   </si>
   <si>
@@ -167,12 +479,6 @@
     <t>Thank you Kaila, welcome back anytime!!</t>
   </si>
   <si>
-    <t>ORP458447</t>
-  </si>
-  <si>
-    <t>Bluff Haven Retreat</t>
-  </si>
-  <si>
     <t>ORB16870867</t>
   </si>
   <si>
@@ -188,9 +494,6 @@
     <t>haboushkaila@gmail.com</t>
   </si>
   <si>
-    <t>Ineligible</t>
-  </si>
-  <si>
     <t>ORREV116475507</t>
   </si>
   <si>
@@ -216,36 +519,6 @@
   </si>
   <si>
     <t>daniellejs2323@yahoo.com</t>
-  </si>
-  <si>
-    <t>ORREV116474301</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Grace P</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>Thank you Grace, Welcome back anytime!!</t>
-  </si>
-  <si>
-    <t>ORB16745308</t>
-  </si>
-  <si>
-    <t>ORG621120064</t>
-  </si>
-  <si>
-    <t>Grace</t>
-  </si>
-  <si>
-    <t>Parker</t>
-  </si>
-  <si>
-    <t>gschelinski@gmail.com</t>
   </si>
   <si>
     <t>ORREV116444769</t>
@@ -2461,7 +2734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP79"/>
+  <dimension ref="A1:AP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.3060188293457" customWidth="1"/>
@@ -2469,7 +2742,7 @@
     <col min="3" max="3" width="11.8295488357544" customWidth="1"/>
     <col min="4" max="4" width="11.047926902771" customWidth="1"/>
     <col min="5" max="5" width="15.7243585586548" customWidth="1"/>
-    <col min="6" max="6" width="9.9061861038208" customWidth="1"/>
+    <col min="6" max="6" width="10.1312608718872" customWidth="1"/>
     <col min="7" max="7" width="11.8295488357544" customWidth="1"/>
     <col min="8" max="8" width="11.5328598022461" customWidth="1"/>
     <col min="9" max="9" width="10.3051815032959" customWidth="1"/>
@@ -2644,7 +2917,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="2">
-        <v>46117</v>
+        <v>46165</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>44</v>
@@ -2656,7 +2929,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="2">
-        <v>46117.4916690046</v>
+        <v>46165.7115106482</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -2667,85 +2940,82 @@
       <c r="J2" s="0">
         <v>5</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="N2" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="O2" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="P2" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="Q2" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="R2" s="2">
+        <v>46164</v>
+      </c>
+      <c r="S2" s="2">
+        <v>46165</v>
+      </c>
+      <c r="T2" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="R2" s="2">
-        <v>46110</v>
-      </c>
-      <c r="S2" s="2">
-        <v>46112</v>
-      </c>
-      <c r="T2" s="0" t="s">
+      <c r="U2" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="V2" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="V2" s="0" t="s">
+      <c r="W2" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="X2" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP2" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="X2" s="0">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="0">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="0">
-        <v>5</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>5</v>
-      </c>
-      <c r="AC2" s="0">
-        <v>5</v>
-      </c>
-      <c r="AD2" s="0">
-        <v>5</v>
-      </c>
-      <c r="AP2" s="0" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="2">
-        <v>46116</v>
+        <v>46160</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="2">
-        <v>46116.7064720255</v>
+        <v>46160.7253088657</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -2756,26 +3026,29 @@
       <c r="J3" s="0">
         <v>5</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="0" t="s">
         <v>60</v>
       </c>
       <c r="N3" s="0" t="s">
         <v>61</v>
       </c>
       <c r="O3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="P3" s="0" t="s">
-        <v>51</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>62</v>
       </c>
       <c r="R3" s="2">
-        <v>46102</v>
+        <v>46157</v>
       </c>
       <c r="S3" s="2">
-        <v>46105</v>
+        <v>46160</v>
       </c>
       <c r="T3" s="0" t="s">
         <v>63</v>
@@ -2808,7 +3081,7 @@
         <v>5</v>
       </c>
       <c r="AP3" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -2816,52 +3089,55 @@
         <v>67</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2">
-        <v>46116</v>
+        <v>46160</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G4" s="2">
-        <v>46116.6444062153</v>
+        <v>46160.6410878935</v>
       </c>
       <c r="H4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="0">
         <v>5</v>
       </c>
       <c r="J4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" s="0" t="s">
         <v>70</v>
       </c>
       <c r="N4" s="0" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="P4" s="0" t="s">
-        <v>51</v>
       </c>
       <c r="Q4" s="0" t="s">
         <v>72</v>
       </c>
       <c r="R4" s="2">
-        <v>46112</v>
+        <v>46149</v>
       </c>
       <c r="S4" s="2">
-        <v>46116</v>
+        <v>46153</v>
       </c>
       <c r="T4" s="0" t="s">
         <v>73</v>
@@ -2882,19 +3158,19 @@
         <v>5</v>
       </c>
       <c r="AA4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB4" s="0">
         <v>5</v>
       </c>
       <c r="AC4" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD4" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP4" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -2905,7 +3181,7 @@
         <v>43</v>
       </c>
       <c r="C5" s="2">
-        <v>46111</v>
+        <v>46157</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>44</v>
@@ -2917,7 +3193,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2">
-        <v>46111.839397338</v>
+        <v>46157.6984679514</v>
       </c>
       <c r="H5" s="0">
         <v>5</v>
@@ -2931,35 +3207,38 @@
       <c r="L5" s="0" t="s">
         <v>79</v>
       </c>
+      <c r="M5" s="0" t="s">
+        <v>80</v>
+      </c>
       <c r="N5" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O5" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q5" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R5" s="2">
-        <v>46105</v>
+        <v>46155</v>
       </c>
       <c r="S5" s="2">
-        <v>46108</v>
+        <v>46157</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V5" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W5" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X5" s="0">
         <v>5</v>
@@ -2980,30 +3259,30 @@
         <v>5</v>
       </c>
       <c r="AP5" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="2">
-        <v>46102</v>
+        <v>46147</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>46</v>
       </c>
       <c r="G6" s="2">
-        <v>46102.6623598032</v>
+        <v>46147.8677982639</v>
       </c>
       <c r="H6" s="0">
         <v>5</v>
@@ -3015,40 +3294,40 @@
         <v>5</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O6" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P6" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q6" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R6" s="2">
-        <v>46100</v>
+        <v>46143</v>
       </c>
       <c r="S6" s="2">
-        <v>46102</v>
+        <v>46147</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V6" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W6" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X6" s="0">
         <v>5</v>
@@ -3069,30 +3348,30 @@
         <v>5</v>
       </c>
       <c r="AP6" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="2">
-        <v>46100</v>
+        <v>46139</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="G7" s="2">
-        <v>46100.7350191667</v>
+        <v>46139.8147854977</v>
       </c>
       <c r="H7" s="0">
         <v>5</v>
@@ -3104,40 +3383,40 @@
         <v>5</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O7" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q7" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R7" s="2">
-        <v>46096</v>
+        <v>46132</v>
       </c>
       <c r="S7" s="2">
-        <v>46100</v>
+        <v>46138</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V7" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W7" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="X7" s="0">
         <v>5</v>
@@ -3155,78 +3434,75 @@
         <v>5</v>
       </c>
       <c r="AD7" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP7" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2">
-        <v>46096</v>
+        <v>46130</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="G8" s="2">
-        <v>46096.7874516898</v>
+        <v>46130.5865972222</v>
       </c>
       <c r="H8" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="0">
         <v>5</v>
       </c>
       <c r="J8" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="M8" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N8" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O8" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P8" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q8" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R8" s="2">
-        <v>46093</v>
+        <v>46112</v>
       </c>
       <c r="S8" s="2">
-        <v>46096</v>
+        <v>46116</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="V8" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="W8" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="X8" s="0">
         <v>5</v>
@@ -3235,42 +3511,42 @@
         <v>5</v>
       </c>
       <c r="AA8" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="0">
         <v>5</v>
       </c>
       <c r="AC8" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD8" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP8" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="2">
-        <v>46093</v>
+        <v>46128</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="G9" s="2">
-        <v>46093.5347989931</v>
+        <v>46128.760563831</v>
       </c>
       <c r="H9" s="0">
         <v>5</v>
@@ -3282,40 +3558,40 @@
         <v>5</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O9" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P9" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q9" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="R9" s="2">
-        <v>46089</v>
+        <v>46123</v>
       </c>
       <c r="S9" s="2">
-        <v>46092</v>
+        <v>46128</v>
       </c>
       <c r="T9" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="V9" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="W9" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="X9" s="0">
         <v>5</v>
@@ -3336,30 +3612,30 @@
         <v>5</v>
       </c>
       <c r="AP9" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="2">
-        <v>46089</v>
+        <v>46123</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="G10" s="2">
-        <v>46089.7169537731</v>
+        <v>46123.901372037</v>
       </c>
       <c r="H10" s="0">
         <v>5</v>
@@ -3370,41 +3646,41 @@
       <c r="J10" s="0">
         <v>5</v>
       </c>
-      <c r="L10" s="0" t="s">
-        <v>128</v>
+      <c r="L10" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P10" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P10" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q10" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="R10" s="2">
-        <v>46085</v>
+        <v>46120</v>
       </c>
       <c r="S10" s="2">
-        <v>46089</v>
+        <v>46123</v>
       </c>
       <c r="T10" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="U10" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="V10" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="W10" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="X10" s="0">
         <v>5</v>
@@ -3425,30 +3701,30 @@
         <v>5</v>
       </c>
       <c r="AP10" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="2">
-        <v>46085</v>
+        <v>46118</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="G11" s="2">
-        <v>46085.7193587963</v>
+        <v>46118.6686156481</v>
       </c>
       <c r="H11" s="0">
         <v>5</v>
@@ -3460,40 +3736,40 @@
         <v>5</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P11" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P11" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q11" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R11" s="2">
-        <v>46082</v>
+        <v>46116</v>
       </c>
       <c r="S11" s="2">
-        <v>46085</v>
+        <v>46118</v>
       </c>
       <c r="T11" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="U11" s="0" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="V11" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W11" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="X11" s="0">
         <v>5</v>
@@ -3514,30 +3790,30 @@
         <v>5</v>
       </c>
       <c r="AP11" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="G12" s="2">
-        <v>46078.6396170949</v>
+        <v>46117.4916690046</v>
       </c>
       <c r="H12" s="0">
         <v>5</v>
@@ -3558,19 +3834,19 @@
         <v>151</v>
       </c>
       <c r="O12" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P12" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="P12" s="0" t="s">
-        <v>51</v>
       </c>
       <c r="Q12" s="0" t="s">
         <v>152</v>
       </c>
       <c r="R12" s="2">
-        <v>46075</v>
+        <v>46110</v>
       </c>
       <c r="S12" s="2">
-        <v>46078</v>
+        <v>46112</v>
       </c>
       <c r="T12" s="0" t="s">
         <v>153</v>
@@ -3603,7 +3879,7 @@
         <v>5</v>
       </c>
       <c r="AP12" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -3614,7 +3890,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="2">
-        <v>46075</v>
+        <v>46116</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>44</v>
@@ -3623,10 +3899,10 @@
         <v>158</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="G13" s="2">
-        <v>46075.7313287847</v>
+        <v>46116.7064720255</v>
       </c>
       <c r="H13" s="0">
         <v>5</v>
@@ -3637,42 +3913,39 @@
       <c r="J13" s="0">
         <v>5</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="L13" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="M13" s="0" t="s">
+      <c r="N13" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="N13" s="0" t="s">
+      <c r="O13" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q13" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="O13" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="P13" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="0" t="s">
+      <c r="R13" s="2">
+        <v>46102</v>
+      </c>
+      <c r="S13" s="2">
+        <v>46105</v>
+      </c>
+      <c r="T13" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="R13" s="2">
-        <v>46073</v>
-      </c>
-      <c r="S13" s="2">
-        <v>46075</v>
-      </c>
-      <c r="T13" s="0" t="s">
+      <c r="U13" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="U13" s="0" t="s">
+      <c r="V13" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="V13" s="0" t="s">
+      <c r="W13" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="W13" s="0" t="s">
-        <v>166</v>
-      </c>
       <c r="X13" s="0">
         <v>5</v>
       </c>
@@ -3692,73 +3965,73 @@
         <v>5</v>
       </c>
       <c r="AP13" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46111.839397338</v>
+      </c>
+      <c r="H14" s="0">
+        <v>5</v>
+      </c>
+      <c r="I14" s="0">
+        <v>5</v>
+      </c>
+      <c r="J14" s="0">
+        <v>5</v>
+      </c>
+      <c r="L14" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46072.546856875</v>
-      </c>
-      <c r="H14" s="0">
-        <v>5</v>
-      </c>
-      <c r="I14" s="0">
-        <v>5</v>
-      </c>
-      <c r="J14" s="0">
-        <v>5</v>
-      </c>
-      <c r="L14" s="0" t="s">
+      <c r="N14" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="N14" s="0" t="s">
+      <c r="O14" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P14" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="O14" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q14" s="0" t="s">
+      <c r="R14" s="2">
+        <v>46105</v>
+      </c>
+      <c r="S14" s="2">
+        <v>46108</v>
+      </c>
+      <c r="T14" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="R14" s="2">
-        <v>46067</v>
-      </c>
-      <c r="S14" s="2">
-        <v>46071</v>
-      </c>
-      <c r="T14" s="0" t="s">
+      <c r="U14" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="U14" s="0" t="s">
+      <c r="V14" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="V14" s="0" t="s">
+      <c r="W14" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="W14" s="0" t="s">
-        <v>175</v>
-      </c>
       <c r="X14" s="0">
         <v>5</v>
       </c>
@@ -3778,72 +4051,75 @@
         <v>5</v>
       </c>
       <c r="AP14" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="2">
-        <v>46071</v>
+        <v>46102</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="2">
+        <v>46102.6623598032</v>
+      </c>
+      <c r="H15" s="0">
+        <v>5</v>
+      </c>
+      <c r="I15" s="0">
+        <v>5</v>
+      </c>
+      <c r="J15" s="0">
+        <v>5</v>
+      </c>
+      <c r="L15" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="F15" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="G15" s="2">
-        <v>46071.6485774074</v>
-      </c>
-      <c r="H15" s="0">
-        <v>5</v>
-      </c>
-      <c r="I15" s="0">
-        <v>5</v>
-      </c>
-      <c r="J15" s="0">
-        <v>5</v>
-      </c>
-      <c r="L15" s="0" t="s">
+      <c r="M15" s="0" t="s">
         <v>178</v>
       </c>
       <c r="N15" s="0" t="s">
         <v>179</v>
       </c>
       <c r="O15" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="P15" s="0" t="s">
-        <v>51</v>
       </c>
       <c r="Q15" s="0" t="s">
         <v>180</v>
       </c>
       <c r="R15" s="2">
-        <v>46065</v>
+        <v>46100</v>
       </c>
       <c r="S15" s="2">
-        <v>46067</v>
+        <v>46102</v>
       </c>
       <c r="T15" s="0" t="s">
         <v>181</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X15" s="0">
         <v>5</v>
@@ -3864,30 +4140,30 @@
         <v>5</v>
       </c>
       <c r="AP15" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2">
-        <v>46062</v>
+        <v>46100</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="G16" s="2">
-        <v>46062.6577711111</v>
+        <v>46100.7350191667</v>
       </c>
       <c r="H16" s="0">
         <v>5</v>
@@ -3899,37 +4175,40 @@
         <v>5</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>188</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O16" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P16" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q16" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R16" s="2">
-        <v>46059</v>
+        <v>46096</v>
       </c>
       <c r="S16" s="2">
-        <v>46062</v>
+        <v>46100</v>
       </c>
       <c r="T16" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="V16" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="W16" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="X16" s="0">
         <v>5</v>
@@ -3950,30 +4229,30 @@
         <v>5</v>
       </c>
       <c r="AP16" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="2">
-        <v>46057</v>
+        <v>46096</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="G17" s="2">
-        <v>46057.6514546875</v>
+        <v>46096.7874516898</v>
       </c>
       <c r="H17" s="0">
         <v>5</v>
@@ -3985,37 +4264,40 @@
         <v>5</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>198</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O17" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P17" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P17" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q17" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R17" s="2">
-        <v>46052</v>
+        <v>46093</v>
       </c>
       <c r="S17" s="2">
-        <v>46057</v>
+        <v>46096</v>
       </c>
       <c r="T17" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U17" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="V17" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="W17" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="X17" s="0">
         <v>5</v>
@@ -4036,30 +4318,30 @@
         <v>5</v>
       </c>
       <c r="AP17" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="2">
-        <v>46046</v>
+        <v>46093</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="G18" s="2">
-        <v>46046.6863551157</v>
+        <v>46093.5347989931</v>
       </c>
       <c r="H18" s="0">
         <v>5</v>
@@ -4071,37 +4353,40 @@
         <v>5</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>208</v>
       </c>
       <c r="N18" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O18" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P18" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P18" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q18" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R18" s="2">
-        <v>46043</v>
+        <v>46089</v>
       </c>
       <c r="S18" s="2">
-        <v>46046</v>
+        <v>46092</v>
       </c>
       <c r="T18" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="W18" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="X18" s="0">
         <v>5</v>
@@ -4122,30 +4407,30 @@
         <v>5</v>
       </c>
       <c r="AP18" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="2">
-        <v>46044</v>
+        <v>46089</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="G19" s="2">
-        <v>46044.5556409607</v>
+        <v>46089.7169537731</v>
       </c>
       <c r="H19" s="0">
         <v>5</v>
@@ -4157,37 +4442,40 @@
         <v>5</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>218</v>
       </c>
       <c r="N19" s="0" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O19" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P19" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P19" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q19" s="0" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="R19" s="2">
-        <v>46038</v>
+        <v>46085</v>
       </c>
       <c r="S19" s="2">
-        <v>46042</v>
+        <v>46089</v>
       </c>
       <c r="T19" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="U19" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="W19" s="0" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="X19" s="0">
         <v>5</v>
@@ -4208,30 +4496,30 @@
         <v>5</v>
       </c>
       <c r="AP19" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="2">
-        <v>46044</v>
+        <v>46085</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="G20" s="2">
-        <v>46044.5534156597</v>
+        <v>46085.7193587963</v>
       </c>
       <c r="H20" s="0">
         <v>5</v>
@@ -4243,37 +4531,40 @@
         <v>5</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>223</v>
+        <v>227</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>228</v>
       </c>
       <c r="N20" s="0" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="O20" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P20" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P20" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q20" s="0" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="R20" s="2">
-        <v>46034</v>
+        <v>46082</v>
       </c>
       <c r="S20" s="2">
-        <v>46037</v>
+        <v>46085</v>
       </c>
       <c r="T20" s="0" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="U20" s="0" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="V20" s="0" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="W20" s="0" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="X20" s="0">
         <v>5</v>
@@ -4294,30 +4585,30 @@
         <v>5</v>
       </c>
       <c r="AP20" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="2">
-        <v>46033</v>
+        <v>46078</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="G21" s="2">
-        <v>46033.7481770718</v>
+        <v>46078.6396170949</v>
       </c>
       <c r="H21" s="0">
         <v>5</v>
@@ -4329,40 +4620,40 @@
         <v>5</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>239</v>
       </c>
       <c r="N21" s="0" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O21" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P21" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P21" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q21" s="0" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R21" s="2">
-        <v>46030</v>
+        <v>46075</v>
       </c>
       <c r="S21" s="2">
-        <v>46033</v>
+        <v>46078</v>
       </c>
       <c r="T21" s="0" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="U21" s="0" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="V21" s="0" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="W21" s="0" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="X21" s="0">
         <v>5</v>
@@ -4383,30 +4674,30 @@
         <v>5</v>
       </c>
       <c r="AP21" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="2">
-        <v>46030</v>
+        <v>46075</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="G22" s="2">
-        <v>46030.801171713</v>
+        <v>46075.7313287847</v>
       </c>
       <c r="H22" s="0">
         <v>5</v>
@@ -4417,41 +4708,41 @@
       <c r="J22" s="0">
         <v>5</v>
       </c>
-      <c r="L22" s="0" t="s">
-        <v>242</v>
+      <c r="L22" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="M22" s="0" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="N22" s="0" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O22" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P22" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P22" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q22" s="0" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="R22" s="2">
-        <v>46027</v>
+        <v>46073</v>
       </c>
       <c r="S22" s="2">
-        <v>46030</v>
+        <v>46075</v>
       </c>
       <c r="T22" s="0" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="U22" s="0" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="V22" s="0" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="W22" s="0" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="X22" s="0">
         <v>5</v>
@@ -4472,30 +4763,30 @@
         <v>5</v>
       </c>
       <c r="AP22" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="2">
-        <v>46026</v>
+        <v>46072</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="G23" s="2">
-        <v>46026.8843540856</v>
+        <v>46072.546856875</v>
       </c>
       <c r="H23" s="0">
         <v>5</v>
@@ -4507,40 +4798,37 @@
         <v>5</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="M23" s="0" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="O23" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P23" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q23" s="0" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="R23" s="2">
-        <v>46025</v>
+        <v>46067</v>
       </c>
       <c r="S23" s="2">
-        <v>46026</v>
+        <v>46071</v>
       </c>
       <c r="T23" s="0" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="V23" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="W23" s="0" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="X23" s="0">
         <v>5</v>
@@ -4561,30 +4849,30 @@
         <v>5</v>
       </c>
       <c r="AP23" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="2">
-        <v>46025</v>
+        <v>46071</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="G24" s="2">
-        <v>46025.9183283912</v>
+        <v>46071.6485774074</v>
       </c>
       <c r="H24" s="0">
         <v>5</v>
@@ -4596,37 +4884,37 @@
         <v>5</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="O24" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P24" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P24" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q24" s="0" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="R24" s="2">
-        <v>46018</v>
+        <v>46065</v>
       </c>
       <c r="S24" s="2">
-        <v>46025</v>
+        <v>46067</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="W24" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="X24" s="0">
         <v>5</v>
@@ -4647,30 +4935,30 @@
         <v>5</v>
       </c>
       <c r="AP24" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="2">
-        <v>46024</v>
+        <v>46062</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="G25" s="2">
-        <v>46024.2781152662</v>
+        <v>46062.6577711111</v>
       </c>
       <c r="H25" s="0">
         <v>5</v>
@@ -4682,37 +4970,37 @@
         <v>5</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O25" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P25" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q25" s="0" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="R25" s="2">
-        <v>46017</v>
+        <v>46059</v>
       </c>
       <c r="S25" s="2">
-        <v>46018</v>
+        <v>46062</v>
       </c>
       <c r="T25" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="W25" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="X25" s="0">
         <v>5</v>
@@ -4733,30 +5021,30 @@
         <v>5</v>
       </c>
       <c r="AP25" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="2">
-        <v>46023</v>
+        <v>46057</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G26" s="2">
-        <v>46023.7304273495</v>
+        <v>46057.6514546875</v>
       </c>
       <c r="H26" s="0">
         <v>5</v>
@@ -4768,37 +5056,37 @@
         <v>5</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="O26" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P26" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P26" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q26" s="0" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="R26" s="2">
-        <v>46010</v>
+        <v>46052</v>
       </c>
       <c r="S26" s="2">
-        <v>46012</v>
+        <v>46057</v>
       </c>
       <c r="T26" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="W26" s="0" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="X26" s="0">
         <v>5</v>
@@ -4816,33 +5104,33 @@
         <v>5</v>
       </c>
       <c r="AD26" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP26" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="2">
-        <v>46018</v>
+        <v>46046</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G27" s="2">
-        <v>46018.4146147801</v>
+        <v>46046.6863551157</v>
       </c>
       <c r="H27" s="0">
         <v>5</v>
@@ -4854,40 +5142,37 @@
         <v>5</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>290</v>
-      </c>
-      <c r="M27" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N27" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="O27" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P27" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P27" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q27" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="R27" s="2">
-        <v>46013</v>
+        <v>46043</v>
       </c>
       <c r="S27" s="2">
-        <v>46017</v>
+        <v>46046</v>
       </c>
       <c r="T27" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="U27" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="V27" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="W27" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="X27" s="0">
         <v>5</v>
@@ -4908,30 +5193,30 @@
         <v>5</v>
       </c>
       <c r="AP27" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="2">
-        <v>46011</v>
+        <v>46044</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G28" s="2">
-        <v>46011.6063615046</v>
+        <v>46044.5556409607</v>
       </c>
       <c r="H28" s="0">
         <v>5</v>
@@ -4943,37 +5228,37 @@
         <v>5</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N28" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="O28" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P28" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P28" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q28" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="R28" s="2">
-        <v>46006</v>
+        <v>46038</v>
       </c>
       <c r="S28" s="2">
-        <v>46010</v>
+        <v>46042</v>
       </c>
       <c r="T28" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="U28" s="0" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="V28" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="W28" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="X28" s="0">
         <v>5</v>
@@ -4994,30 +5279,30 @@
         <v>5</v>
       </c>
       <c r="AP28" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="2">
-        <v>46005</v>
+        <v>46044</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G29" s="2">
-        <v>46005.7644445486</v>
+        <v>46044.5534156597</v>
       </c>
       <c r="H29" s="0">
         <v>5</v>
@@ -5029,37 +5314,37 @@
         <v>5</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="N29" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="O29" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P29" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P29" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q29" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="R29" s="2">
-        <v>46002</v>
+        <v>46034</v>
       </c>
       <c r="S29" s="2">
-        <v>46005</v>
+        <v>46037</v>
       </c>
       <c r="T29" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="U29" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="V29" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="W29" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="X29" s="0">
         <v>5</v>
@@ -5080,78 +5365,78 @@
         <v>5</v>
       </c>
       <c r="AP29" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2">
-        <v>46003</v>
+        <v>46033</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G30" s="2">
-        <v>46003.8492650926</v>
+        <v>46033.7481770718</v>
       </c>
       <c r="H30" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="0">
         <v>5</v>
       </c>
       <c r="J30" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="M30" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="N30" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O30" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P30" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P30" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q30" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="R30" s="2">
-        <v>45996</v>
+        <v>46030</v>
       </c>
       <c r="S30" s="2">
-        <v>45998</v>
+        <v>46033</v>
       </c>
       <c r="T30" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="U30" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="V30" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="W30" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="X30" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y30" s="0">
         <v>5</v>
@@ -5166,33 +5451,33 @@
         <v>5</v>
       </c>
       <c r="AD30" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP30" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G31" s="2">
-        <v>46001.7156633218</v>
+        <v>46030.801171713</v>
       </c>
       <c r="H31" s="0">
         <v>5</v>
@@ -5204,37 +5489,40 @@
         <v>5</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>332</v>
       </c>
       <c r="N31" s="0" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O31" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P31" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P31" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q31" s="0" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="R31" s="2">
-        <v>45998</v>
+        <v>46027</v>
       </c>
       <c r="S31" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="T31" s="0" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="U31" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="V31" s="0" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="W31" s="0" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="X31" s="0">
         <v>5</v>
@@ -5255,30 +5543,30 @@
         <v>5</v>
       </c>
       <c r="AP31" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="2">
-        <v>45999</v>
+        <v>46026</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G32" s="2">
-        <v>45999.39383875</v>
+        <v>46026.8843540856</v>
       </c>
       <c r="H32" s="0">
         <v>5</v>
@@ -5290,37 +5578,40 @@
         <v>5</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>337</v>
+        <v>341</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>342</v>
       </c>
       <c r="N32" s="0" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="O32" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P32" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P32" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q32" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="R32" s="2">
-        <v>45993</v>
+        <v>46025</v>
       </c>
       <c r="S32" s="2">
-        <v>45994</v>
+        <v>46026</v>
       </c>
       <c r="T32" s="0" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="U32" s="0" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="V32" s="0" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="W32" s="0" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="X32" s="0">
         <v>5</v>
@@ -5341,30 +5632,30 @@
         <v>5</v>
       </c>
       <c r="AP32" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="2">
-        <v>45997</v>
+        <v>46025</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="G33" s="2">
-        <v>45997.7247070486</v>
+        <v>46025.9183283912</v>
       </c>
       <c r="H33" s="0">
         <v>5</v>
@@ -5376,40 +5667,37 @@
         <v>5</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="M33" s="0" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="N33" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="O33" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P33" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P33" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q33" s="0" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="R33" s="2">
-        <v>45994</v>
+        <v>46018</v>
       </c>
       <c r="S33" s="2">
-        <v>45996</v>
+        <v>46025</v>
       </c>
       <c r="T33" s="0" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="U33" s="0" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="V33" s="0" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="W33" s="0" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="X33" s="0">
         <v>5</v>
@@ -5430,30 +5718,30 @@
         <v>5</v>
       </c>
       <c r="AP33" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="2">
-        <v>45993</v>
+        <v>46024</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G34" s="2">
-        <v>45993.7333972569</v>
+        <v>46024.2781152662</v>
       </c>
       <c r="H34" s="0">
         <v>5</v>
@@ -5465,37 +5753,37 @@
         <v>5</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="N34" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="O34" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P34" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P34" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q34" s="0" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="R34" s="2">
-        <v>45990</v>
+        <v>46017</v>
       </c>
       <c r="S34" s="2">
-        <v>45993</v>
+        <v>46018</v>
       </c>
       <c r="T34" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U34" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="V34" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="W34" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="X34" s="0">
         <v>5</v>
@@ -5516,30 +5804,30 @@
         <v>5</v>
       </c>
       <c r="AP34" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="2">
-        <v>45990</v>
+        <v>46023</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G35" s="2">
-        <v>45990.6230057292</v>
+        <v>46023.7304273495</v>
       </c>
       <c r="H35" s="0">
         <v>5</v>
@@ -5551,40 +5839,37 @@
         <v>5</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="M35" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N35" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O35" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P35" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P35" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q35" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="R35" s="2">
-        <v>45986</v>
+        <v>46010</v>
       </c>
       <c r="S35" s="2">
-        <v>45990</v>
+        <v>46012</v>
       </c>
       <c r="T35" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="U35" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="V35" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="W35" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="X35" s="0">
         <v>5</v>
@@ -5602,33 +5887,33 @@
         <v>5</v>
       </c>
       <c r="AD35" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP35" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="2">
-        <v>45986</v>
+        <v>46018</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G36" s="2">
-        <v>45986.7385835995</v>
+        <v>46018.4146147801</v>
       </c>
       <c r="H36" s="0">
         <v>5</v>
@@ -5639,41 +5924,41 @@
       <c r="J36" s="0">
         <v>5</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>377</v>
+      <c r="L36" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="M36" s="0" t="s">
+        <v>380</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="O36" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P36" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P36" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q36" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R36" s="2">
-        <v>45977</v>
+        <v>46013</v>
       </c>
       <c r="S36" s="2">
-        <v>45983</v>
+        <v>46017</v>
       </c>
       <c r="T36" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="U36" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="V36" s="0" t="s">
-        <v>103</v>
+        <v>385</v>
       </c>
       <c r="W36" s="0" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="X36" s="0">
         <v>5</v>
@@ -5694,78 +5979,75 @@
         <v>5</v>
       </c>
       <c r="AP36" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C37" s="2">
-        <v>45986</v>
+        <v>46011</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G37" s="2">
-        <v>45986.574325081</v>
+        <v>46011.6063615046</v>
       </c>
       <c r="H37" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37" s="0">
         <v>5</v>
       </c>
       <c r="J37" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>385</v>
-      </c>
-      <c r="M37" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N37" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="O37" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P37" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P37" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q37" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R37" s="2">
-        <v>45983</v>
+        <v>46006</v>
       </c>
       <c r="S37" s="2">
-        <v>45986</v>
+        <v>46010</v>
       </c>
       <c r="T37" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="U37" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="V37" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="W37" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="X37" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y37" s="0">
         <v>5</v>
@@ -5774,39 +6056,39 @@
         <v>5</v>
       </c>
       <c r="AB37" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC37" s="0">
         <v>5</v>
       </c>
       <c r="AD37" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP37" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="2">
-        <v>45981</v>
+        <v>46005</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G38" s="2">
-        <v>45981.6819216319</v>
+        <v>46005.7644445486</v>
       </c>
       <c r="H38" s="0">
         <v>5</v>
@@ -5818,40 +6100,37 @@
         <v>5</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>395</v>
-      </c>
-      <c r="M38" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N38" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O38" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P38" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P38" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q38" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="R38" s="2">
-        <v>45970</v>
+        <v>46002</v>
       </c>
       <c r="S38" s="2">
-        <v>45977</v>
+        <v>46005</v>
       </c>
       <c r="T38" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="U38" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="V38" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="W38" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="X38" s="0">
         <v>5</v>
@@ -5872,75 +6151,78 @@
         <v>5</v>
       </c>
       <c r="AP38" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C39" s="2">
-        <v>45970</v>
+        <v>46003</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G39" s="2">
-        <v>45970.7607620602</v>
+        <v>46003.8492650926</v>
       </c>
       <c r="H39" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39" s="0">
         <v>5</v>
       </c>
       <c r="J39" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
+      </c>
+      <c r="M39" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="N39" s="0" t="s">
+        <v>409</v>
       </c>
       <c r="O39" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P39" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P39" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q39" s="0" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="R39" s="2">
-        <v>45969</v>
+        <v>45996</v>
       </c>
       <c r="S39" s="2">
-        <v>45970</v>
+        <v>45998</v>
       </c>
       <c r="T39" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="U39" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="V39" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="W39" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="X39" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y39" s="0">
         <v>5</v>
@@ -5955,33 +6237,33 @@
         <v>5</v>
       </c>
       <c r="AD39" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP39" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="2">
-        <v>45970</v>
+        <v>46001</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G40" s="2">
-        <v>45970.4829323264</v>
+        <v>46001.7156633218</v>
       </c>
       <c r="H40" s="0">
         <v>5</v>
@@ -5993,40 +6275,37 @@
         <v>5</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="M40" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
+      </c>
+      <c r="N40" s="0" t="s">
+        <v>418</v>
       </c>
       <c r="O40" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P40" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P40" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q40" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="R40" s="2">
-        <v>45967</v>
+        <v>45998</v>
       </c>
       <c r="S40" s="2">
-        <v>45969</v>
+        <v>46001</v>
       </c>
       <c r="T40" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="U40" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="V40" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W40" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="X40" s="0">
         <v>5</v>
@@ -6047,30 +6326,30 @@
         <v>5</v>
       </c>
       <c r="AP40" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="2">
-        <v>45965</v>
+        <v>45999</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G41" s="2">
-        <v>45965.8421596644</v>
+        <v>45999.39383875</v>
       </c>
       <c r="H41" s="0">
         <v>5</v>
@@ -6082,37 +6361,37 @@
         <v>5</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O41" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P41" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P41" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q41" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="R41" s="2">
-        <v>45962</v>
+        <v>45993</v>
       </c>
       <c r="S41" s="2">
-        <v>45965</v>
+        <v>45994</v>
       </c>
       <c r="T41" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="U41" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="V41" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="W41" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="X41" s="0">
         <v>5</v>
@@ -6133,30 +6412,30 @@
         <v>5</v>
       </c>
       <c r="AP41" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="2">
-        <v>45962</v>
+        <v>45997</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>433</v>
+        <v>351</v>
       </c>
       <c r="G42" s="2">
-        <v>45962.6437613773</v>
+        <v>45997.7247070486</v>
       </c>
       <c r="H42" s="0">
         <v>5</v>
@@ -6168,40 +6447,40 @@
         <v>5</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="N42" s="3" t="s">
         <v>436</v>
       </c>
+      <c r="N42" s="0" t="s">
+        <v>437</v>
+      </c>
       <c r="O42" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P42" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P42" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q42" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="R42" s="2">
-        <v>45959</v>
+        <v>45994</v>
       </c>
       <c r="S42" s="2">
-        <v>45962</v>
+        <v>45996</v>
       </c>
       <c r="T42" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="U42" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="V42" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="W42" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X42" s="0">
         <v>5</v>
@@ -6222,30 +6501,30 @@
         <v>5</v>
       </c>
       <c r="AP42" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="2">
-        <v>45959</v>
+        <v>45993</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G43" s="2">
-        <v>45959.6416564352</v>
+        <v>45993.7333972569</v>
       </c>
       <c r="H43" s="0">
         <v>5</v>
@@ -6257,40 +6536,37 @@
         <v>5</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>444</v>
-      </c>
-      <c r="M43" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N43" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O43" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P43" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P43" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q43" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="R43" s="2">
-        <v>45955</v>
+        <v>45990</v>
       </c>
       <c r="S43" s="2">
-        <v>45959</v>
+        <v>45993</v>
       </c>
       <c r="T43" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="U43" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="V43" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="W43" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="X43" s="0">
         <v>5</v>
@@ -6299,7 +6575,7 @@
         <v>5</v>
       </c>
       <c r="AA43" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB43" s="0">
         <v>5</v>
@@ -6308,78 +6584,81 @@
         <v>5</v>
       </c>
       <c r="AD43" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP43" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C44" s="2">
-        <v>45955</v>
+        <v>45990</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G44" s="2">
-        <v>45955.8044966319</v>
+        <v>45990.6230057292</v>
       </c>
       <c r="H44" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="0">
         <v>5</v>
       </c>
       <c r="J44" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
+      </c>
+      <c r="M44" s="0" t="s">
+        <v>456</v>
       </c>
       <c r="N44" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O44" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P44" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P44" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q44" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="R44" s="2">
-        <v>45954</v>
+        <v>45986</v>
       </c>
       <c r="S44" s="2">
-        <v>45955</v>
+        <v>45990</v>
       </c>
       <c r="T44" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="U44" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="V44" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="W44" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="X44" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y44" s="0">
         <v>5</v>
@@ -6391,36 +6670,36 @@
         <v>5</v>
       </c>
       <c r="AC44" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD44" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP44" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="2">
-        <v>45954</v>
+        <v>45986</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G45" s="2">
-        <v>45954.9526523148</v>
+        <v>45986.7385835995</v>
       </c>
       <c r="H45" s="0">
         <v>5</v>
@@ -6431,38 +6710,41 @@
       <c r="J45" s="0">
         <v>5</v>
       </c>
-      <c r="L45" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>464</v>
+      <c r="L45" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="N45" s="0" t="s">
+        <v>467</v>
       </c>
       <c r="O45" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P45" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P45" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q45" s="0" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="R45" s="2">
-        <v>45949</v>
+        <v>45977</v>
       </c>
       <c r="S45" s="2">
-        <v>45954</v>
+        <v>45983</v>
       </c>
       <c r="T45" s="0" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="U45" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="V45" s="0" t="s">
-        <v>468</v>
+        <v>192</v>
       </c>
       <c r="W45" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="X45" s="0">
         <v>5</v>
@@ -6483,75 +6765,78 @@
         <v>5</v>
       </c>
       <c r="AP45" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C46" s="2">
-        <v>45949</v>
+        <v>45986</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G46" s="2">
-        <v>45949.8261354282</v>
+        <v>45986.574325081</v>
       </c>
       <c r="H46" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I46" s="0">
         <v>5</v>
       </c>
       <c r="J46" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
+      </c>
+      <c r="M46" s="0" t="s">
+        <v>475</v>
       </c>
       <c r="N46" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="O46" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P46" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P46" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q46" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="R46" s="2">
-        <v>45946</v>
+        <v>45983</v>
       </c>
       <c r="S46" s="2">
-        <v>45949</v>
+        <v>45986</v>
       </c>
       <c r="T46" s="0" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="U46" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="V46" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="W46" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="X46" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y46" s="0">
         <v>5</v>
@@ -6560,39 +6845,39 @@
         <v>5</v>
       </c>
       <c r="AB46" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC46" s="0">
         <v>5</v>
       </c>
       <c r="AD46" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP46" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="2">
-        <v>45946</v>
+        <v>45981</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G47" s="2">
-        <v>45946.8340835069</v>
+        <v>45981.6819216319</v>
       </c>
       <c r="H47" s="0">
         <v>5</v>
@@ -6604,40 +6889,40 @@
         <v>5</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M47" s="0" t="s">
-        <v>482</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
+      </c>
+      <c r="N47" s="0" t="s">
+        <v>486</v>
       </c>
       <c r="O47" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P47" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P47" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q47" s="0" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="R47" s="2">
-        <v>45941</v>
+        <v>45970</v>
       </c>
       <c r="S47" s="2">
-        <v>45946</v>
+        <v>45977</v>
       </c>
       <c r="T47" s="0" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="U47" s="0" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="V47" s="0" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="W47" s="0" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="X47" s="0">
         <v>5</v>
@@ -6658,30 +6943,30 @@
         <v>5</v>
       </c>
       <c r="AP47" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="2">
-        <v>45938</v>
+        <v>45970</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G48" s="2">
-        <v>45938.7601655556</v>
+        <v>45970.7607620602</v>
       </c>
       <c r="H48" s="0">
         <v>5</v>
@@ -6693,37 +6978,37 @@
         <v>5</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="O48" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P48" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P48" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q48" s="0" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R48" s="2">
-        <v>45932</v>
+        <v>45969</v>
       </c>
       <c r="S48" s="2">
-        <v>45935</v>
+        <v>45970</v>
       </c>
       <c r="T48" s="0" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="U48" s="0" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="V48" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="W48" s="0" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="X48" s="0">
         <v>5</v>
@@ -6744,30 +7029,30 @@
         <v>5</v>
       </c>
       <c r="AP48" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="2">
-        <v>45937</v>
+        <v>45970</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G49" s="2">
-        <v>45937.8034676042</v>
+        <v>45970.4829323264</v>
       </c>
       <c r="H49" s="0">
         <v>5</v>
@@ -6779,37 +7064,40 @@
         <v>5</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="N49" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="O49" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P49" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P49" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q49" s="0" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="R49" s="2">
-        <v>45935</v>
+        <v>45967</v>
       </c>
       <c r="S49" s="2">
-        <v>45937</v>
+        <v>45969</v>
       </c>
       <c r="T49" s="0" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="U49" s="0" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="V49" s="0" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="W49" s="0" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="X49" s="0">
         <v>5</v>
@@ -6827,33 +7115,33 @@
         <v>5</v>
       </c>
       <c r="AD49" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP49" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="2">
-        <v>45928</v>
+        <v>45965</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>509</v>
+        <v>445</v>
       </c>
       <c r="G50" s="2">
-        <v>45928.7262096412</v>
+        <v>45965.8421596644</v>
       </c>
       <c r="H50" s="0">
         <v>5</v>
@@ -6865,40 +7153,37 @@
         <v>5</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="M50" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>514</v>
       </c>
       <c r="O50" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P50" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P50" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q50" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="R50" s="2">
-        <v>45925</v>
+        <v>45962</v>
       </c>
       <c r="S50" s="2">
-        <v>45928</v>
+        <v>45965</v>
       </c>
       <c r="T50" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="U50" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="V50" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="W50" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="X50" s="0">
         <v>5</v>
@@ -6919,30 +7204,30 @@
         <v>5</v>
       </c>
       <c r="AP50" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="2">
-        <v>45924</v>
+        <v>45962</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="G51" s="2">
-        <v>45924.6507670833</v>
+        <v>45962.6437613773</v>
       </c>
       <c r="H51" s="0">
         <v>5</v>
@@ -6954,37 +7239,40 @@
         <v>5</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>520</v>
-      </c>
-      <c r="N51" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="O51" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P51" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P51" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q51" s="0" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="R51" s="2">
-        <v>45921</v>
+        <v>45959</v>
       </c>
       <c r="S51" s="2">
-        <v>45924</v>
+        <v>45962</v>
       </c>
       <c r="T51" s="0" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="U51" s="0" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="V51" s="0" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="W51" s="0" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="X51" s="0">
         <v>5</v>
@@ -7005,30 +7293,30 @@
         <v>5</v>
       </c>
       <c r="AP51" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="2">
-        <v>45923</v>
+        <v>45959</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="G52" s="2">
-        <v>45923.3761746296</v>
+        <v>45959.6416564352</v>
       </c>
       <c r="H52" s="0">
         <v>5</v>
@@ -7040,37 +7328,40 @@
         <v>5</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>529</v>
+        <v>533</v>
+      </c>
+      <c r="M52" s="0" t="s">
+        <v>534</v>
       </c>
       <c r="N52" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="O52" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P52" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P52" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q52" s="0" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="R52" s="2">
-        <v>45918</v>
+        <v>45955</v>
       </c>
       <c r="S52" s="2">
-        <v>45921</v>
+        <v>45959</v>
       </c>
       <c r="T52" s="0" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="U52" s="0" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="V52" s="0" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="W52" s="0" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="X52" s="0">
         <v>5</v>
@@ -7079,7 +7370,7 @@
         <v>5</v>
       </c>
       <c r="AA52" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB52" s="0">
         <v>5</v>
@@ -7088,78 +7379,78 @@
         <v>5</v>
       </c>
       <c r="AD52" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP52" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C53" s="2">
-        <v>45922</v>
+        <v>45955</v>
       </c>
       <c r="D53" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="G53" s="2">
-        <v>45922.4128161921</v>
+        <v>45955.8044966319</v>
       </c>
       <c r="H53" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I53" s="0">
         <v>5</v>
       </c>
       <c r="J53" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="N53" s="0" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="O53" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P53" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P53" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q53" s="0" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="R53" s="2">
-        <v>45914</v>
+        <v>45954</v>
       </c>
       <c r="S53" s="2">
-        <v>45918</v>
+        <v>45955</v>
       </c>
       <c r="T53" s="0" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="U53" s="0" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="V53" s="0" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="W53" s="0" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="X53" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y53" s="0">
         <v>5</v>
@@ -7171,78 +7462,78 @@
         <v>5</v>
       </c>
       <c r="AC53" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD53" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP53" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C54" s="2">
-        <v>45920</v>
+        <v>45954</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="G54" s="2">
-        <v>45920.6962243171</v>
+        <v>45954.9526523148</v>
       </c>
       <c r="H54" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="0">
         <v>5</v>
       </c>
       <c r="J54" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>548</v>
-      </c>
-      <c r="M54" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="O54" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P54" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P54" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q54" s="0" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="R54" s="2">
-        <v>45900</v>
+        <v>45949</v>
       </c>
       <c r="S54" s="2">
-        <v>45906</v>
+        <v>45954</v>
       </c>
       <c r="T54" s="0" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="U54" s="0" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="V54" s="0" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="W54" s="0" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="X54" s="0">
         <v>5</v>
@@ -7257,36 +7548,36 @@
         <v>5</v>
       </c>
       <c r="AC54" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD54" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP54" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="2">
-        <v>45916</v>
+        <v>45949</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="G55" s="2">
-        <v>45916.4699822917</v>
+        <v>45949.8261354282</v>
       </c>
       <c r="H55" s="0">
         <v>5</v>
@@ -7298,43 +7589,43 @@
         <v>5</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N55" s="0" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="O55" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P55" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P55" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q55" s="0" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="R55" s="2">
-        <v>45913</v>
+        <v>45946</v>
       </c>
       <c r="S55" s="2">
-        <v>45914</v>
+        <v>45949</v>
       </c>
       <c r="T55" s="0" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="U55" s="0" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="V55" s="0" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="W55" s="0" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="X55" s="0">
         <v>5</v>
       </c>
       <c r="Y55" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA55" s="0">
         <v>5</v>
@@ -7349,30 +7640,30 @@
         <v>5</v>
       </c>
       <c r="AP55" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="2">
-        <v>45914</v>
+        <v>45946</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="G56" s="2">
-        <v>45914.5820426389</v>
+        <v>45946.8340835069</v>
       </c>
       <c r="H56" s="0">
         <v>5</v>
@@ -7384,37 +7675,40 @@
         <v>5</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>565</v>
-      </c>
-      <c r="N56" s="0" t="s">
-        <v>566</v>
+        <v>570</v>
+      </c>
+      <c r="M56" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>572</v>
       </c>
       <c r="O56" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P56" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P56" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q56" s="0" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="R56" s="2">
-        <v>45907</v>
+        <v>45941</v>
       </c>
       <c r="S56" s="2">
-        <v>45913</v>
+        <v>45946</v>
       </c>
       <c r="T56" s="0" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="U56" s="0" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="V56" s="0" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="W56" s="0" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="X56" s="0">
         <v>5</v>
@@ -7435,30 +7729,30 @@
         <v>5</v>
       </c>
       <c r="AP56" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="2">
-        <v>45909</v>
+        <v>45938</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="G57" s="2">
-        <v>45909.7231987963</v>
+        <v>45938.7601655556</v>
       </c>
       <c r="H57" s="0">
         <v>5</v>
@@ -7470,37 +7764,37 @@
         <v>5</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="O57" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P57" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P57" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q57" s="0" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="R57" s="2">
-        <v>45906</v>
+        <v>45932</v>
       </c>
       <c r="S57" s="2">
-        <v>45907</v>
+        <v>45935</v>
       </c>
       <c r="T57" s="0" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="U57" s="0" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="V57" s="0" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="W57" s="0" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="X57" s="0">
         <v>5</v>
@@ -7521,30 +7815,30 @@
         <v>5</v>
       </c>
       <c r="AP57" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="2">
-        <v>45900</v>
+        <v>45937</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="G58" s="2">
-        <v>45900.6461770602</v>
+        <v>45937.8034676042</v>
       </c>
       <c r="H58" s="0">
         <v>5</v>
@@ -7556,37 +7850,37 @@
         <v>5</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>584</v>
+        <v>589</v>
+      </c>
+      <c r="N58" s="0" t="s">
+        <v>590</v>
       </c>
       <c r="O58" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P58" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P58" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q58" s="0" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="R58" s="2">
-        <v>45897</v>
+        <v>45935</v>
       </c>
       <c r="S58" s="2">
-        <v>45900</v>
+        <v>45937</v>
       </c>
       <c r="T58" s="0" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="U58" s="0" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="V58" s="0" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="W58" s="0" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="X58" s="0">
         <v>5</v>
@@ -7604,33 +7898,33 @@
         <v>5</v>
       </c>
       <c r="AD58" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP58" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="2">
-        <v>45899</v>
+        <v>45928</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>591</v>
+        <v>44</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G59" s="2">
-        <v>45898.9353472222</v>
+        <v>45928.7262096412</v>
       </c>
       <c r="H59" s="0">
         <v>5</v>
@@ -7642,37 +7936,43 @@
         <v>5</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>593</v>
-      </c>
-      <c r="N59" s="0" t="s">
-        <v>594</v>
+        <v>599</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="O59" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P59" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P59" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q59" s="0" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="R59" s="2">
-        <v>45893</v>
+        <v>45925</v>
       </c>
       <c r="S59" s="2">
-        <v>45896</v>
+        <v>45928</v>
       </c>
       <c r="T59" s="0" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="U59" s="0" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="V59" s="0" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="W59" s="0" t="s">
-        <v>599</v>
+        <v>606</v>
+      </c>
+      <c r="X59" s="0">
+        <v>5</v>
       </c>
       <c r="Y59" s="0">
         <v>5</v>
@@ -7686,34 +7986,34 @@
       <c r="AC59" s="0">
         <v>5</v>
       </c>
-      <c r="AE59" s="0">
+      <c r="AD59" s="0">
         <v>5</v>
       </c>
       <c r="AP59" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C60" s="2">
-        <v>45897</v>
+        <v>45924</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G60" s="2">
-        <v>45897.7557321412</v>
+        <v>45924.6507670833</v>
       </c>
       <c r="H60" s="0">
         <v>5</v>
@@ -7725,40 +8025,37 @@
         <v>5</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>602</v>
-      </c>
-      <c r="M60" s="0" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="N60" s="0" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="O60" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P60" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P60" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q60" s="0" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="R60" s="2">
-        <v>45896</v>
+        <v>45921</v>
       </c>
       <c r="S60" s="2">
-        <v>45897</v>
+        <v>45924</v>
       </c>
       <c r="T60" s="0" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="U60" s="0" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="V60" s="0" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="W60" s="0" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="X60" s="0">
         <v>5</v>
@@ -7779,30 +8076,30 @@
         <v>5</v>
       </c>
       <c r="AP60" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="2">
-        <v>45894</v>
+        <v>45923</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G61" s="2">
-        <v>45894.8301493981</v>
+        <v>45923.3761746296</v>
       </c>
       <c r="H61" s="0">
         <v>5</v>
@@ -7814,37 +8111,37 @@
         <v>5</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="N61" s="0" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="O61" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P61" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P61" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q61" s="0" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="R61" s="2">
-        <v>45890</v>
+        <v>45918</v>
       </c>
       <c r="S61" s="2">
-        <v>45893</v>
+        <v>45921</v>
       </c>
       <c r="T61" s="0" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="U61" s="0" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="V61" s="0" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="W61" s="0" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="X61" s="0">
         <v>5</v>
@@ -7865,30 +8162,30 @@
         <v>5</v>
       </c>
       <c r="AP61" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="2">
-        <v>45889</v>
+        <v>45922</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G62" s="2">
-        <v>45889.6599939468</v>
+        <v>45922.4128161921</v>
       </c>
       <c r="H62" s="0">
         <v>5</v>
@@ -7900,40 +8197,37 @@
         <v>5</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>620</v>
-      </c>
-      <c r="M62" s="0" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="N62" s="0" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="O62" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P62" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P62" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q62" s="0" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="R62" s="2">
-        <v>45886</v>
+        <v>45914</v>
       </c>
       <c r="S62" s="2">
-        <v>45889</v>
+        <v>45918</v>
       </c>
       <c r="T62" s="0" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="U62" s="0" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="V62" s="0" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="W62" s="0" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="X62" s="0">
         <v>5</v>
@@ -7954,72 +8248,72 @@
         <v>5</v>
       </c>
       <c r="AP62" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C63" s="2">
-        <v>45888</v>
+        <v>45920</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>547</v>
+        <v>636</v>
       </c>
       <c r="G63" s="2">
-        <v>45888.5413223148</v>
+        <v>45920.6962243171</v>
       </c>
       <c r="H63" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I63" s="0">
         <v>5</v>
       </c>
       <c r="J63" s="0">
-        <v>5</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>631</v>
+        <v>4</v>
+      </c>
+      <c r="L63" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="M63" s="0" t="s">
+        <v>638</v>
       </c>
       <c r="O63" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P63" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P63" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q63" s="0" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="R63" s="2">
-        <v>45883</v>
+        <v>45900</v>
       </c>
       <c r="S63" s="2">
-        <v>45886</v>
+        <v>45906</v>
       </c>
       <c r="T63" s="0" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="U63" s="0" t="s">
-        <v>247</v>
+        <v>641</v>
       </c>
       <c r="V63" s="0" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="W63" s="0" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="X63" s="0">
         <v>5</v>
@@ -8034,36 +8328,36 @@
         <v>5</v>
       </c>
       <c r="AC63" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD63" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP63" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="2">
-        <v>45884</v>
+        <v>45916</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G64" s="2">
-        <v>45884.5080971296</v>
+        <v>45916.4699822917</v>
       </c>
       <c r="H64" s="0">
         <v>5</v>
@@ -8075,43 +8369,43 @@
         <v>5</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="O64" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P64" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P64" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q64" s="0" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="R64" s="2">
-        <v>45880</v>
+        <v>45913</v>
       </c>
       <c r="S64" s="2">
-        <v>45883</v>
+        <v>45914</v>
       </c>
       <c r="T64" s="0" t="s">
+        <v>649</v>
+      </c>
+      <c r="U64" s="0" t="s">
         <v>641</v>
       </c>
-      <c r="U64" s="0" t="s">
-        <v>642</v>
-      </c>
       <c r="V64" s="0" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="W64" s="0" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="X64" s="0">
         <v>5</v>
       </c>
       <c r="Y64" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA64" s="0">
         <v>5</v>
@@ -8126,30 +8420,30 @@
         <v>5</v>
       </c>
       <c r="AP64" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="2">
-        <v>45884</v>
+        <v>45914</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G65" s="2">
-        <v>45884.3282971181</v>
+        <v>45914.5820426389</v>
       </c>
       <c r="H65" s="0">
         <v>5</v>
@@ -8161,37 +8455,37 @@
         <v>5</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="N65" s="0" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="O65" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P65" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P65" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q65" s="0" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="R65" s="2">
-        <v>45876</v>
+        <v>45907</v>
       </c>
       <c r="S65" s="2">
-        <v>45877</v>
+        <v>45913</v>
       </c>
       <c r="T65" s="0" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="U65" s="0" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="V65" s="0" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="W65" s="0" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="X65" s="0">
         <v>5</v>
@@ -8212,30 +8506,30 @@
         <v>5</v>
       </c>
       <c r="AP65" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C66" s="2">
-        <v>45880</v>
+        <v>45909</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="G66" s="2">
-        <v>45880.7327610417</v>
+        <v>45909.7231987963</v>
       </c>
       <c r="H66" s="0">
         <v>5</v>
@@ -8247,37 +8541,37 @@
         <v>5</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>656</v>
-      </c>
-      <c r="N66" s="0" t="s">
-        <v>657</v>
+        <v>663</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="O66" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P66" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P66" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q66" s="0" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="R66" s="2">
-        <v>45877</v>
+        <v>45906</v>
       </c>
       <c r="S66" s="2">
-        <v>45880</v>
+        <v>45907</v>
       </c>
       <c r="T66" s="0" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="U66" s="0" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="V66" s="0" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="W66" s="0" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="X66" s="0">
         <v>5</v>
@@ -8298,30 +8592,30 @@
         <v>5</v>
       </c>
       <c r="AP66" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C67" s="2">
-        <v>45877</v>
+        <v>45900</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>547</v>
+        <v>636</v>
       </c>
       <c r="G67" s="2">
-        <v>45877.4773553819</v>
+        <v>45900.6461770602</v>
       </c>
       <c r="H67" s="0">
         <v>5</v>
@@ -8333,37 +8627,37 @@
         <v>5</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>665</v>
-      </c>
-      <c r="N67" s="0" t="s">
-        <v>666</v>
+        <v>672</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="O67" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P67" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P67" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q67" s="0" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="R67" s="2">
-        <v>45873</v>
+        <v>45897</v>
       </c>
       <c r="S67" s="2">
-        <v>45876</v>
+        <v>45900</v>
       </c>
       <c r="T67" s="0" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="U67" s="0" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="V67" s="0" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="W67" s="0" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="X67" s="0">
         <v>5</v>
@@ -8384,30 +8678,30 @@
         <v>5</v>
       </c>
       <c r="AP67" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="2">
-        <v>45873</v>
+        <v>45899</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>44</v>
+        <v>680</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>547</v>
+        <v>636</v>
       </c>
       <c r="G68" s="2">
-        <v>45873.7425913657</v>
+        <v>45898.9353472222</v>
       </c>
       <c r="H68" s="0">
         <v>5</v>
@@ -8418,41 +8712,38 @@
       <c r="J68" s="0">
         <v>5</v>
       </c>
-      <c r="L68" s="3" t="s">
-        <v>674</v>
+      <c r="L68" s="0" t="s">
+        <v>682</v>
       </c>
       <c r="N68" s="0" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="O68" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P68" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P68" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q68" s="0" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="R68" s="2">
-        <v>45871</v>
+        <v>45893</v>
       </c>
       <c r="S68" s="2">
-        <v>45873</v>
+        <v>45896</v>
       </c>
       <c r="T68" s="0" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="U68" s="0" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="V68" s="0" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="W68" s="0" t="s">
-        <v>680</v>
-      </c>
-      <c r="X68" s="0">
-        <v>5</v>
+        <v>688</v>
       </c>
       <c r="Y68" s="0">
         <v>5</v>
@@ -8466,34 +8757,34 @@
       <c r="AC68" s="0">
         <v>5</v>
       </c>
-      <c r="AD68" s="0">
+      <c r="AE68" s="0">
         <v>5</v>
       </c>
       <c r="AP68" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="2">
-        <v>45871</v>
+        <v>45897</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G69" s="2">
-        <v>45871.6773271875</v>
+        <v>45897.7557321412</v>
       </c>
       <c r="H69" s="0">
         <v>5</v>
@@ -8505,37 +8796,40 @@
         <v>5</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>684</v>
+        <v>691</v>
+      </c>
+      <c r="M69" s="0" t="s">
+        <v>692</v>
       </c>
       <c r="N69" s="0" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O69" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P69" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P69" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q69" s="0" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="R69" s="2">
-        <v>45867</v>
+        <v>45896</v>
       </c>
       <c r="S69" s="2">
-        <v>45871</v>
+        <v>45897</v>
       </c>
       <c r="T69" s="0" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="U69" s="0" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="V69" s="0" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="W69" s="0" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="X69" s="0">
         <v>5</v>
@@ -8556,30 +8850,30 @@
         <v>5</v>
       </c>
       <c r="AP69" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C70" s="2">
-        <v>45866</v>
+        <v>45894</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G70" s="2">
-        <v>45866.5828246181</v>
+        <v>45894.8301493981</v>
       </c>
       <c r="H70" s="0">
         <v>5</v>
@@ -8591,40 +8885,37 @@
         <v>5</v>
       </c>
       <c r="L70" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="N70" s="0" t="s">
         <v>693</v>
       </c>
-      <c r="M70" s="0" t="s">
-        <v>694</v>
-      </c>
-      <c r="N70" s="0" t="s">
-        <v>695</v>
-      </c>
       <c r="O70" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P70" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P70" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q70" s="0" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="R70" s="2">
-        <v>45863</v>
+        <v>45890</v>
       </c>
       <c r="S70" s="2">
-        <v>45865</v>
+        <v>45893</v>
       </c>
       <c r="T70" s="0" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="U70" s="0" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="V70" s="0" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="W70" s="0" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="X70" s="0">
         <v>5</v>
@@ -8645,30 +8936,30 @@
         <v>5</v>
       </c>
       <c r="AP70" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="2">
-        <v>45865</v>
+        <v>45889</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G71" s="2">
-        <v>45865.9243556134</v>
+        <v>45889.6599939468</v>
       </c>
       <c r="H71" s="0">
         <v>5</v>
@@ -8680,37 +8971,40 @@
         <v>5</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>703</v>
+        <v>709</v>
+      </c>
+      <c r="M71" s="0" t="s">
+        <v>710</v>
       </c>
       <c r="N71" s="0" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="O71" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P71" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P71" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q71" s="0" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="R71" s="2">
-        <v>45856</v>
+        <v>45886</v>
       </c>
       <c r="S71" s="2">
-        <v>45863</v>
+        <v>45889</v>
       </c>
       <c r="T71" s="0" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="U71" s="0" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="V71" s="0" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="W71" s="0" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="X71" s="0">
         <v>5</v>
@@ -8731,30 +9025,30 @@
         <v>5</v>
       </c>
       <c r="AP71" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C72" s="2">
-        <v>45856</v>
+        <v>45888</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G72" s="2">
-        <v>45856.6443881597</v>
+        <v>45888.5413223148</v>
       </c>
       <c r="H72" s="0">
         <v>5</v>
@@ -8766,40 +9060,37 @@
         <v>5</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="M72" s="0" t="s">
-        <v>713</v>
-      </c>
-      <c r="N72" s="0" t="s">
-        <v>714</v>
+        <v>719</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>720</v>
       </c>
       <c r="O72" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P72" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P72" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q72" s="0" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="R72" s="2">
-        <v>45852</v>
+        <v>45883</v>
       </c>
       <c r="S72" s="2">
-        <v>45856</v>
+        <v>45886</v>
       </c>
       <c r="T72" s="0" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="U72" s="0" t="s">
-        <v>717</v>
+        <v>336</v>
       </c>
       <c r="V72" s="0" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="W72" s="0" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="X72" s="0">
         <v>5</v>
@@ -8820,30 +9111,30 @@
         <v>5</v>
       </c>
       <c r="AP72" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C73" s="2">
-        <v>45852</v>
+        <v>45884</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G73" s="2">
-        <v>45852.7965359028</v>
+        <v>45884.5080971296</v>
       </c>
       <c r="H73" s="0">
         <v>5</v>
@@ -8855,37 +9146,37 @@
         <v>5</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="N73" s="0" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="O73" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P73" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P73" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q73" s="0" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="R73" s="2">
-        <v>45849</v>
+        <v>45880</v>
       </c>
       <c r="S73" s="2">
-        <v>45852</v>
+        <v>45883</v>
       </c>
       <c r="T73" s="0" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="U73" s="0" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="V73" s="0" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="W73" s="0" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="X73" s="0">
         <v>5</v>
@@ -8906,30 +9197,30 @@
         <v>5</v>
       </c>
       <c r="AP73" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="2">
-        <v>45849</v>
+        <v>45884</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G74" s="2">
-        <v>45849.5684718982</v>
+        <v>45884.3282971181</v>
       </c>
       <c r="H74" s="0">
         <v>5</v>
@@ -8941,37 +9232,37 @@
         <v>5</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="N74" s="0" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="O74" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P74" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P74" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q74" s="0" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="R74" s="2">
-        <v>45844</v>
+        <v>45876</v>
       </c>
       <c r="S74" s="2">
-        <v>45849</v>
+        <v>45877</v>
       </c>
       <c r="T74" s="0" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="U74" s="0" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="V74" s="0" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="W74" s="0" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="X74" s="0">
         <v>5</v>
@@ -8992,30 +9283,30 @@
         <v>5</v>
       </c>
       <c r="AP74" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C75" s="2">
-        <v>45848</v>
+        <v>45880</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="G75" s="2">
-        <v>45848.4790960417</v>
+        <v>45880.7327610417</v>
       </c>
       <c r="H75" s="0">
         <v>5</v>
@@ -9027,40 +9318,37 @@
         <v>5</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>740</v>
-      </c>
-      <c r="M75" s="0" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="N75" s="0" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="O75" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P75" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P75" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q75" s="0" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="R75" s="2">
-        <v>45843</v>
+        <v>45877</v>
       </c>
       <c r="S75" s="2">
-        <v>45844</v>
+        <v>45880</v>
       </c>
       <c r="T75" s="0" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="U75" s="0" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="V75" s="0" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="W75" s="0" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="X75" s="0">
         <v>5</v>
@@ -9081,30 +9369,30 @@
         <v>5</v>
       </c>
       <c r="AP75" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="2">
-        <v>45845</v>
+        <v>45877</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>750</v>
+        <v>636</v>
       </c>
       <c r="G76" s="2">
-        <v>45845.9336395949</v>
+        <v>45877.4773553819</v>
       </c>
       <c r="H76" s="0">
         <v>5</v>
@@ -9116,37 +9404,37 @@
         <v>5</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="N76" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="O76" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P76" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P76" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q76" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="R76" s="2">
-        <v>45838</v>
+        <v>45873</v>
       </c>
       <c r="S76" s="2">
-        <v>45839</v>
+        <v>45876</v>
       </c>
       <c r="T76" s="0" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="U76" s="0" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="V76" s="0" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="W76" s="0" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="X76" s="0">
         <v>5</v>
@@ -9164,33 +9452,33 @@
         <v>5</v>
       </c>
       <c r="AD76" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP76" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C77" s="2">
-        <v>45840</v>
+        <v>45873</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>750</v>
+        <v>636</v>
       </c>
       <c r="G77" s="2">
-        <v>45840.9692126389</v>
+        <v>45873.7425913657</v>
       </c>
       <c r="H77" s="0">
         <v>5</v>
@@ -9201,38 +9489,38 @@
       <c r="J77" s="0">
         <v>5</v>
       </c>
-      <c r="L77" s="0" t="s">
-        <v>760</v>
+      <c r="L77" s="3" t="s">
+        <v>763</v>
       </c>
       <c r="N77" s="0" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="O77" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P77" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P77" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q77" s="0" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="R77" s="2">
-        <v>45836</v>
+        <v>45871</v>
       </c>
       <c r="S77" s="2">
-        <v>45838</v>
+        <v>45873</v>
       </c>
       <c r="T77" s="0" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="U77" s="0" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="V77" s="0" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="W77" s="0" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="X77" s="0">
         <v>5</v>
@@ -9253,30 +9541,30 @@
         <v>5</v>
       </c>
       <c r="AP77" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C78" s="2">
-        <v>45834</v>
+        <v>45871</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="G78" s="2">
-        <v>45834.7373021991</v>
+        <v>45871.6773271875</v>
       </c>
       <c r="H78" s="0">
         <v>5</v>
@@ -9288,37 +9576,37 @@
         <v>5</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="N78" s="0" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="O78" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P78" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P78" s="0" t="s">
-        <v>51</v>
-      </c>
       <c r="Q78" s="0" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="R78" s="2">
-        <v>45833</v>
+        <v>45867</v>
       </c>
       <c r="S78" s="2">
-        <v>45834</v>
+        <v>45871</v>
       </c>
       <c r="T78" s="0" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="U78" s="0" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="V78" s="0" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="W78" s="0" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="X78" s="0">
         <v>5</v>
@@ -9339,97 +9627,880 @@
         <v>5</v>
       </c>
       <c r="AP78" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C79" s="2">
-        <v>45831</v>
+        <v>45866</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="G79" s="2">
+        <v>45866.5828246181</v>
+      </c>
+      <c r="H79" s="0">
+        <v>5</v>
+      </c>
+      <c r="I79" s="0">
+        <v>5</v>
+      </c>
+      <c r="J79" s="0">
+        <v>5</v>
+      </c>
+      <c r="L79" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="M79" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="N79" s="0" t="s">
+        <v>784</v>
+      </c>
+      <c r="O79" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P79" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q79" s="0" t="s">
+        <v>785</v>
+      </c>
+      <c r="R79" s="2">
+        <v>45863</v>
+      </c>
+      <c r="S79" s="2">
+        <v>45865</v>
+      </c>
+      <c r="T79" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="U79" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="V79" s="0" t="s">
+        <v>788</v>
+      </c>
+      <c r="W79" s="0" t="s">
+        <v>789</v>
+      </c>
+      <c r="X79" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD79" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP79" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>790</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" s="2">
+        <v>45865</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>791</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45865.9243556134</v>
+      </c>
+      <c r="H80" s="0">
+        <v>5</v>
+      </c>
+      <c r="I80" s="0">
+        <v>5</v>
+      </c>
+      <c r="J80" s="0">
+        <v>5</v>
+      </c>
+      <c r="L80" s="0" t="s">
+        <v>792</v>
+      </c>
+      <c r="N80" s="0" t="s">
+        <v>793</v>
+      </c>
+      <c r="O80" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P80" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q80" s="0" t="s">
+        <v>794</v>
+      </c>
+      <c r="R80" s="2">
+        <v>45856</v>
+      </c>
+      <c r="S80" s="2">
+        <v>45863</v>
+      </c>
+      <c r="T80" s="0" t="s">
+        <v>795</v>
+      </c>
+      <c r="U80" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="V80" s="0" t="s">
+        <v>797</v>
+      </c>
+      <c r="W80" s="0" t="s">
+        <v>798</v>
+      </c>
+      <c r="X80" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y80" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA80" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB80" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC80" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD80" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP80" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>799</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" s="2">
+        <v>45856</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>800</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45856.6443881597</v>
+      </c>
+      <c r="H81" s="0">
+        <v>5</v>
+      </c>
+      <c r="I81" s="0">
+        <v>5</v>
+      </c>
+      <c r="J81" s="0">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="M81" s="0" t="s">
+        <v>802</v>
+      </c>
+      <c r="N81" s="0" t="s">
+        <v>803</v>
+      </c>
+      <c r="O81" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P81" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q81" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="R81" s="2">
+        <v>45852</v>
+      </c>
+      <c r="S81" s="2">
+        <v>45856</v>
+      </c>
+      <c r="T81" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="U81" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="V81" s="0" t="s">
+        <v>807</v>
+      </c>
+      <c r="W81" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="X81" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP81" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>809</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C82" s="2">
+        <v>45852</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>810</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45852.7965359028</v>
+      </c>
+      <c r="H82" s="0">
+        <v>5</v>
+      </c>
+      <c r="I82" s="0">
+        <v>5</v>
+      </c>
+      <c r="J82" s="0">
+        <v>5</v>
+      </c>
+      <c r="L82" s="0" t="s">
+        <v>811</v>
+      </c>
+      <c r="N82" s="0" t="s">
+        <v>812</v>
+      </c>
+      <c r="O82" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P82" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q82" s="0" t="s">
+        <v>813</v>
+      </c>
+      <c r="R82" s="2">
+        <v>45849</v>
+      </c>
+      <c r="S82" s="2">
+        <v>45852</v>
+      </c>
+      <c r="T82" s="0" t="s">
+        <v>814</v>
+      </c>
+      <c r="U82" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="V82" s="0" t="s">
+        <v>816</v>
+      </c>
+      <c r="W82" s="0" t="s">
+        <v>817</v>
+      </c>
+      <c r="X82" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y82" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA82" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB82" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC82" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD82" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP82" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>818</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83" s="2">
+        <v>45849</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>819</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45849.5684718982</v>
+      </c>
+      <c r="H83" s="0">
+        <v>5</v>
+      </c>
+      <c r="I83" s="0">
+        <v>5</v>
+      </c>
+      <c r="J83" s="0">
+        <v>5</v>
+      </c>
+      <c r="L83" s="0" t="s">
+        <v>820</v>
+      </c>
+      <c r="N83" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="O83" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P83" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q83" s="0" t="s">
+        <v>822</v>
+      </c>
+      <c r="R83" s="2">
+        <v>45844</v>
+      </c>
+      <c r="S83" s="2">
+        <v>45849</v>
+      </c>
+      <c r="T83" s="0" t="s">
+        <v>823</v>
+      </c>
+      <c r="U83" s="0" t="s">
+        <v>824</v>
+      </c>
+      <c r="V83" s="0" t="s">
+        <v>825</v>
+      </c>
+      <c r="W83" s="0" t="s">
+        <v>826</v>
+      </c>
+      <c r="X83" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP83" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>827</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84" s="2">
+        <v>45848</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>828</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45848.4790960417</v>
+      </c>
+      <c r="H84" s="0">
+        <v>5</v>
+      </c>
+      <c r="I84" s="0">
+        <v>5</v>
+      </c>
+      <c r="J84" s="0">
+        <v>5</v>
+      </c>
+      <c r="L84" s="0" t="s">
+        <v>829</v>
+      </c>
+      <c r="M84" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="N84" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="O84" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P84" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q84" s="0" t="s">
+        <v>832</v>
+      </c>
+      <c r="R84" s="2">
+        <v>45843</v>
+      </c>
+      <c r="S84" s="2">
+        <v>45844</v>
+      </c>
+      <c r="T84" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="U84" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="V84" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="W84" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="X84" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y84" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA84" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB84" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC84" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD84" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP84" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C85" s="2">
+        <v>45845</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45845.9336395949</v>
+      </c>
+      <c r="H85" s="0">
+        <v>5</v>
+      </c>
+      <c r="I85" s="0">
+        <v>5</v>
+      </c>
+      <c r="J85" s="0">
+        <v>5</v>
+      </c>
+      <c r="L85" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="N85" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="O85" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P85" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q85" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="R85" s="2">
+        <v>45838</v>
+      </c>
+      <c r="S85" s="2">
+        <v>45839</v>
+      </c>
+      <c r="T85" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="U85" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="V85" s="0" t="s">
+        <v>845</v>
+      </c>
+      <c r="W85" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="X85" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y85" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA85" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB85" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC85" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD85" s="0">
+        <v>4</v>
+      </c>
+      <c r="AP85" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" s="2">
+        <v>45840</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45840.9692126389</v>
+      </c>
+      <c r="H86" s="0">
+        <v>5</v>
+      </c>
+      <c r="I86" s="0">
+        <v>5</v>
+      </c>
+      <c r="J86" s="0">
+        <v>5</v>
+      </c>
+      <c r="L86" s="0" t="s">
+        <v>849</v>
+      </c>
+      <c r="N86" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="O86" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P86" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q86" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="R86" s="2">
+        <v>45836</v>
+      </c>
+      <c r="S86" s="2">
+        <v>45838</v>
+      </c>
+      <c r="T86" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="U86" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="V86" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="W86" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="X86" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y86" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA86" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB86" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC86" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD86" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP86" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>856</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" s="2">
+        <v>45834</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>857</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45834.7373021991</v>
+      </c>
+      <c r="H87" s="0">
+        <v>5</v>
+      </c>
+      <c r="I87" s="0">
+        <v>5</v>
+      </c>
+      <c r="J87" s="0">
+        <v>5</v>
+      </c>
+      <c r="L87" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="N87" s="0" t="s">
+        <v>859</v>
+      </c>
+      <c r="O87" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P87" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q87" s="0" t="s">
+        <v>860</v>
+      </c>
+      <c r="R87" s="2">
+        <v>45833</v>
+      </c>
+      <c r="S87" s="2">
+        <v>45834</v>
+      </c>
+      <c r="T87" s="0" t="s">
+        <v>861</v>
+      </c>
+      <c r="U87" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="V87" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="W87" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="X87" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y87" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA87" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB87" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC87" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD87" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP87" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>865</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" s="2">
+        <v>45831</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>866</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="G88" s="2">
         <v>45831.0369623843</v>
       </c>
-      <c r="H79" s="0">
-        <v>5</v>
-      </c>
-      <c r="I79" s="0">
-        <v>5</v>
-      </c>
-      <c r="J79" s="0">
-        <v>5</v>
-      </c>
-      <c r="L79" s="0" t="s">
-        <v>778</v>
-      </c>
-      <c r="N79" s="0" t="s">
-        <v>779</v>
-      </c>
-      <c r="O79" s="0" t="s">
+      <c r="H88" s="0">
+        <v>5</v>
+      </c>
+      <c r="I88" s="0">
+        <v>5</v>
+      </c>
+      <c r="J88" s="0">
+        <v>5</v>
+      </c>
+      <c r="L88" s="0" t="s">
+        <v>867</v>
+      </c>
+      <c r="N88" s="0" t="s">
+        <v>868</v>
+      </c>
+      <c r="O88" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P88" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="P79" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q79" s="0" t="s">
-        <v>780</v>
-      </c>
-      <c r="R79" s="2">
+      <c r="Q88" s="0" t="s">
+        <v>869</v>
+      </c>
+      <c r="R88" s="2">
         <v>45828</v>
       </c>
-      <c r="S79" s="2">
+      <c r="S88" s="2">
         <v>45830</v>
       </c>
-      <c r="T79" s="0" t="s">
-        <v>781</v>
-      </c>
-      <c r="U79" s="0" t="s">
-        <v>782</v>
-      </c>
-      <c r="V79" s="0" t="s">
-        <v>783</v>
-      </c>
-      <c r="W79" s="0" t="s">
-        <v>784</v>
-      </c>
-      <c r="X79" s="0">
-        <v>5</v>
-      </c>
-      <c r="Y79" s="0">
-        <v>5</v>
-      </c>
-      <c r="AA79" s="0">
-        <v>5</v>
-      </c>
-      <c r="AB79" s="0">
-        <v>5</v>
-      </c>
-      <c r="AC79" s="0">
-        <v>5</v>
-      </c>
-      <c r="AD79" s="0">
-        <v>5</v>
-      </c>
-      <c r="AP79" s="0" t="s">
-        <v>57</v>
+      <c r="T88" s="0" t="s">
+        <v>870</v>
+      </c>
+      <c r="U88" s="0" t="s">
+        <v>871</v>
+      </c>
+      <c r="V88" s="0" t="s">
+        <v>872</v>
+      </c>
+      <c r="W88" s="0" t="s">
+        <v>873</v>
+      </c>
+      <c r="X88" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y88" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA88" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB88" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC88" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD88" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP88" s="0" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP79"/>
+  <autoFilter ref="A1:AP88"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/public/data/review-export.xlsx
+++ b/public/data/review-export.xlsx
@@ -8,14 +8,14 @@
     <sheet name="review-export" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review-export'!$A$1:$AP$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review-export'!$A$1:$AP$102</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="1005">
   <si>
     <t>ReviewId</t>
   </si>
@@ -143,19 +143,450 @@
     <t>Distribution</t>
   </si>
   <si>
+    <t>ORREV117319443</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
+  </si>
+  <si>
+    <t>Bianca G</t>
+  </si>
+  <si>
+    <t>Jul 2026</t>
+  </si>
+  <si>
+    <t>Very beautiful! Will be back again! Great views and it’s a spectacular house!❤️</t>
+  </si>
+  <si>
+    <t>Thank you Bianca, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORP458447</t>
+  </si>
+  <si>
+    <t>Bluff Haven Retreat</t>
+  </si>
+  <si>
+    <t>ORB18468385</t>
+  </si>
+  <si>
+    <t>ORG623165127</t>
+  </si>
+  <si>
+    <t>Bianca</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>biancabenavidez00@gmail.com</t>
+  </si>
+  <si>
+    <t>Ineligible</t>
+  </si>
+  <si>
+    <t>ORREV117300820</t>
+  </si>
+  <si>
+    <t>Nancy P</t>
+  </si>
+  <si>
+    <t>Lovely stay. Nice touches throughout the home that showed the owners attention to detail and elevating the experience for their guests.</t>
+  </si>
+  <si>
+    <t>Thank you. Great touches throughout. Main floor bathroom I am sure is on your list for some TLC and I am sure it will be beautiful. Laundry room light was out but no big deal. Great location. Slept well. Loved decor and color choices. Also for cleaner. Only used bath upstairs :)</t>
+  </si>
+  <si>
+    <t>Thank you Nancy, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB18327452</t>
+  </si>
+  <si>
+    <t>ORG622907583</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Patterson</t>
+  </si>
+  <si>
+    <t>jodynanc95@yahoo.com</t>
+  </si>
+  <si>
+    <t>ORREV117273456</t>
+  </si>
+  <si>
+    <t>Elyssa J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolutely gorgeous house, exactly as pictured, with a lovely view. Very clean and easy to check into. The deck was perfect for relaxing, and we also had a great view of lightning during a storm that rolled through. We were looking for somewhere peaceful to come back to after exploring Pigeon Forge and this was perfect. 
+Like most houses in the area, the driveway was steep and a little treacherous though. I would recommend having someone out of the car watching/directing as you turn around at the top because I unfortunately did get my tire stuck in a small ditch at the top and had to be towed out. Just be careful and you can easily avoid it, but if I were the hosts I’d fill in that ditch with some gravel. Other than that, great place, and big thanks to the hosts!</t>
+  </si>
+  <si>
+    <t>Thank you!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you so much for your wonderful review! We’re thrilled to hear that you enjoyed the home, the views, and the peaceful setting. It’s great to know the deck was a highlight and that you were able to relax after exploring Pigeon Forge.
+We truly appreciate your feedback about the driveway. Mountain roads and driveways in this area can definitely be a little challenging. We’re sorry you experienced the inconvenience of getting your tire stuck, but we’re glad you were able to get assistance and continue enjoying your stay.
+We appreciate your suggestion regarding the small ditch and will take a look at that area to see how we can improve it. We’ll also continue reminding future guests to use extra caution when turning around at the top of the driveway.
+Thank you again for choosing our cabin and for sharing your experience. We’d love to welcome you back for another peaceful mountain getaway!</t>
+  </si>
+  <si>
+    <t>ORB18357854</t>
+  </si>
+  <si>
+    <t>ORG623027957</t>
+  </si>
+  <si>
+    <t>Elyssa</t>
+  </si>
+  <si>
+    <t>Johannesen</t>
+  </si>
+  <si>
+    <t>elyssa.johannesen@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV117205196</t>
+  </si>
+  <si>
+    <t>Alejandro V</t>
+  </si>
+  <si>
+    <t>Amazing views and a perfect cabin for a family of 4.</t>
+  </si>
+  <si>
+    <t>Thank you so much for your place. This was a memory for the books for our first family vacation!</t>
+  </si>
+  <si>
+    <t>Thank you so much Alejandro! 🥰 What an honor to be part of your family's first vacation memory, that truly means everything to us! We are so glad the views and cabin were perfect for your family and we hope to welcome you all back to Bluff Haven Retreat again someday! 🏡🏔️</t>
+  </si>
+  <si>
+    <t>ORB17600923</t>
+  </si>
+  <si>
+    <t>ORG622048337</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>Varela-Irps</t>
+  </si>
+  <si>
+    <t>varelaalex66@yahoo.com</t>
+  </si>
+  <si>
+    <t>ORREV117177852</t>
+  </si>
+  <si>
+    <t>Angela G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We had an amazing stay and would absolutely come back! In fact we plane to for next 4th of July weekend. 
+The cabin was spotless, cozy, and beautifully maintained, with everything we needed for a comfortable and relaxing getaway. The peaceful surroundings made it the perfect place to unwind, and we especially loved spending time on the porch enjoying the scenery.
+The hosts were welcoming, responsive, and made the entire experience seamless from check-in to check-out. It was clear they put a lot of care into making guests feel at home. If you're looking for a quiet, comfortable, and charming place to stay, we highly recommend this cabin. We can't wait to visit again!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything was perfect.
+Most comfortable beds ever!</t>
+  </si>
+  <si>
+    <t>Thank you Angela, welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB18184162</t>
+  </si>
+  <si>
+    <t>ORG622696289</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>Guthrie</t>
+  </si>
+  <si>
+    <t>taylorang79@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV117148864</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Marissa L</t>
+  </si>
+  <si>
+    <t>Jun 2026</t>
+  </si>
+  <si>
+    <t>We had a great stay at this cabin. It was beautiful and clean and we enjoyed the decor and spotless kitchen. The hosts were very quick to respond and let us check in early, which was amazing. The beds were comfortable and we enjoyed the amazing view. The only 2 things I feel could improve would be the downstairs bathroom could use some updated fixtures, they were very flimsy. And the upstairs large window was not clean so the view of the mountains from the loft was obscured. But, other than that this cabin was flawless! Thank you for the amazing stay!</t>
+  </si>
+  <si>
+    <t>Thank you, Marissa. Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB18132736</t>
+  </si>
+  <si>
+    <t>ORG622635070</t>
+  </si>
+  <si>
+    <t>Marissa</t>
+  </si>
+  <si>
+    <t>Lally</t>
+  </si>
+  <si>
+    <t>marissalally20@yahoo.com</t>
+  </si>
+  <si>
+    <t>ORREV117093169</t>
+  </si>
+  <si>
+    <t>Anthony Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabin was cozy! Views definitely lived up to the hype. We went when there was a little rain but it was so peaceful to be in a hot tub while it rained (hot tub area was covered). Kitchen was well equipped with basic tools. Beds were super comfortable, we greatly appreciated that after a long day of travel. 
+Hosts were very kind</t>
+  </si>
+  <si>
+    <t>Thanks for hosting us! We’ll certainly come back next time we find ourselves in TN!!</t>
+  </si>
+  <si>
+    <t>Thank you Anthony, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB18066421</t>
+  </si>
+  <si>
+    <t>ORG622551267</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>Zamacona</t>
+  </si>
+  <si>
+    <t>anthonyzamacona04@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV117093001</t>
+  </si>
+  <si>
+    <t>Trisha M</t>
+  </si>
+  <si>
+    <t>We had the best stay in this cabin! The location was perfect with the most amazing views. The cabin was clean, comfortable and had everything we needed. I loved the guide with local attractions and restaurant suggestions. That was very helpful. We would love to come back and stay at this cabin again!</t>
+  </si>
+  <si>
+    <t>Thank you for a great cabin experience! It was great!</t>
+  </si>
+  <si>
+    <t>Thank you Trisha, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17871759</t>
+  </si>
+  <si>
+    <t>ORG622326999</t>
+  </si>
+  <si>
+    <t>Trisha</t>
+  </si>
+  <si>
+    <t>Merritt</t>
+  </si>
+  <si>
+    <t>lawmerri@msn.com</t>
+  </si>
+  <si>
+    <t>ORREV117031790</t>
+  </si>
+  <si>
+    <t>Joshua Z</t>
+  </si>
+  <si>
+    <t>Awesome views</t>
+  </si>
+  <si>
+    <t>Thank you Joshua, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17784891</t>
+  </si>
+  <si>
+    <t>ORG622227652</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Zimmerman</t>
+  </si>
+  <si>
+    <t>zimmerjk@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116996872</t>
+  </si>
+  <si>
+    <t>Emily P</t>
+  </si>
+  <si>
+    <t>It was the perfect stay for me &amp; my friends! Almost didn’t want to leave to see the rest of Tennessee!</t>
+  </si>
+  <si>
+    <t>Thank you, Emily. Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17862493</t>
+  </si>
+  <si>
+    <t>ORG622315194</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>Perry</t>
+  </si>
+  <si>
+    <t>emilyjane655@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116924138</t>
+  </si>
+  <si>
+    <t>Shannon B</t>
+  </si>
+  <si>
+    <t>Every detail was thought of. From the beautifully folded towels and blankets to the absolutely immaculate kitchen, I can say it is the cleanest most well thought out home I have ever stayed in and the views are breathtaking. Thank you for sharing it with me.</t>
+  </si>
+  <si>
+    <t>Thank you for sharing your home with me. You have outdone yourself.</t>
+  </si>
+  <si>
+    <t>Thank you Shannon, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17392463</t>
+  </si>
+  <si>
+    <t>ORG621809300</t>
+  </si>
+  <si>
+    <t>Shannon</t>
+  </si>
+  <si>
+    <t>Bryant-Atkins</t>
+  </si>
+  <si>
+    <t>satkins.5kids@aol.com</t>
+  </si>
+  <si>
+    <t>ORREV116914126</t>
+  </si>
+  <si>
+    <t>Hans H</t>
+  </si>
+  <si>
+    <t>May 2026</t>
+  </si>
+  <si>
+    <t>We needed a quick get away for the family and this was perfect. 10/10 we would definitely come back.</t>
+  </si>
+  <si>
+    <t>Thank you again for hosting us. Everything was perfect!</t>
+  </si>
+  <si>
+    <t>Thank you, Hans. Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17912623</t>
+  </si>
+  <si>
+    <t>ORG622373142</t>
+  </si>
+  <si>
+    <t>Hans</t>
+  </si>
+  <si>
+    <t>Hetrick</t>
+  </si>
+  <si>
+    <t>hans.hetrick@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116893544</t>
+  </si>
+  <si>
+    <t>Adam L</t>
+  </si>
+  <si>
+    <t>The cabin was as described. The hosts were great and responsive. The cabin balcony faces west for nice sunsets over the mountains in the evenings.</t>
+  </si>
+  <si>
+    <t>A suggestion: The cushions on the swinging bucket seats hold water and the birds sit on top of them go to the bathroom on them. Possibly leave them on the deck until ready for use.</t>
+  </si>
+  <si>
+    <t>Thank you Adam, Welcome back anytime!!</t>
+  </si>
+  <si>
+    <t>ORB17607253</t>
+  </si>
+  <si>
+    <t>ORG622054665</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Logue</t>
+  </si>
+  <si>
+    <t>adam.logue87@gmail.com</t>
+  </si>
+  <si>
+    <t>ORREV116838527</t>
+  </si>
+  <si>
+    <t>Hope P</t>
+  </si>
+  <si>
+    <t>Anusha and Manesh responded quickly when we needed something. The cabin was described accurately, close to everything we needed and it was great to come back to the hot tub after a long hike. The beds were comfortable although we tried sleeping in the upstairs bed the first night and the AC above it was too loud for us so we switched bedrooms. Nothing much can be done about that but it’s a bummer since it has a good view in the morning. Overall recommend!</t>
+  </si>
+  <si>
+    <t>We appreciated the quick response when we needed something. We did spend a while looking prior to messaging you and got a message back that was slightly unhelpful to check the kitchen and to “please look”, not where it might be located. We were slightly disappointed in the response and that what we needed wasn’t available for the amententies offered. Otherwise we loved the cabin and it was a cozy stay.</t>
+  </si>
+  <si>
+    <t>Thank you so much Hope! We're thrilled you enjoyed the hot tub after your hike and found the cabin well described! We truly appreciate the feedback about the AC in the upstairs bedroom, we're looking into solutions to make that space even more comfortable. We'd love to welcome you back again soon! 🏡</t>
+  </si>
+  <si>
+    <t>ORB16988962</t>
+  </si>
+  <si>
+    <t>ORG621389426</t>
+  </si>
+  <si>
+    <t>Hope</t>
+  </si>
+  <si>
+    <t>hopepa20@gmail.com</t>
+  </si>
+  <si>
     <t>ORREV116809398</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
     <t>Dip C</t>
-  </si>
-  <si>
-    <t>May 2026</t>
   </si>
   <si>
     <t xml:space="preserve">We had an amazing stay at this beautiful wooden cabin! The cabin was spotless, cozy, and surrounded by gorgeous mountain scenery. Everything felt peaceful and relaxing, especially sitting outside in the fresh air and enjoying the quiet atmosphere.
@@ -166,12 +597,6 @@
     <t>Thank you Dip, Welcome back anytime!!</t>
   </si>
   <si>
-    <t>ORP458447</t>
-  </si>
-  <si>
-    <t>Bluff Haven Retreat</t>
-  </si>
-  <si>
     <t>ORB17462323</t>
   </si>
   <si>
@@ -185,9 +610,6 @@
   </si>
   <si>
     <t>dipto114@gmail.com</t>
-  </si>
-  <si>
-    <t>Ineligible</t>
   </si>
   <si>
     <t>ORREV116781804</t>
@@ -347,9 +769,6 @@
     <t>ORREV116474301</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Grace P</t>
   </si>
   <si>
@@ -396,9 +815,6 @@
   </si>
   <si>
     <t>ORG621479769</t>
-  </si>
-  <si>
-    <t>Emily</t>
   </si>
   <si>
     <t>Breezley</t>
@@ -1654,9 +2070,6 @@
     <t>ORG617848834</t>
   </si>
   <si>
-    <t>Shannon</t>
-  </si>
-  <si>
     <t>Joyner</t>
   </si>
   <si>
@@ -1967,9 +2380,6 @@
     <t>ORG617441763</t>
   </si>
   <si>
-    <t>Joshua</t>
-  </si>
-  <si>
     <t>Hendrix</t>
   </si>
   <si>
@@ -1983,9 +2393,6 @@
   </si>
   <si>
     <t>Great stay! Only regret was not having more time to be there.</t>
-  </si>
-  <si>
-    <t>Thank you Joshua, Welcome back anytime!!</t>
   </si>
   <si>
     <t>ORB14907171</t>
@@ -2548,16 +2955,10 @@
     <t>Thanks guys !</t>
   </si>
   <si>
-    <t>Thank you Anthony, Welcome back anytime!!</t>
-  </si>
-  <si>
     <t>ORB14266025</t>
   </si>
   <si>
     <t>ORG617455155</t>
-  </si>
-  <si>
-    <t>Anthony</t>
   </si>
   <si>
     <t>Reviguet</t>
@@ -2734,7 +3135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP88"/>
+  <dimension ref="A1:AP102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.3060188293457" customWidth="1"/>
@@ -2917,7 +3318,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="2">
-        <v>46165</v>
+        <v>46222</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>44</v>
@@ -2929,7 +3330,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="2">
-        <v>46165.7115106482</v>
+        <v>46222.6063853241</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -2940,7 +3341,7 @@
       <c r="J2" s="0">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="0" t="s">
         <v>47</v>
       </c>
       <c r="N2" s="0" t="s">
@@ -2956,10 +3357,10 @@
         <v>51</v>
       </c>
       <c r="R2" s="2">
-        <v>46164</v>
+        <v>46221</v>
       </c>
       <c r="S2" s="2">
-        <v>46165</v>
+        <v>46222</v>
       </c>
       <c r="T2" s="0" t="s">
         <v>52</v>
@@ -3003,7 +3404,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="2">
-        <v>46160</v>
+        <v>46221</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>44</v>
@@ -3015,7 +3416,7 @@
         <v>46</v>
       </c>
       <c r="G3" s="2">
-        <v>46160.7253088657</v>
+        <v>46221.4982837963</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -3026,7 +3427,7 @@
       <c r="J3" s="0">
         <v>5</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="0" t="s">
         <v>59</v>
       </c>
       <c r="M3" s="0" t="s">
@@ -3045,10 +3446,10 @@
         <v>62</v>
       </c>
       <c r="R3" s="2">
-        <v>46157</v>
+        <v>46217</v>
       </c>
       <c r="S3" s="2">
-        <v>46160</v>
+        <v>46221</v>
       </c>
       <c r="T3" s="0" t="s">
         <v>63</v>
@@ -3092,7 +3493,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2">
-        <v>46160</v>
+        <v>46217</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>44</v>
@@ -3104,7 +3505,7 @@
         <v>46</v>
       </c>
       <c r="G4" s="2">
-        <v>46160.6410878935</v>
+        <v>46217.4772626273</v>
       </c>
       <c r="H4" s="0">
         <v>5</v>
@@ -3115,13 +3516,13 @@
       <c r="J4" s="0">
         <v>5</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="3" t="s">
         <v>69</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="N4" s="3" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="0" t="s">
@@ -3134,10 +3535,10 @@
         <v>72</v>
       </c>
       <c r="R4" s="2">
-        <v>46149</v>
+        <v>46215</v>
       </c>
       <c r="S4" s="2">
-        <v>46153</v>
+        <v>46217</v>
       </c>
       <c r="T4" s="0" t="s">
         <v>73</v>
@@ -3181,7 +3582,7 @@
         <v>43</v>
       </c>
       <c r="C5" s="2">
-        <v>46157</v>
+        <v>46212</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>44</v>
@@ -3193,7 +3594,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2">
-        <v>46157.6984679514</v>
+        <v>46212.9264494329</v>
       </c>
       <c r="H5" s="0">
         <v>5</v>
@@ -3223,10 +3624,10 @@
         <v>82</v>
       </c>
       <c r="R5" s="2">
-        <v>46155</v>
+        <v>46209</v>
       </c>
       <c r="S5" s="2">
-        <v>46157</v>
+        <v>46212</v>
       </c>
       <c r="T5" s="0" t="s">
         <v>83</v>
@@ -3270,7 +3671,7 @@
         <v>43</v>
       </c>
       <c r="C6" s="2">
-        <v>46147</v>
+        <v>46209</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>44</v>
@@ -3282,7 +3683,7 @@
         <v>46</v>
       </c>
       <c r="G6" s="2">
-        <v>46147.8677982639</v>
+        <v>46209.6328085532</v>
       </c>
       <c r="H6" s="0">
         <v>5</v>
@@ -3293,10 +3694,10 @@
       <c r="J6" s="0">
         <v>5</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="3" t="s">
         <v>90</v>
       </c>
       <c r="N6" s="0" t="s">
@@ -3312,10 +3713,10 @@
         <v>92</v>
       </c>
       <c r="R6" s="2">
-        <v>46143</v>
+        <v>46205</v>
       </c>
       <c r="S6" s="2">
-        <v>46147</v>
+        <v>46209</v>
       </c>
       <c r="T6" s="0" t="s">
         <v>93</v>
@@ -3356,36 +3757,33 @@
         <v>97</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2">
-        <v>46139</v>
+        <v>46205</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>46139.8147854977</v>
+        <v>46205.8546512384</v>
       </c>
       <c r="H7" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="0">
         <v>5</v>
       </c>
       <c r="J7" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="M7" s="0" t="s">
         <v>101</v>
       </c>
       <c r="N7" s="0" t="s">
@@ -3401,10 +3799,10 @@
         <v>103</v>
       </c>
       <c r="R7" s="2">
-        <v>46132</v>
+        <v>46202</v>
       </c>
       <c r="S7" s="2">
-        <v>46138</v>
+        <v>46205</v>
       </c>
       <c r="T7" s="0" t="s">
         <v>104</v>
@@ -3445,37 +3843,40 @@
         <v>108</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2">
-        <v>46130</v>
+        <v>46198</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46198.9829474768</v>
+      </c>
+      <c r="H8" s="0">
+        <v>5</v>
+      </c>
+      <c r="I8" s="0">
+        <v>5</v>
+      </c>
+      <c r="J8" s="0">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="M8" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="G8" s="2">
-        <v>46130.5865972222</v>
-      </c>
-      <c r="H8" s="0">
-        <v>4</v>
-      </c>
-      <c r="I8" s="0">
-        <v>5</v>
-      </c>
-      <c r="J8" s="0">
-        <v>4</v>
-      </c>
-      <c r="L8" s="0" t="s">
+      <c r="N8" s="0" t="s">
         <v>112</v>
-      </c>
-      <c r="N8" s="0" t="s">
-        <v>113</v>
       </c>
       <c r="O8" s="0" t="s">
         <v>49</v>
@@ -3484,26 +3885,26 @@
         <v>50</v>
       </c>
       <c r="Q8" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="R8" s="2">
+        <v>46190</v>
+      </c>
+      <c r="S8" s="2">
+        <v>46194</v>
+      </c>
+      <c r="T8" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="R8" s="2">
-        <v>46112</v>
-      </c>
-      <c r="S8" s="2">
-        <v>46116</v>
-      </c>
-      <c r="T8" s="0" t="s">
+      <c r="U8" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="U8" s="0" t="s">
+      <c r="V8" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="V8" s="0" t="s">
+      <c r="W8" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="W8" s="0" t="s">
-        <v>118</v>
-      </c>
       <c r="X8" s="0">
         <v>5</v>
       </c>
@@ -3511,16 +3912,16 @@
         <v>5</v>
       </c>
       <c r="AA8" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="0">
         <v>5</v>
       </c>
       <c r="AC8" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD8" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP8" s="0" t="s">
         <v>56</v>
@@ -3528,43 +3929,43 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="2">
-        <v>46128</v>
+        <v>46198</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46198.9157279051</v>
+      </c>
+      <c r="H9" s="0">
+        <v>5</v>
+      </c>
+      <c r="I9" s="0">
+        <v>5</v>
+      </c>
+      <c r="J9" s="0">
+        <v>5</v>
+      </c>
+      <c r="L9" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="2">
-        <v>46128.760563831</v>
-      </c>
-      <c r="H9" s="0">
-        <v>5</v>
-      </c>
-      <c r="I9" s="0">
-        <v>5</v>
-      </c>
-      <c r="J9" s="0">
-        <v>5</v>
-      </c>
-      <c r="L9" s="0" t="s">
+      <c r="M9" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="N9" s="0" t="s">
         <v>122</v>
-      </c>
-      <c r="N9" s="0" t="s">
-        <v>123</v>
       </c>
       <c r="O9" s="0" t="s">
         <v>49</v>
@@ -3573,25 +3974,25 @@
         <v>50</v>
       </c>
       <c r="Q9" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="R9" s="2">
+        <v>46194</v>
+      </c>
+      <c r="S9" s="2">
+        <v>46198</v>
+      </c>
+      <c r="T9" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="R9" s="2">
-        <v>46123</v>
-      </c>
-      <c r="S9" s="2">
-        <v>46128</v>
-      </c>
-      <c r="T9" s="0" t="s">
+      <c r="U9" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="U9" s="0" t="s">
+      <c r="V9" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="V9" s="0" t="s">
+      <c r="W9" s="0" t="s">
         <v>127</v>
-      </c>
-      <c r="W9" s="0" t="s">
-        <v>128</v>
       </c>
       <c r="X9" s="0">
         <v>5</v>
@@ -3617,43 +4018,40 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="2">
-        <v>46123</v>
+        <v>46190</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46190.7466374537</v>
+      </c>
+      <c r="H10" s="0">
+        <v>5</v>
+      </c>
+      <c r="I10" s="0">
+        <v>5</v>
+      </c>
+      <c r="J10" s="0">
+        <v>5</v>
+      </c>
+      <c r="L10" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="2">
-        <v>46123.901372037</v>
-      </c>
-      <c r="H10" s="0">
-        <v>5</v>
-      </c>
-      <c r="I10" s="0">
-        <v>5</v>
-      </c>
-      <c r="J10" s="0">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="N10" s="0" t="s">
         <v>131</v>
-      </c>
-      <c r="M10" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="N10" s="0" t="s">
-        <v>133</v>
       </c>
       <c r="O10" s="0" t="s">
         <v>49</v>
@@ -3662,25 +4060,25 @@
         <v>50</v>
       </c>
       <c r="Q10" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="R10" s="2">
+        <v>46187</v>
+      </c>
+      <c r="S10" s="2">
+        <v>46190</v>
+      </c>
+      <c r="T10" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="U10" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="R10" s="2">
-        <v>46120</v>
-      </c>
-      <c r="S10" s="2">
-        <v>46123</v>
-      </c>
-      <c r="T10" s="0" t="s">
+      <c r="V10" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="U10" s="0" t="s">
+      <c r="W10" s="0" t="s">
         <v>136</v>
-      </c>
-      <c r="V10" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="W10" s="0" t="s">
-        <v>138</v>
       </c>
       <c r="X10" s="0">
         <v>5</v>
@@ -3706,43 +4104,40 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="2">
-        <v>46118</v>
+        <v>46187</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="2">
+        <v>46187.5248984954</v>
+      </c>
+      <c r="H11" s="0">
+        <v>5</v>
+      </c>
+      <c r="I11" s="0">
+        <v>5</v>
+      </c>
+      <c r="J11" s="0">
+        <v>5</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="N11" s="0" t="s">
         <v>140</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="2">
-        <v>46118.6686156481</v>
-      </c>
-      <c r="H11" s="0">
-        <v>5</v>
-      </c>
-      <c r="I11" s="0">
-        <v>5</v>
-      </c>
-      <c r="J11" s="0">
-        <v>5</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="M11" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>133</v>
       </c>
       <c r="O11" s="0" t="s">
         <v>49</v>
@@ -3751,25 +4146,25 @@
         <v>50</v>
       </c>
       <c r="Q11" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="R11" s="2">
+        <v>46186</v>
+      </c>
+      <c r="S11" s="2">
+        <v>46187</v>
+      </c>
+      <c r="T11" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="U11" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="R11" s="2">
-        <v>46116</v>
-      </c>
-      <c r="S11" s="2">
-        <v>46118</v>
-      </c>
-      <c r="T11" s="0" t="s">
+      <c r="V11" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="U11" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="V11" s="0" t="s">
+      <c r="W11" s="0" t="s">
         <v>145</v>
-      </c>
-      <c r="W11" s="0" t="s">
-        <v>146</v>
       </c>
       <c r="X11" s="0">
         <v>5</v>
@@ -3795,43 +4190,43 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="2">
-        <v>46117</v>
+        <v>46177</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2">
+        <v>46177.8246490278</v>
+      </c>
+      <c r="H12" s="0">
+        <v>5</v>
+      </c>
+      <c r="I12" s="0">
+        <v>5</v>
+      </c>
+      <c r="J12" s="0">
+        <v>5</v>
+      </c>
+      <c r="L12" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="2">
-        <v>46117.4916690046</v>
-      </c>
-      <c r="H12" s="0">
-        <v>5</v>
-      </c>
-      <c r="I12" s="0">
-        <v>5</v>
-      </c>
-      <c r="J12" s="0">
-        <v>5</v>
-      </c>
-      <c r="L12" s="0" t="s">
+      <c r="M12" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="M12" s="0" t="s">
+      <c r="N12" s="0" t="s">
         <v>150</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>151</v>
       </c>
       <c r="O12" s="0" t="s">
         <v>49</v>
@@ -3840,25 +4235,25 @@
         <v>50</v>
       </c>
       <c r="Q12" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="R12" s="2">
+        <v>46174</v>
+      </c>
+      <c r="S12" s="2">
+        <v>46177</v>
+      </c>
+      <c r="T12" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="R12" s="2">
-        <v>46110</v>
-      </c>
-      <c r="S12" s="2">
-        <v>46112</v>
-      </c>
-      <c r="T12" s="0" t="s">
+      <c r="U12" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="U12" s="0" t="s">
+      <c r="V12" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="V12" s="0" t="s">
+      <c r="W12" s="0" t="s">
         <v>155</v>
-      </c>
-      <c r="W12" s="0" t="s">
-        <v>156</v>
       </c>
       <c r="X12" s="0">
         <v>5</v>
@@ -3884,25 +4279,25 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="2">
-        <v>46116</v>
+        <v>46176</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="F13" s="0" t="s">
-        <v>111</v>
-      </c>
       <c r="G13" s="2">
-        <v>46116.7064720255</v>
+        <v>46176.971699294</v>
       </c>
       <c r="H13" s="0">
         <v>5</v>
@@ -3916,8 +4311,11 @@
       <c r="L13" s="0" t="s">
         <v>159</v>
       </c>
+      <c r="M13" s="0" t="s">
+        <v>160</v>
+      </c>
       <c r="N13" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" s="0" t="s">
         <v>49</v>
@@ -3926,25 +4324,25 @@
         <v>50</v>
       </c>
       <c r="Q13" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R13" s="2">
-        <v>46102</v>
+        <v>46173</v>
       </c>
       <c r="S13" s="2">
-        <v>46105</v>
+        <v>46174</v>
       </c>
       <c r="T13" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="W13" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="X13" s="0">
         <v>5</v>
@@ -3970,25 +4368,25 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="2">
-        <v>46111</v>
+        <v>46174</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G14" s="2">
-        <v>46111.839397338</v>
+        <v>46174.5132260069</v>
       </c>
       <c r="H14" s="0">
         <v>5</v>
@@ -4000,10 +4398,13 @@
         <v>5</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>170</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O14" s="0" t="s">
         <v>49</v>
@@ -4012,25 +4413,25 @@
         <v>50</v>
       </c>
       <c r="Q14" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R14" s="2">
-        <v>46105</v>
+        <v>46168</v>
       </c>
       <c r="S14" s="2">
-        <v>46108</v>
+        <v>46173</v>
       </c>
       <c r="T14" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="W14" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X14" s="0">
         <v>5</v>
@@ -4056,43 +4457,43 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C15" s="2">
-        <v>46102</v>
+        <v>46168</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G15" s="2">
-        <v>46102.6623598032</v>
+        <v>46168.8309850694</v>
       </c>
       <c r="H15" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="0">
         <v>5</v>
       </c>
       <c r="J15" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O15" s="0" t="s">
         <v>49</v>
@@ -4101,28 +4502,28 @@
         <v>50</v>
       </c>
       <c r="Q15" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R15" s="2">
-        <v>46100</v>
+        <v>46165</v>
       </c>
       <c r="S15" s="2">
-        <v>46102</v>
+        <v>46168</v>
       </c>
       <c r="T15" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="X15" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="0">
         <v>5</v>
@@ -4137,7 +4538,7 @@
         <v>5</v>
       </c>
       <c r="AD15" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP15" s="0" t="s">
         <v>56</v>
@@ -4145,25 +4546,25 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2">
-        <v>46100</v>
+        <v>46165</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G16" s="2">
-        <v>46100.7350191667</v>
+        <v>46165.7115106482</v>
       </c>
       <c r="H16" s="0">
         <v>5</v>
@@ -4174,10 +4575,7 @@
       <c r="J16" s="0">
         <v>5</v>
       </c>
-      <c r="L16" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="M16" s="0" t="s">
+      <c r="L16" s="3" t="s">
         <v>188</v>
       </c>
       <c r="N16" s="0" t="s">
@@ -4193,10 +4591,10 @@
         <v>190</v>
       </c>
       <c r="R16" s="2">
-        <v>46096</v>
+        <v>46164</v>
       </c>
       <c r="S16" s="2">
-        <v>46100</v>
+        <v>46165</v>
       </c>
       <c r="T16" s="0" t="s">
         <v>191</v>
@@ -4240,7 +4638,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="2">
-        <v>46096</v>
+        <v>46160</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>44</v>
@@ -4249,10 +4647,10 @@
         <v>196</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G17" s="2">
-        <v>46096.7874516898</v>
+        <v>46160.7253088657</v>
       </c>
       <c r="H17" s="0">
         <v>5</v>
@@ -4263,7 +4661,7 @@
       <c r="J17" s="0">
         <v>5</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="3" t="s">
         <v>197</v>
       </c>
       <c r="M17" s="0" t="s">
@@ -4282,10 +4680,10 @@
         <v>200</v>
       </c>
       <c r="R17" s="2">
-        <v>46093</v>
+        <v>46157</v>
       </c>
       <c r="S17" s="2">
-        <v>46096</v>
+        <v>46160</v>
       </c>
       <c r="T17" s="0" t="s">
         <v>201</v>
@@ -4329,7 +4727,7 @@
         <v>43</v>
       </c>
       <c r="C18" s="2">
-        <v>46093</v>
+        <v>46160</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>44</v>
@@ -4338,10 +4736,10 @@
         <v>206</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G18" s="2">
-        <v>46093.5347989931</v>
+        <v>46160.6410878935</v>
       </c>
       <c r="H18" s="0">
         <v>5</v>
@@ -4371,10 +4769,10 @@
         <v>210</v>
       </c>
       <c r="R18" s="2">
-        <v>46089</v>
+        <v>46149</v>
       </c>
       <c r="S18" s="2">
-        <v>46092</v>
+        <v>46153</v>
       </c>
       <c r="T18" s="0" t="s">
         <v>211</v>
@@ -4418,7 +4816,7 @@
         <v>43</v>
       </c>
       <c r="C19" s="2">
-        <v>46089</v>
+        <v>46157</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>44</v>
@@ -4427,10 +4825,10 @@
         <v>216</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G19" s="2">
-        <v>46089.7169537731</v>
+        <v>46157.6984679514</v>
       </c>
       <c r="H19" s="0">
         <v>5</v>
@@ -4460,10 +4858,10 @@
         <v>220</v>
       </c>
       <c r="R19" s="2">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="S19" s="2">
-        <v>46089</v>
+        <v>46157</v>
       </c>
       <c r="T19" s="0" t="s">
         <v>221</v>
@@ -4507,7 +4905,7 @@
         <v>43</v>
       </c>
       <c r="C20" s="2">
-        <v>46085</v>
+        <v>46147</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>44</v>
@@ -4516,10 +4914,10 @@
         <v>226</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="G20" s="2">
-        <v>46085.7193587963</v>
+        <v>46147.8677982639</v>
       </c>
       <c r="H20" s="0">
         <v>5</v>
@@ -4549,10 +4947,10 @@
         <v>230</v>
       </c>
       <c r="R20" s="2">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="S20" s="2">
-        <v>46085</v>
+        <v>46147</v>
       </c>
       <c r="T20" s="0" t="s">
         <v>231</v>
@@ -4596,7 +4994,7 @@
         <v>43</v>
       </c>
       <c r="C21" s="2">
-        <v>46078</v>
+        <v>46139</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>44</v>
@@ -4608,7 +5006,7 @@
         <v>237</v>
       </c>
       <c r="G21" s="2">
-        <v>46078.6396170949</v>
+        <v>46139.8147854977</v>
       </c>
       <c r="H21" s="0">
         <v>5</v>
@@ -4638,10 +5036,10 @@
         <v>241</v>
       </c>
       <c r="R21" s="2">
-        <v>46075</v>
+        <v>46132</v>
       </c>
       <c r="S21" s="2">
-        <v>46078</v>
+        <v>46138</v>
       </c>
       <c r="T21" s="0" t="s">
         <v>242</v>
@@ -4671,7 +5069,7 @@
         <v>5</v>
       </c>
       <c r="AD21" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP21" s="0" t="s">
         <v>56</v>
@@ -4682,10 +5080,10 @@
         <v>246</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C22" s="2">
-        <v>46075</v>
+        <v>46130</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>44</v>
@@ -4694,24 +5092,21 @@
         <v>247</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G22" s="2">
-        <v>46075.7313287847</v>
+        <v>46130.5865972222</v>
       </c>
       <c r="H22" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="0">
         <v>5</v>
       </c>
       <c r="J22" s="0">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="M22" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="0" t="s">
         <v>249</v>
       </c>
       <c r="N22" s="0" t="s">
@@ -4727,10 +5122,10 @@
         <v>251</v>
       </c>
       <c r="R22" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="S22" s="2">
-        <v>46075</v>
+        <v>46116</v>
       </c>
       <c r="T22" s="0" t="s">
         <v>252</v>
@@ -4751,16 +5146,16 @@
         <v>5</v>
       </c>
       <c r="AA22" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB22" s="0">
         <v>5</v>
       </c>
       <c r="AC22" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD22" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP22" s="0" t="s">
         <v>56</v>
@@ -4774,7 +5169,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="2">
-        <v>46072</v>
+        <v>46128</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>44</v>
@@ -4786,7 +5181,7 @@
         <v>237</v>
       </c>
       <c r="G23" s="2">
-        <v>46072.546856875</v>
+        <v>46128.760563831</v>
       </c>
       <c r="H23" s="0">
         <v>5</v>
@@ -4800,8 +5195,11 @@
       <c r="L23" s="0" t="s">
         <v>258</v>
       </c>
+      <c r="M23" s="0" t="s">
+        <v>259</v>
+      </c>
       <c r="N23" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O23" s="0" t="s">
         <v>49</v>
@@ -4810,19 +5208,19 @@
         <v>50</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R23" s="2">
-        <v>46067</v>
+        <v>46123</v>
       </c>
       <c r="S23" s="2">
-        <v>46071</v>
+        <v>46128</v>
       </c>
       <c r="T23" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>262</v>
+        <v>143</v>
       </c>
       <c r="V23" s="0" t="s">
         <v>263</v>
@@ -4860,7 +5258,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="2">
-        <v>46071</v>
+        <v>46123</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>44</v>
@@ -4872,7 +5270,7 @@
         <v>237</v>
       </c>
       <c r="G24" s="2">
-        <v>46071.6485774074</v>
+        <v>46123.901372037</v>
       </c>
       <c r="H24" s="0">
         <v>5</v>
@@ -4883,11 +5281,14 @@
       <c r="J24" s="0">
         <v>5</v>
       </c>
-      <c r="L24" s="0" t="s">
+      <c r="L24" s="3" t="s">
         <v>267</v>
       </c>
+      <c r="M24" s="0" t="s">
+        <v>268</v>
+      </c>
       <c r="N24" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O24" s="0" t="s">
         <v>49</v>
@@ -4896,25 +5297,25 @@
         <v>50</v>
       </c>
       <c r="Q24" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R24" s="2">
-        <v>46065</v>
+        <v>46120</v>
       </c>
       <c r="S24" s="2">
-        <v>46067</v>
+        <v>46123</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="W24" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="X24" s="0">
         <v>5</v>
@@ -4940,25 +5341,25 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="2">
-        <v>46062</v>
+        <v>46118</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>237</v>
       </c>
       <c r="G25" s="2">
-        <v>46062.6577711111</v>
+        <v>46118.6686156481</v>
       </c>
       <c r="H25" s="0">
         <v>5</v>
@@ -4970,10 +5371,13 @@
         <v>5</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>278</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="O25" s="0" t="s">
         <v>49</v>
@@ -4982,25 +5386,25 @@
         <v>50</v>
       </c>
       <c r="Q25" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="R25" s="2">
-        <v>46059</v>
+        <v>46116</v>
       </c>
       <c r="S25" s="2">
-        <v>46062</v>
+        <v>46118</v>
       </c>
       <c r="T25" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="W25" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X25" s="0">
         <v>5</v>
@@ -5026,25 +5430,25 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="2">
-        <v>46057</v>
+        <v>46117</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G26" s="2">
-        <v>46057.6514546875</v>
+        <v>46117.4916690046</v>
       </c>
       <c r="H26" s="0">
         <v>5</v>
@@ -5058,8 +5462,11 @@
       <c r="L26" s="0" t="s">
         <v>285</v>
       </c>
+      <c r="M26" s="0" t="s">
+        <v>286</v>
+      </c>
       <c r="N26" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O26" s="0" t="s">
         <v>49</v>
@@ -5068,25 +5475,25 @@
         <v>50</v>
       </c>
       <c r="Q26" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R26" s="2">
-        <v>46052</v>
+        <v>46110</v>
       </c>
       <c r="S26" s="2">
-        <v>46057</v>
+        <v>46112</v>
       </c>
       <c r="T26" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="W26" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="X26" s="0">
         <v>5</v>
@@ -5112,25 +5519,25 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="2">
-        <v>46046</v>
+        <v>46116</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G27" s="2">
-        <v>46046.6863551157</v>
+        <v>46116.7064720255</v>
       </c>
       <c r="H27" s="0">
         <v>5</v>
@@ -5142,10 +5549,10 @@
         <v>5</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N27" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O27" s="0" t="s">
         <v>49</v>
@@ -5154,25 +5561,25 @@
         <v>50</v>
       </c>
       <c r="Q27" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R27" s="2">
-        <v>46043</v>
+        <v>46102</v>
       </c>
       <c r="S27" s="2">
-        <v>46046</v>
+        <v>46105</v>
       </c>
       <c r="T27" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="U27" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V27" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="W27" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="X27" s="0">
         <v>5</v>
@@ -5198,25 +5605,25 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="2">
-        <v>46044</v>
+        <v>46111</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G28" s="2">
-        <v>46044.5556409607</v>
+        <v>46111.839397338</v>
       </c>
       <c r="H28" s="0">
         <v>5</v>
@@ -5228,10 +5635,10 @@
         <v>5</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N28" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O28" s="0" t="s">
         <v>49</v>
@@ -5240,25 +5647,25 @@
         <v>50</v>
       </c>
       <c r="Q28" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R28" s="2">
-        <v>46038</v>
+        <v>46105</v>
       </c>
       <c r="S28" s="2">
-        <v>46042</v>
+        <v>46108</v>
       </c>
       <c r="T28" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="U28" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="V28" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="W28" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X28" s="0">
         <v>5</v>
@@ -5284,25 +5691,25 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="2">
-        <v>46044</v>
+        <v>46102</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G29" s="2">
-        <v>46044.5534156597</v>
+        <v>46102.6623598032</v>
       </c>
       <c r="H29" s="0">
         <v>5</v>
@@ -5314,10 +5721,13 @@
         <v>5</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+      <c r="M29" s="0" t="s">
+        <v>314</v>
       </c>
       <c r="N29" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O29" s="0" t="s">
         <v>49</v>
@@ -5326,25 +5736,25 @@
         <v>50</v>
       </c>
       <c r="Q29" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="R29" s="2">
-        <v>46034</v>
+        <v>46100</v>
       </c>
       <c r="S29" s="2">
-        <v>46037</v>
+        <v>46102</v>
       </c>
       <c r="T29" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="U29" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="V29" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W29" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X29" s="0">
         <v>5</v>
@@ -5370,25 +5780,25 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="2">
-        <v>46033</v>
+        <v>46100</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G30" s="2">
-        <v>46033.7481770718</v>
+        <v>46100.7350191667</v>
       </c>
       <c r="H30" s="0">
         <v>5</v>
@@ -5400,13 +5810,13 @@
         <v>5</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>321</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>324</v>
       </c>
       <c r="N30" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O30" s="0" t="s">
         <v>49</v>
@@ -5415,25 +5825,25 @@
         <v>50</v>
       </c>
       <c r="Q30" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="R30" s="2">
-        <v>46030</v>
+        <v>46096</v>
       </c>
       <c r="S30" s="2">
-        <v>46033</v>
+        <v>46100</v>
       </c>
       <c r="T30" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="U30" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="V30" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="W30" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="X30" s="0">
         <v>5</v>
@@ -5459,25 +5869,25 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="2">
-        <v>46030</v>
+        <v>46096</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G31" s="2">
-        <v>46030.801171713</v>
+        <v>46096.7874516898</v>
       </c>
       <c r="H31" s="0">
         <v>5</v>
@@ -5489,13 +5899,13 @@
         <v>5</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M31" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N31" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O31" s="0" t="s">
         <v>49</v>
@@ -5504,25 +5914,25 @@
         <v>50</v>
       </c>
       <c r="Q31" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="R31" s="2">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="S31" s="2">
-        <v>46030</v>
+        <v>46096</v>
       </c>
       <c r="T31" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="U31" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="V31" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W31" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="X31" s="0">
         <v>5</v>
@@ -5548,25 +5958,25 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="2">
-        <v>46026</v>
+        <v>46093</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="G32" s="2">
-        <v>46026.8843540856</v>
+        <v>46093.5347989931</v>
       </c>
       <c r="H32" s="0">
         <v>5</v>
@@ -5578,13 +5988,13 @@
         <v>5</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N32" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O32" s="0" t="s">
         <v>49</v>
@@ -5593,25 +6003,25 @@
         <v>50</v>
       </c>
       <c r="Q32" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="R32" s="2">
-        <v>46025</v>
+        <v>46089</v>
       </c>
       <c r="S32" s="2">
-        <v>46026</v>
+        <v>46092</v>
       </c>
       <c r="T32" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U32" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V32" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W32" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X32" s="0">
         <v>5</v>
@@ -5637,25 +6047,25 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="2">
-        <v>46025</v>
+        <v>46089</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>351</v>
+        <v>248</v>
       </c>
       <c r="G33" s="2">
-        <v>46025.9183283912</v>
+        <v>46089.7169537731</v>
       </c>
       <c r="H33" s="0">
         <v>5</v>
@@ -5667,10 +6077,13 @@
         <v>5</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+      <c r="M33" s="0" t="s">
+        <v>354</v>
       </c>
       <c r="N33" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O33" s="0" t="s">
         <v>49</v>
@@ -5679,25 +6092,25 @@
         <v>50</v>
       </c>
       <c r="Q33" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="R33" s="2">
-        <v>46018</v>
+        <v>46085</v>
       </c>
       <c r="S33" s="2">
-        <v>46025</v>
+        <v>46089</v>
       </c>
       <c r="T33" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="U33" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="V33" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="W33" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="X33" s="0">
         <v>5</v>
@@ -5723,25 +6136,25 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="2">
-        <v>46024</v>
+        <v>46085</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>351</v>
+        <v>248</v>
       </c>
       <c r="G34" s="2">
-        <v>46024.2781152662</v>
+        <v>46085.7193587963</v>
       </c>
       <c r="H34" s="0">
         <v>5</v>
@@ -5753,10 +6166,13 @@
         <v>5</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
+      </c>
+      <c r="M34" s="0" t="s">
+        <v>364</v>
       </c>
       <c r="N34" s="0" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O34" s="0" t="s">
         <v>49</v>
@@ -5765,25 +6181,25 @@
         <v>50</v>
       </c>
       <c r="Q34" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="R34" s="2">
-        <v>46017</v>
+        <v>46082</v>
       </c>
       <c r="S34" s="2">
-        <v>46018</v>
+        <v>46085</v>
       </c>
       <c r="T34" s="0" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="U34" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="V34" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="W34" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="X34" s="0">
         <v>5</v>
@@ -5809,25 +6225,25 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="2">
-        <v>46023</v>
+        <v>46078</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G35" s="2">
-        <v>46023.7304273495</v>
+        <v>46078.6396170949</v>
       </c>
       <c r="H35" s="0">
         <v>5</v>
@@ -5839,10 +6255,13 @@
         <v>5</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>375</v>
       </c>
       <c r="N35" s="0" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O35" s="0" t="s">
         <v>49</v>
@@ -5851,25 +6270,25 @@
         <v>50</v>
       </c>
       <c r="Q35" s="0" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="R35" s="2">
-        <v>46010</v>
+        <v>46075</v>
       </c>
       <c r="S35" s="2">
-        <v>46012</v>
+        <v>46078</v>
       </c>
       <c r="T35" s="0" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="U35" s="0" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="V35" s="0" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="W35" s="0" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="X35" s="0">
         <v>5</v>
@@ -5887,7 +6306,7 @@
         <v>5</v>
       </c>
       <c r="AD35" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP35" s="0" t="s">
         <v>56</v>
@@ -5895,25 +6314,25 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="2">
-        <v>46018</v>
+        <v>46075</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G36" s="2">
-        <v>46018.4146147801</v>
+        <v>46075.7313287847</v>
       </c>
       <c r="H36" s="0">
         <v>5</v>
@@ -5924,14 +6343,14 @@
       <c r="J36" s="0">
         <v>5</v>
       </c>
-      <c r="L36" s="0" t="s">
-        <v>379</v>
+      <c r="L36" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="O36" s="0" t="s">
         <v>49</v>
@@ -5940,25 +6359,25 @@
         <v>50</v>
       </c>
       <c r="Q36" s="0" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="R36" s="2">
-        <v>46013</v>
+        <v>46073</v>
       </c>
       <c r="S36" s="2">
-        <v>46017</v>
+        <v>46075</v>
       </c>
       <c r="T36" s="0" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="U36" s="0" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="V36" s="0" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="W36" s="0" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="X36" s="0">
         <v>5</v>
@@ -5984,25 +6403,25 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="2">
-        <v>46011</v>
+        <v>46072</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G37" s="2">
-        <v>46011.6063615046</v>
+        <v>46072.546856875</v>
       </c>
       <c r="H37" s="0">
         <v>5</v>
@@ -6014,10 +6433,10 @@
         <v>5</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="N37" s="0" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="O37" s="0" t="s">
         <v>49</v>
@@ -6026,25 +6445,25 @@
         <v>50</v>
       </c>
       <c r="Q37" s="0" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="R37" s="2">
-        <v>46006</v>
+        <v>46067</v>
       </c>
       <c r="S37" s="2">
-        <v>46010</v>
+        <v>46071</v>
       </c>
       <c r="T37" s="0" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="U37" s="0" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="V37" s="0" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="W37" s="0" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="X37" s="0">
         <v>5</v>
@@ -6070,25 +6489,25 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="2">
-        <v>46005</v>
+        <v>46071</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G38" s="2">
-        <v>46005.7644445486</v>
+        <v>46071.6485774074</v>
       </c>
       <c r="H38" s="0">
         <v>5</v>
@@ -6100,10 +6519,10 @@
         <v>5</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="N38" s="0" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="O38" s="0" t="s">
         <v>49</v>
@@ -6112,25 +6531,25 @@
         <v>50</v>
       </c>
       <c r="Q38" s="0" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="R38" s="2">
-        <v>46002</v>
+        <v>46065</v>
       </c>
       <c r="S38" s="2">
-        <v>46005</v>
+        <v>46067</v>
       </c>
       <c r="T38" s="0" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="U38" s="0" t="s">
-        <v>402</v>
+        <v>338</v>
       </c>
       <c r="V38" s="0" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="W38" s="0" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="X38" s="0">
         <v>5</v>
@@ -6156,43 +6575,40 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C39" s="2">
-        <v>46003</v>
+        <v>46062</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G39" s="2">
-        <v>46003.8492650926</v>
+        <v>46062.6577711111</v>
       </c>
       <c r="H39" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="0">
         <v>5</v>
       </c>
       <c r="J39" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="M39" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N39" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O39" s="0" t="s">
         <v>49</v>
@@ -6201,28 +6617,28 @@
         <v>50</v>
       </c>
       <c r="Q39" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="R39" s="2">
-        <v>45996</v>
+        <v>46059</v>
       </c>
       <c r="S39" s="2">
-        <v>45998</v>
+        <v>46062</v>
       </c>
       <c r="T39" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="U39" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="V39" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="W39" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="X39" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y39" s="0">
         <v>5</v>
@@ -6237,7 +6653,7 @@
         <v>5</v>
       </c>
       <c r="AD39" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP39" s="0" t="s">
         <v>56</v>
@@ -6245,25 +6661,25 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="2">
-        <v>46001</v>
+        <v>46057</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="G40" s="2">
-        <v>46001.7156633218</v>
+        <v>46057.6514546875</v>
       </c>
       <c r="H40" s="0">
         <v>5</v>
@@ -6275,10 +6691,10 @@
         <v>5</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="N40" s="0" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="O40" s="0" t="s">
         <v>49</v>
@@ -6287,25 +6703,25 @@
         <v>50</v>
       </c>
       <c r="Q40" s="0" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="R40" s="2">
-        <v>45998</v>
+        <v>46052</v>
       </c>
       <c r="S40" s="2">
-        <v>46001</v>
+        <v>46057</v>
       </c>
       <c r="T40" s="0" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="U40" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="V40" s="0" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="W40" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="X40" s="0">
         <v>5</v>
@@ -6331,25 +6747,25 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="2">
-        <v>45999</v>
+        <v>46046</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="G41" s="2">
-        <v>45999.39383875</v>
+        <v>46046.6863551157</v>
       </c>
       <c r="H41" s="0">
         <v>5</v>
@@ -6361,10 +6777,10 @@
         <v>5</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="O41" s="0" t="s">
         <v>49</v>
@@ -6373,25 +6789,25 @@
         <v>50</v>
       </c>
       <c r="Q41" s="0" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="R41" s="2">
-        <v>45993</v>
+        <v>46043</v>
       </c>
       <c r="S41" s="2">
-        <v>45994</v>
+        <v>46046</v>
       </c>
       <c r="T41" s="0" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="U41" s="0" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="V41" s="0" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="W41" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="X41" s="0">
         <v>5</v>
@@ -6417,25 +6833,25 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="2">
-        <v>45997</v>
+        <v>46044</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="G42" s="2">
-        <v>45997.7247070486</v>
+        <v>46044.5556409607</v>
       </c>
       <c r="H42" s="0">
         <v>5</v>
@@ -6447,13 +6863,10 @@
         <v>5</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="M42" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="N42" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O42" s="0" t="s">
         <v>49</v>
@@ -6462,25 +6875,25 @@
         <v>50</v>
       </c>
       <c r="Q42" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="R42" s="2">
-        <v>45994</v>
+        <v>46038</v>
       </c>
       <c r="S42" s="2">
-        <v>45996</v>
+        <v>46042</v>
       </c>
       <c r="T42" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="U42" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="V42" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="W42" s="0" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="X42" s="0">
         <v>5</v>
@@ -6506,25 +6919,25 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="2">
-        <v>45993</v>
+        <v>46044</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="G43" s="2">
-        <v>45993.7333972569</v>
+        <v>46044.5534156597</v>
       </c>
       <c r="H43" s="0">
         <v>5</v>
@@ -6536,10 +6949,10 @@
         <v>5</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N43" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O43" s="0" t="s">
         <v>49</v>
@@ -6548,25 +6961,25 @@
         <v>50</v>
       </c>
       <c r="Q43" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="R43" s="2">
-        <v>45990</v>
+        <v>46034</v>
       </c>
       <c r="S43" s="2">
-        <v>45993</v>
+        <v>46037</v>
       </c>
       <c r="T43" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="U43" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="V43" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="W43" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="X43" s="0">
         <v>5</v>
@@ -6592,25 +7005,25 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="2">
-        <v>45990</v>
+        <v>46033</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="G44" s="2">
-        <v>45990.6230057292</v>
+        <v>46033.7481770718</v>
       </c>
       <c r="H44" s="0">
         <v>5</v>
@@ -6622,13 +7035,13 @@
         <v>5</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="M44" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>458</v>
       </c>
       <c r="N44" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O44" s="0" t="s">
         <v>49</v>
@@ -6637,25 +7050,25 @@
         <v>50</v>
       </c>
       <c r="Q44" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R44" s="2">
-        <v>45986</v>
+        <v>46030</v>
       </c>
       <c r="S44" s="2">
-        <v>45990</v>
+        <v>46033</v>
       </c>
       <c r="T44" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="U44" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="V44" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="W44" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="X44" s="0">
         <v>5</v>
@@ -6681,25 +7094,25 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="2">
-        <v>45986</v>
+        <v>46030</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="G45" s="2">
-        <v>45986.7385835995</v>
+        <v>46030.801171713</v>
       </c>
       <c r="H45" s="0">
         <v>5</v>
@@ -6710,14 +7123,14 @@
       <c r="J45" s="0">
         <v>5</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>466</v>
+      <c r="L45" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="M45" s="0" t="s">
+        <v>468</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O45" s="0" t="s">
         <v>49</v>
@@ -6726,25 +7139,25 @@
         <v>50</v>
       </c>
       <c r="Q45" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="R45" s="2">
-        <v>45977</v>
+        <v>46027</v>
       </c>
       <c r="S45" s="2">
-        <v>45983</v>
+        <v>46030</v>
       </c>
       <c r="T45" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="U45" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="V45" s="0" t="s">
-        <v>192</v>
+        <v>473</v>
       </c>
       <c r="W45" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="X45" s="0">
         <v>5</v>
@@ -6770,43 +7183,43 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C46" s="2">
-        <v>45986</v>
+        <v>46026</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="G46" s="2">
-        <v>45986.574325081</v>
+        <v>46026.8843540856</v>
       </c>
       <c r="H46" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I46" s="0">
         <v>5</v>
       </c>
       <c r="J46" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M46" s="0" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N46" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="O46" s="0" t="s">
         <v>49</v>
@@ -6815,28 +7228,28 @@
         <v>50</v>
       </c>
       <c r="Q46" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="R46" s="2">
-        <v>45983</v>
+        <v>46025</v>
       </c>
       <c r="S46" s="2">
-        <v>45986</v>
+        <v>46026</v>
       </c>
       <c r="T46" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="U46" s="0" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="V46" s="0" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="W46" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="X46" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y46" s="0">
         <v>5</v>
@@ -6845,13 +7258,13 @@
         <v>5</v>
       </c>
       <c r="AB46" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC46" s="0">
         <v>5</v>
       </c>
       <c r="AD46" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP46" s="0" t="s">
         <v>56</v>
@@ -6859,25 +7272,25 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="2">
-        <v>45981</v>
+        <v>46025</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="G47" s="2">
-        <v>45981.6819216319</v>
+        <v>46025.9183283912</v>
       </c>
       <c r="H47" s="0">
         <v>5</v>
@@ -6889,13 +7302,10 @@
         <v>5</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="M47" s="0" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N47" s="0" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O47" s="0" t="s">
         <v>49</v>
@@ -6904,25 +7314,25 @@
         <v>50</v>
       </c>
       <c r="Q47" s="0" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="R47" s="2">
-        <v>45970</v>
+        <v>46018</v>
       </c>
       <c r="S47" s="2">
-        <v>45977</v>
+        <v>46025</v>
       </c>
       <c r="T47" s="0" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="U47" s="0" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="V47" s="0" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="W47" s="0" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="X47" s="0">
         <v>5</v>
@@ -6948,25 +7358,25 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="2">
-        <v>45970</v>
+        <v>46024</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="G48" s="2">
-        <v>45970.7607620602</v>
+        <v>46024.2781152662</v>
       </c>
       <c r="H48" s="0">
         <v>5</v>
@@ -6978,10 +7388,10 @@
         <v>5</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
+      </c>
+      <c r="N48" s="0" t="s">
+        <v>498</v>
       </c>
       <c r="O48" s="0" t="s">
         <v>49</v>
@@ -6990,25 +7400,25 @@
         <v>50</v>
       </c>
       <c r="Q48" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R48" s="2">
-        <v>45969</v>
+        <v>46017</v>
       </c>
       <c r="S48" s="2">
-        <v>45970</v>
+        <v>46018</v>
       </c>
       <c r="T48" s="0" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="U48" s="0" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="V48" s="0" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="W48" s="0" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="X48" s="0">
         <v>5</v>
@@ -7034,25 +7444,25 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="2">
-        <v>45970</v>
+        <v>46023</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="G49" s="2">
-        <v>45970.4829323264</v>
+        <v>46023.7304273495</v>
       </c>
       <c r="H49" s="0">
         <v>5</v>
@@ -7064,13 +7474,10 @@
         <v>5</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="M49" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
+      </c>
+      <c r="N49" s="0" t="s">
+        <v>507</v>
       </c>
       <c r="O49" s="0" t="s">
         <v>49</v>
@@ -7079,25 +7486,25 @@
         <v>50</v>
       </c>
       <c r="Q49" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="R49" s="2">
-        <v>45967</v>
+        <v>46010</v>
       </c>
       <c r="S49" s="2">
-        <v>45969</v>
+        <v>46012</v>
       </c>
       <c r="T49" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="U49" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="V49" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="W49" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="X49" s="0">
         <v>5</v>
@@ -7115,7 +7522,7 @@
         <v>5</v>
       </c>
       <c r="AD49" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP49" s="0" t="s">
         <v>56</v>
@@ -7123,25 +7530,25 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="2">
-        <v>45965</v>
+        <v>46018</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="G50" s="2">
-        <v>45965.8421596644</v>
+        <v>46018.4146147801</v>
       </c>
       <c r="H50" s="0">
         <v>5</v>
@@ -7153,10 +7560,13 @@
         <v>5</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
+      </c>
+      <c r="M50" s="0" t="s">
+        <v>516</v>
       </c>
       <c r="N50" s="0" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="O50" s="0" t="s">
         <v>49</v>
@@ -7165,25 +7575,25 @@
         <v>50</v>
       </c>
       <c r="Q50" s="0" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="R50" s="2">
-        <v>45962</v>
+        <v>46013</v>
       </c>
       <c r="S50" s="2">
-        <v>45965</v>
+        <v>46017</v>
       </c>
       <c r="T50" s="0" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="U50" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="V50" s="0" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="W50" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="X50" s="0">
         <v>5</v>
@@ -7209,25 +7619,25 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="2">
-        <v>45962</v>
+        <v>46011</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="G51" s="2">
-        <v>45962.6437613773</v>
+        <v>46011.6063615046</v>
       </c>
       <c r="H51" s="0">
         <v>5</v>
@@ -7239,13 +7649,10 @@
         <v>5</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>523</v>
-      </c>
-      <c r="M51" s="0" t="s">
-        <v>524</v>
-      </c>
-      <c r="N51" s="3" t="s">
         <v>525</v>
+      </c>
+      <c r="N51" s="0" t="s">
+        <v>526</v>
       </c>
       <c r="O51" s="0" t="s">
         <v>49</v>
@@ -7254,25 +7661,25 @@
         <v>50</v>
       </c>
       <c r="Q51" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="R51" s="2">
-        <v>45959</v>
+        <v>46006</v>
       </c>
       <c r="S51" s="2">
-        <v>45962</v>
+        <v>46010</v>
       </c>
       <c r="T51" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="U51" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="V51" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="W51" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="X51" s="0">
         <v>5</v>
@@ -7298,25 +7705,25 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="2">
-        <v>45959</v>
+        <v>46005</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="G52" s="2">
-        <v>45959.6416564352</v>
+        <v>46005.7644445486</v>
       </c>
       <c r="H52" s="0">
         <v>5</v>
@@ -7328,9 +7735,6 @@
         <v>5</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>533</v>
-      </c>
-      <c r="M52" s="0" t="s">
         <v>534</v>
       </c>
       <c r="N52" s="0" t="s">
@@ -7346,10 +7750,10 @@
         <v>536</v>
       </c>
       <c r="R52" s="2">
-        <v>45955</v>
+        <v>46002</v>
       </c>
       <c r="S52" s="2">
-        <v>45959</v>
+        <v>46005</v>
       </c>
       <c r="T52" s="0" t="s">
         <v>537</v>
@@ -7370,7 +7774,7 @@
         <v>5</v>
       </c>
       <c r="AA52" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB52" s="0">
         <v>5</v>
@@ -7379,7 +7783,7 @@
         <v>5</v>
       </c>
       <c r="AD52" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP52" s="0" t="s">
         <v>56</v>
@@ -7390,10 +7794,10 @@
         <v>541</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C53" s="2">
-        <v>45955</v>
+        <v>46003</v>
       </c>
       <c r="D53" s="0" t="s">
         <v>44</v>
@@ -7402,10 +7806,10 @@
         <v>542</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="G53" s="2">
-        <v>45955.8044966319</v>
+        <v>46003.8492650926</v>
       </c>
       <c r="H53" s="0">
         <v>4</v>
@@ -7419,8 +7823,11 @@
       <c r="L53" s="0" t="s">
         <v>543</v>
       </c>
+      <c r="M53" s="0" t="s">
+        <v>544</v>
+      </c>
       <c r="N53" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O53" s="0" t="s">
         <v>49</v>
@@ -7429,28 +7836,28 @@
         <v>50</v>
       </c>
       <c r="Q53" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="R53" s="2">
-        <v>45954</v>
+        <v>45996</v>
       </c>
       <c r="S53" s="2">
-        <v>45955</v>
+        <v>45998</v>
       </c>
       <c r="T53" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U53" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="V53" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="W53" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="X53" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y53" s="0">
         <v>5</v>
@@ -7462,7 +7869,7 @@
         <v>5</v>
       </c>
       <c r="AC53" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD53" s="0">
         <v>4</v>
@@ -7473,25 +7880,25 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="2">
-        <v>45954</v>
+        <v>46001</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="G54" s="2">
-        <v>45954.9526523148</v>
+        <v>46001.7156633218</v>
       </c>
       <c r="H54" s="0">
         <v>5</v>
@@ -7503,10 +7910,10 @@
         <v>5</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>552</v>
-      </c>
-      <c r="N54" s="3" t="s">
         <v>553</v>
+      </c>
+      <c r="N54" s="0" t="s">
+        <v>554</v>
       </c>
       <c r="O54" s="0" t="s">
         <v>49</v>
@@ -7515,25 +7922,25 @@
         <v>50</v>
       </c>
       <c r="Q54" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R54" s="2">
-        <v>45949</v>
+        <v>45998</v>
       </c>
       <c r="S54" s="2">
-        <v>45954</v>
+        <v>46001</v>
       </c>
       <c r="T54" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="U54" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="V54" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="W54" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="X54" s="0">
         <v>5</v>
@@ -7559,25 +7966,25 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="2">
-        <v>45949</v>
+        <v>45999</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="G55" s="2">
-        <v>45949.8261354282</v>
+        <v>45999.39383875</v>
       </c>
       <c r="H55" s="0">
         <v>5</v>
@@ -7589,10 +7996,10 @@
         <v>5</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N55" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O55" s="0" t="s">
         <v>49</v>
@@ -7601,25 +8008,25 @@
         <v>50</v>
       </c>
       <c r="Q55" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="R55" s="2">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="S55" s="2">
-        <v>45949</v>
+        <v>45994</v>
       </c>
       <c r="T55" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="U55" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="V55" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="W55" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="X55" s="0">
         <v>5</v>
@@ -7645,25 +8052,25 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="2">
-        <v>45946</v>
+        <v>45997</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="G56" s="2">
-        <v>45946.8340835069</v>
+        <v>45997.7247070486</v>
       </c>
       <c r="H56" s="0">
         <v>5</v>
@@ -7675,13 +8082,13 @@
         <v>5</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="N56" s="3" t="s">
         <v>572</v>
+      </c>
+      <c r="N56" s="0" t="s">
+        <v>573</v>
       </c>
       <c r="O56" s="0" t="s">
         <v>49</v>
@@ -7690,25 +8097,25 @@
         <v>50</v>
       </c>
       <c r="Q56" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="R56" s="2">
-        <v>45941</v>
+        <v>45994</v>
       </c>
       <c r="S56" s="2">
-        <v>45946</v>
+        <v>45996</v>
       </c>
       <c r="T56" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="U56" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="V56" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="W56" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="X56" s="0">
         <v>5</v>
@@ -7734,25 +8141,25 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="2">
-        <v>45938</v>
+        <v>45993</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>522</v>
+        <v>581</v>
       </c>
       <c r="G57" s="2">
-        <v>45938.7601655556</v>
+        <v>45993.7333972569</v>
       </c>
       <c r="H57" s="0">
         <v>5</v>
@@ -7764,10 +8171,10 @@
         <v>5</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>580</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
+      </c>
+      <c r="N57" s="0" t="s">
+        <v>583</v>
       </c>
       <c r="O57" s="0" t="s">
         <v>49</v>
@@ -7776,25 +8183,25 @@
         <v>50</v>
       </c>
       <c r="Q57" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R57" s="2">
-        <v>45932</v>
+        <v>45990</v>
       </c>
       <c r="S57" s="2">
-        <v>45935</v>
+        <v>45993</v>
       </c>
       <c r="T57" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="U57" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="V57" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="W57" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="X57" s="0">
         <v>5</v>
@@ -7820,25 +8227,25 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="2">
-        <v>45937</v>
+        <v>45990</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>522</v>
+        <v>581</v>
       </c>
       <c r="G58" s="2">
-        <v>45937.8034676042</v>
+        <v>45990.6230057292</v>
       </c>
       <c r="H58" s="0">
         <v>5</v>
@@ -7850,10 +8257,13 @@
         <v>5</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>592</v>
       </c>
       <c r="N58" s="0" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="O58" s="0" t="s">
         <v>49</v>
@@ -7862,25 +8272,25 @@
         <v>50</v>
       </c>
       <c r="Q58" s="0" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="R58" s="2">
-        <v>45935</v>
+        <v>45986</v>
       </c>
       <c r="S58" s="2">
-        <v>45937</v>
+        <v>45990</v>
       </c>
       <c r="T58" s="0" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="U58" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="V58" s="0" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="W58" s="0" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="X58" s="0">
         <v>5</v>
@@ -7898,7 +8308,7 @@
         <v>5</v>
       </c>
       <c r="AD58" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP58" s="0" t="s">
         <v>56</v>
@@ -7906,25 +8316,25 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="2">
-        <v>45928</v>
+        <v>45986</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="G59" s="2">
-        <v>45928.7262096412</v>
+        <v>45986.7385835995</v>
       </c>
       <c r="H59" s="0">
         <v>5</v>
@@ -7935,14 +8345,14 @@
       <c r="J59" s="0">
         <v>5</v>
       </c>
-      <c r="L59" s="0" t="s">
-        <v>599</v>
-      </c>
-      <c r="M59" s="0" t="s">
-        <v>600</v>
-      </c>
-      <c r="N59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>601</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="N59" s="0" t="s">
+        <v>603</v>
       </c>
       <c r="O59" s="0" t="s">
         <v>49</v>
@@ -7951,25 +8361,25 @@
         <v>50</v>
       </c>
       <c r="Q59" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="R59" s="2">
-        <v>45925</v>
+        <v>45977</v>
       </c>
       <c r="S59" s="2">
-        <v>45928</v>
+        <v>45983</v>
       </c>
       <c r="T59" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="U59" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="V59" s="0" t="s">
-        <v>605</v>
+        <v>328</v>
       </c>
       <c r="W59" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="X59" s="0">
         <v>5</v>
@@ -7995,40 +8405,43 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C60" s="2">
-        <v>45924</v>
+        <v>45986</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="G60" s="2">
-        <v>45924.6507670833</v>
+        <v>45986.574325081</v>
       </c>
       <c r="H60" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I60" s="0">
         <v>5</v>
       </c>
       <c r="J60" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>611</v>
       </c>
       <c r="N60" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="O60" s="0" t="s">
         <v>49</v>
@@ -8037,28 +8450,28 @@
         <v>50</v>
       </c>
       <c r="Q60" s="0" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="R60" s="2">
-        <v>45921</v>
+        <v>45983</v>
       </c>
       <c r="S60" s="2">
-        <v>45924</v>
+        <v>45986</v>
       </c>
       <c r="T60" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="U60" s="0" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="V60" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="W60" s="0" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="X60" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y60" s="0">
         <v>5</v>
@@ -8067,13 +8480,13 @@
         <v>5</v>
       </c>
       <c r="AB60" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC60" s="0">
         <v>5</v>
       </c>
       <c r="AD60" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP60" s="0" t="s">
         <v>56</v>
@@ -8081,25 +8494,25 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="2">
-        <v>45923</v>
+        <v>45981</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="G61" s="2">
-        <v>45923.3761746296</v>
+        <v>45981.6819216319</v>
       </c>
       <c r="H61" s="0">
         <v>5</v>
@@ -8111,10 +8524,13 @@
         <v>5</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
+      </c>
+      <c r="M61" s="0" t="s">
+        <v>621</v>
       </c>
       <c r="N61" s="0" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="O61" s="0" t="s">
         <v>49</v>
@@ -8123,25 +8539,25 @@
         <v>50</v>
       </c>
       <c r="Q61" s="0" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="R61" s="2">
-        <v>45918</v>
+        <v>45970</v>
       </c>
       <c r="S61" s="2">
-        <v>45921</v>
+        <v>45977</v>
       </c>
       <c r="T61" s="0" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="U61" s="0" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="V61" s="0" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="W61" s="0" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="X61" s="0">
         <v>5</v>
@@ -8167,25 +8583,25 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="2">
-        <v>45922</v>
+        <v>45970</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="G62" s="2">
-        <v>45922.4128161921</v>
+        <v>45970.7607620602</v>
       </c>
       <c r="H62" s="0">
         <v>5</v>
@@ -8197,10 +8613,10 @@
         <v>5</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>627</v>
-      </c>
-      <c r="N62" s="0" t="s">
-        <v>628</v>
+        <v>630</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>631</v>
       </c>
       <c r="O62" s="0" t="s">
         <v>49</v>
@@ -8209,25 +8625,25 @@
         <v>50</v>
       </c>
       <c r="Q62" s="0" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="R62" s="2">
-        <v>45914</v>
+        <v>45969</v>
       </c>
       <c r="S62" s="2">
-        <v>45918</v>
+        <v>45970</v>
       </c>
       <c r="T62" s="0" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="U62" s="0" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="V62" s="0" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="W62" s="0" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="X62" s="0">
         <v>5</v>
@@ -8253,40 +8669,43 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C63" s="2">
-        <v>45920</v>
+        <v>45970</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>636</v>
+        <v>581</v>
       </c>
       <c r="G63" s="2">
-        <v>45920.6962243171</v>
+        <v>45970.4829323264</v>
       </c>
       <c r="H63" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" s="0">
         <v>5</v>
       </c>
       <c r="J63" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>641</v>
       </c>
       <c r="O63" s="0" t="s">
         <v>49</v>
@@ -8295,25 +8714,25 @@
         <v>50</v>
       </c>
       <c r="Q63" s="0" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="R63" s="2">
-        <v>45900</v>
+        <v>45967</v>
       </c>
       <c r="S63" s="2">
-        <v>45906</v>
+        <v>45969</v>
       </c>
       <c r="T63" s="0" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="U63" s="0" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="V63" s="0" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="W63" s="0" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="X63" s="0">
         <v>5</v>
@@ -8328,10 +8747,10 @@
         <v>5</v>
       </c>
       <c r="AC63" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD63" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP63" s="0" t="s">
         <v>56</v>
@@ -8339,25 +8758,25 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="2">
-        <v>45916</v>
+        <v>45965</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="G64" s="2">
-        <v>45916.4699822917</v>
+        <v>45965.8421596644</v>
       </c>
       <c r="H64" s="0">
         <v>5</v>
@@ -8369,10 +8788,10 @@
         <v>5</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="O64" s="0" t="s">
         <v>49</v>
@@ -8381,31 +8800,31 @@
         <v>50</v>
       </c>
       <c r="Q64" s="0" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="R64" s="2">
-        <v>45913</v>
+        <v>45962</v>
       </c>
       <c r="S64" s="2">
-        <v>45914</v>
+        <v>45965</v>
       </c>
       <c r="T64" s="0" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="U64" s="0" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="V64" s="0" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="W64" s="0" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="X64" s="0">
         <v>5</v>
       </c>
       <c r="Y64" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA64" s="0">
         <v>5</v>
@@ -8425,25 +8844,25 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="2">
-        <v>45914</v>
+        <v>45962</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>598</v>
+        <v>658</v>
       </c>
       <c r="G65" s="2">
-        <v>45914.5820426389</v>
+        <v>45962.6437613773</v>
       </c>
       <c r="H65" s="0">
         <v>5</v>
@@ -8455,10 +8874,13 @@
         <v>5</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>654</v>
-      </c>
-      <c r="N65" s="0" t="s">
-        <v>655</v>
+        <v>659</v>
+      </c>
+      <c r="M65" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>661</v>
       </c>
       <c r="O65" s="0" t="s">
         <v>49</v>
@@ -8467,25 +8889,25 @@
         <v>50</v>
       </c>
       <c r="Q65" s="0" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="R65" s="2">
-        <v>45907</v>
+        <v>45959</v>
       </c>
       <c r="S65" s="2">
-        <v>45913</v>
+        <v>45962</v>
       </c>
       <c r="T65" s="0" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="U65" s="0" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="V65" s="0" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="W65" s="0" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="X65" s="0">
         <v>5</v>
@@ -8511,25 +8933,25 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C66" s="2">
-        <v>45909</v>
+        <v>45959</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>598</v>
+        <v>658</v>
       </c>
       <c r="G66" s="2">
-        <v>45909.7231987963</v>
+        <v>45959.6416564352</v>
       </c>
       <c r="H66" s="0">
         <v>5</v>
@@ -8541,10 +8963,13 @@
         <v>5</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>663</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>664</v>
+        <v>669</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="N66" s="0" t="s">
+        <v>671</v>
       </c>
       <c r="O66" s="0" t="s">
         <v>49</v>
@@ -8553,25 +8978,25 @@
         <v>50</v>
       </c>
       <c r="Q66" s="0" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="R66" s="2">
-        <v>45906</v>
+        <v>45955</v>
       </c>
       <c r="S66" s="2">
-        <v>45907</v>
+        <v>45959</v>
       </c>
       <c r="T66" s="0" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="U66" s="0" t="s">
-        <v>667</v>
+        <v>153</v>
       </c>
       <c r="V66" s="0" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="W66" s="0" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="X66" s="0">
         <v>5</v>
@@ -8580,7 +9005,7 @@
         <v>5</v>
       </c>
       <c r="AA66" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB66" s="0">
         <v>5</v>
@@ -8589,7 +9014,7 @@
         <v>5</v>
       </c>
       <c r="AD66" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP66" s="0" t="s">
         <v>56</v>
@@ -8597,40 +9022,40 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C67" s="2">
-        <v>45900</v>
+        <v>45955</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="G67" s="2">
-        <v>45900.6461770602</v>
+        <v>45955.8044966319</v>
       </c>
       <c r="H67" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I67" s="0">
         <v>5</v>
       </c>
       <c r="J67" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>672</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
+      </c>
+      <c r="N67" s="0" t="s">
+        <v>679</v>
       </c>
       <c r="O67" s="0" t="s">
         <v>49</v>
@@ -8639,28 +9064,28 @@
         <v>50</v>
       </c>
       <c r="Q67" s="0" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="R67" s="2">
-        <v>45897</v>
+        <v>45954</v>
       </c>
       <c r="S67" s="2">
-        <v>45900</v>
+        <v>45955</v>
       </c>
       <c r="T67" s="0" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="U67" s="0" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="V67" s="0" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="W67" s="0" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="X67" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y67" s="0">
         <v>5</v>
@@ -8672,10 +9097,10 @@
         <v>5</v>
       </c>
       <c r="AC67" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD67" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP67" s="0" t="s">
         <v>56</v>
@@ -8683,25 +9108,25 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="2">
-        <v>45899</v>
+        <v>45954</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>680</v>
+        <v>44</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="G68" s="2">
-        <v>45898.9353472222</v>
+        <v>45954.9526523148</v>
       </c>
       <c r="H68" s="0">
         <v>5</v>
@@ -8713,10 +9138,10 @@
         <v>5</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>682</v>
-      </c>
-      <c r="N68" s="0" t="s">
-        <v>683</v>
+        <v>687</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>688</v>
       </c>
       <c r="O68" s="0" t="s">
         <v>49</v>
@@ -8725,25 +9150,28 @@
         <v>50</v>
       </c>
       <c r="Q68" s="0" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="R68" s="2">
-        <v>45893</v>
+        <v>45949</v>
       </c>
       <c r="S68" s="2">
-        <v>45896</v>
+        <v>45954</v>
       </c>
       <c r="T68" s="0" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="U68" s="0" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="V68" s="0" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="W68" s="0" t="s">
-        <v>688</v>
+        <v>693</v>
+      </c>
+      <c r="X68" s="0">
+        <v>5</v>
       </c>
       <c r="Y68" s="0">
         <v>5</v>
@@ -8757,7 +9185,7 @@
       <c r="AC68" s="0">
         <v>5</v>
       </c>
-      <c r="AE68" s="0">
+      <c r="AD68" s="0">
         <v>5</v>
       </c>
       <c r="AP68" s="0" t="s">
@@ -8766,25 +9194,25 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="2">
-        <v>45897</v>
+        <v>45949</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="G69" s="2">
-        <v>45897.7557321412</v>
+        <v>45949.8261354282</v>
       </c>
       <c r="H69" s="0">
         <v>5</v>
@@ -8796,13 +9224,10 @@
         <v>5</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>691</v>
-      </c>
-      <c r="M69" s="0" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="N69" s="0" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="O69" s="0" t="s">
         <v>49</v>
@@ -8811,25 +9236,25 @@
         <v>50</v>
       </c>
       <c r="Q69" s="0" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="R69" s="2">
-        <v>45896</v>
+        <v>45946</v>
       </c>
       <c r="S69" s="2">
-        <v>45897</v>
+        <v>45949</v>
       </c>
       <c r="T69" s="0" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="U69" s="0" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="V69" s="0" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="W69" s="0" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="X69" s="0">
         <v>5</v>
@@ -8855,25 +9280,25 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C70" s="2">
-        <v>45894</v>
+        <v>45946</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="G70" s="2">
-        <v>45894.8301493981</v>
+        <v>45946.8340835069</v>
       </c>
       <c r="H70" s="0">
         <v>5</v>
@@ -8885,10 +9310,13 @@
         <v>5</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>701</v>
-      </c>
-      <c r="N70" s="0" t="s">
-        <v>693</v>
+        <v>705</v>
+      </c>
+      <c r="M70" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>707</v>
       </c>
       <c r="O70" s="0" t="s">
         <v>49</v>
@@ -8897,25 +9325,25 @@
         <v>50</v>
       </c>
       <c r="Q70" s="0" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="R70" s="2">
-        <v>45890</v>
+        <v>45941</v>
       </c>
       <c r="S70" s="2">
-        <v>45893</v>
+        <v>45946</v>
       </c>
       <c r="T70" s="0" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="U70" s="0" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="V70" s="0" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="W70" s="0" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="X70" s="0">
         <v>5</v>
@@ -8941,25 +9369,25 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="2">
-        <v>45889</v>
+        <v>45938</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="G71" s="2">
-        <v>45889.6599939468</v>
+        <v>45938.7601655556</v>
       </c>
       <c r="H71" s="0">
         <v>5</v>
@@ -8971,13 +9399,10 @@
         <v>5</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>709</v>
-      </c>
-      <c r="M71" s="0" t="s">
-        <v>710</v>
-      </c>
-      <c r="N71" s="0" t="s">
-        <v>711</v>
+        <v>715</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>716</v>
       </c>
       <c r="O71" s="0" t="s">
         <v>49</v>
@@ -8986,25 +9411,25 @@
         <v>50</v>
       </c>
       <c r="Q71" s="0" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="R71" s="2">
-        <v>45886</v>
+        <v>45932</v>
       </c>
       <c r="S71" s="2">
-        <v>45889</v>
+        <v>45935</v>
       </c>
       <c r="T71" s="0" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="U71" s="0" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="V71" s="0" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="W71" s="0" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="X71" s="0">
         <v>5</v>
@@ -9030,25 +9455,25 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C72" s="2">
-        <v>45888</v>
+        <v>45937</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
       <c r="G72" s="2">
-        <v>45888.5413223148</v>
+        <v>45937.8034676042</v>
       </c>
       <c r="H72" s="0">
         <v>5</v>
@@ -9059,11 +9484,11 @@
       <c r="J72" s="0">
         <v>5</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>720</v>
+      <c r="L72" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="N72" s="0" t="s">
+        <v>725</v>
       </c>
       <c r="O72" s="0" t="s">
         <v>49</v>
@@ -9072,25 +9497,25 @@
         <v>50</v>
       </c>
       <c r="Q72" s="0" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="R72" s="2">
-        <v>45883</v>
+        <v>45935</v>
       </c>
       <c r="S72" s="2">
-        <v>45886</v>
+        <v>45937</v>
       </c>
       <c r="T72" s="0" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="U72" s="0" t="s">
-        <v>336</v>
+        <v>728</v>
       </c>
       <c r="V72" s="0" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="W72" s="0" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="X72" s="0">
         <v>5</v>
@@ -9108,7 +9533,7 @@
         <v>5</v>
       </c>
       <c r="AD72" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP72" s="0" t="s">
         <v>56</v>
@@ -9116,25 +9541,25 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C73" s="2">
-        <v>45884</v>
+        <v>45928</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>636</v>
+        <v>733</v>
       </c>
       <c r="G73" s="2">
-        <v>45884.5080971296</v>
+        <v>45928.7262096412</v>
       </c>
       <c r="H73" s="0">
         <v>5</v>
@@ -9146,10 +9571,13 @@
         <v>5</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="N73" s="0" t="s">
-        <v>728</v>
+        <v>734</v>
+      </c>
+      <c r="M73" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>736</v>
       </c>
       <c r="O73" s="0" t="s">
         <v>49</v>
@@ -9158,25 +9586,25 @@
         <v>50</v>
       </c>
       <c r="Q73" s="0" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="R73" s="2">
-        <v>45880</v>
+        <v>45925</v>
       </c>
       <c r="S73" s="2">
-        <v>45883</v>
+        <v>45928</v>
       </c>
       <c r="T73" s="0" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="U73" s="0" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="V73" s="0" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="W73" s="0" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="X73" s="0">
         <v>5</v>
@@ -9202,25 +9630,25 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="2">
-        <v>45884</v>
+        <v>45924</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>636</v>
+        <v>733</v>
       </c>
       <c r="G74" s="2">
-        <v>45884.3282971181</v>
+        <v>45924.6507670833</v>
       </c>
       <c r="H74" s="0">
         <v>5</v>
@@ -9232,10 +9660,10 @@
         <v>5</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="N74" s="0" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="O74" s="0" t="s">
         <v>49</v>
@@ -9244,25 +9672,25 @@
         <v>50</v>
       </c>
       <c r="Q74" s="0" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="R74" s="2">
-        <v>45876</v>
+        <v>45921</v>
       </c>
       <c r="S74" s="2">
-        <v>45877</v>
+        <v>45924</v>
       </c>
       <c r="T74" s="0" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="U74" s="0" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="V74" s="0" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="W74" s="0" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="X74" s="0">
         <v>5</v>
@@ -9288,25 +9716,25 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C75" s="2">
-        <v>45880</v>
+        <v>45923</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>636</v>
+        <v>733</v>
       </c>
       <c r="G75" s="2">
-        <v>45880.7327610417</v>
+        <v>45923.3761746296</v>
       </c>
       <c r="H75" s="0">
         <v>5</v>
@@ -9318,10 +9746,10 @@
         <v>5</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="N75" s="0" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="O75" s="0" t="s">
         <v>49</v>
@@ -9330,25 +9758,25 @@
         <v>50</v>
       </c>
       <c r="Q75" s="0" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="R75" s="2">
-        <v>45877</v>
+        <v>45918</v>
       </c>
       <c r="S75" s="2">
-        <v>45880</v>
+        <v>45921</v>
       </c>
       <c r="T75" s="0" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="U75" s="0" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="V75" s="0" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="W75" s="0" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="X75" s="0">
         <v>5</v>
@@ -9374,25 +9802,25 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="2">
-        <v>45877</v>
+        <v>45922</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>636</v>
+        <v>733</v>
       </c>
       <c r="G76" s="2">
-        <v>45877.4773553819</v>
+        <v>45922.4128161921</v>
       </c>
       <c r="H76" s="0">
         <v>5</v>
@@ -9404,10 +9832,10 @@
         <v>5</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="N76" s="0" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="O76" s="0" t="s">
         <v>49</v>
@@ -9416,25 +9844,25 @@
         <v>50</v>
       </c>
       <c r="Q76" s="0" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="R76" s="2">
-        <v>45873</v>
+        <v>45914</v>
       </c>
       <c r="S76" s="2">
-        <v>45876</v>
+        <v>45918</v>
       </c>
       <c r="T76" s="0" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="U76" s="0" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="V76" s="0" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="W76" s="0" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="X76" s="0">
         <v>5</v>
@@ -9460,40 +9888,40 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C77" s="2">
-        <v>45873</v>
+        <v>45920</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>636</v>
+        <v>771</v>
       </c>
       <c r="G77" s="2">
-        <v>45873.7425913657</v>
+        <v>45920.6962243171</v>
       </c>
       <c r="H77" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I77" s="0">
         <v>5</v>
       </c>
       <c r="J77" s="0">
-        <v>5</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="N77" s="0" t="s">
-        <v>764</v>
+        <v>4</v>
+      </c>
+      <c r="L77" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="M77" s="0" t="s">
+        <v>773</v>
       </c>
       <c r="O77" s="0" t="s">
         <v>49</v>
@@ -9502,25 +9930,25 @@
         <v>50</v>
       </c>
       <c r="Q77" s="0" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="R77" s="2">
-        <v>45871</v>
+        <v>45900</v>
       </c>
       <c r="S77" s="2">
-        <v>45873</v>
+        <v>45906</v>
       </c>
       <c r="T77" s="0" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="U77" s="0" t="s">
-        <v>767</v>
+        <v>134</v>
       </c>
       <c r="V77" s="0" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="W77" s="0" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="X77" s="0">
         <v>5</v>
@@ -9535,10 +9963,10 @@
         <v>5</v>
       </c>
       <c r="AC77" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD77" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP77" s="0" t="s">
         <v>56</v>
@@ -9546,25 +9974,25 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C78" s="2">
-        <v>45871</v>
+        <v>45916</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>772</v>
+        <v>733</v>
       </c>
       <c r="G78" s="2">
-        <v>45871.6773271875</v>
+        <v>45916.4699822917</v>
       </c>
       <c r="H78" s="0">
         <v>5</v>
@@ -9576,10 +10004,10 @@
         <v>5</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="N78" s="0" t="s">
-        <v>774</v>
+        <v>131</v>
       </c>
       <c r="O78" s="0" t="s">
         <v>49</v>
@@ -9588,31 +10016,31 @@
         <v>50</v>
       </c>
       <c r="Q78" s="0" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="R78" s="2">
-        <v>45867</v>
+        <v>45913</v>
       </c>
       <c r="S78" s="2">
-        <v>45871</v>
+        <v>45914</v>
       </c>
       <c r="T78" s="0" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="U78" s="0" t="s">
-        <v>777</v>
+        <v>134</v>
       </c>
       <c r="V78" s="0" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="W78" s="0" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="X78" s="0">
         <v>5</v>
       </c>
       <c r="Y78" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA78" s="0">
         <v>5</v>
@@ -9632,25 +10060,25 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C79" s="2">
-        <v>45866</v>
+        <v>45914</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>772</v>
+        <v>733</v>
       </c>
       <c r="G79" s="2">
-        <v>45866.5828246181</v>
+        <v>45914.5820426389</v>
       </c>
       <c r="H79" s="0">
         <v>5</v>
@@ -9662,13 +10090,10 @@
         <v>5</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>782</v>
-      </c>
-      <c r="M79" s="0" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="N79" s="0" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="O79" s="0" t="s">
         <v>49</v>
@@ -9677,25 +10102,25 @@
         <v>50</v>
       </c>
       <c r="Q79" s="0" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="R79" s="2">
-        <v>45863</v>
+        <v>45907</v>
       </c>
       <c r="S79" s="2">
-        <v>45865</v>
+        <v>45913</v>
       </c>
       <c r="T79" s="0" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="U79" s="0" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="V79" s="0" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="W79" s="0" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="X79" s="0">
         <v>5</v>
@@ -9721,25 +10146,25 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C80" s="2">
-        <v>45865</v>
+        <v>45909</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>772</v>
+        <v>733</v>
       </c>
       <c r="G80" s="2">
-        <v>45865.9243556134</v>
+        <v>45909.7231987963</v>
       </c>
       <c r="H80" s="0">
         <v>5</v>
@@ -9751,10 +10176,10 @@
         <v>5</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>792</v>
-      </c>
-      <c r="N80" s="0" t="s">
-        <v>793</v>
+        <v>796</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>797</v>
       </c>
       <c r="O80" s="0" t="s">
         <v>49</v>
@@ -9763,25 +10188,25 @@
         <v>50</v>
       </c>
       <c r="Q80" s="0" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="R80" s="2">
-        <v>45856</v>
+        <v>45906</v>
       </c>
       <c r="S80" s="2">
-        <v>45863</v>
+        <v>45907</v>
       </c>
       <c r="T80" s="0" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="U80" s="0" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="V80" s="0" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="W80" s="0" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="X80" s="0">
         <v>5</v>
@@ -9807,25 +10232,25 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C81" s="2">
-        <v>45856</v>
+        <v>45900</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G81" s="2">
-        <v>45856.6443881597</v>
+        <v>45900.6461770602</v>
       </c>
       <c r="H81" s="0">
         <v>5</v>
@@ -9836,14 +10261,11 @@
       <c r="J81" s="0">
         <v>5</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="M81" s="0" t="s">
-        <v>802</v>
-      </c>
-      <c r="N81" s="0" t="s">
-        <v>803</v>
+      <c r="L81" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>806</v>
       </c>
       <c r="O81" s="0" t="s">
         <v>49</v>
@@ -9852,25 +10274,25 @@
         <v>50</v>
       </c>
       <c r="Q81" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="R81" s="2">
-        <v>45852</v>
+        <v>45897</v>
       </c>
       <c r="S81" s="2">
-        <v>45856</v>
+        <v>45900</v>
       </c>
       <c r="T81" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="U81" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="V81" s="0" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="W81" s="0" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="X81" s="0">
         <v>5</v>
@@ -9896,25 +10318,25 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C82" s="2">
-        <v>45852</v>
+        <v>45899</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>44</v>
+        <v>813</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G82" s="2">
-        <v>45852.7965359028</v>
+        <v>45898.9353472222</v>
       </c>
       <c r="H82" s="0">
         <v>5</v>
@@ -9926,10 +10348,10 @@
         <v>5</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="N82" s="0" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="O82" s="0" t="s">
         <v>49</v>
@@ -9938,28 +10360,25 @@
         <v>50</v>
       </c>
       <c r="Q82" s="0" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="R82" s="2">
-        <v>45849</v>
+        <v>45893</v>
       </c>
       <c r="S82" s="2">
-        <v>45852</v>
+        <v>45896</v>
       </c>
       <c r="T82" s="0" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="U82" s="0" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="V82" s="0" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="W82" s="0" t="s">
-        <v>817</v>
-      </c>
-      <c r="X82" s="0">
-        <v>5</v>
+        <v>821</v>
       </c>
       <c r="Y82" s="0">
         <v>5</v>
@@ -9973,7 +10392,7 @@
       <c r="AC82" s="0">
         <v>5</v>
       </c>
-      <c r="AD82" s="0">
+      <c r="AE82" s="0">
         <v>5</v>
       </c>
       <c r="AP82" s="0" t="s">
@@ -9982,25 +10401,25 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C83" s="2">
-        <v>45849</v>
+        <v>45897</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G83" s="2">
-        <v>45849.5684718982</v>
+        <v>45897.7557321412</v>
       </c>
       <c r="H83" s="0">
         <v>5</v>
@@ -10012,10 +10431,13 @@
         <v>5</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>820</v>
+        <v>824</v>
+      </c>
+      <c r="M83" s="0" t="s">
+        <v>825</v>
       </c>
       <c r="N83" s="0" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="O83" s="0" t="s">
         <v>49</v>
@@ -10024,25 +10446,25 @@
         <v>50</v>
       </c>
       <c r="Q83" s="0" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="R83" s="2">
-        <v>45844</v>
+        <v>45896</v>
       </c>
       <c r="S83" s="2">
-        <v>45849</v>
+        <v>45897</v>
       </c>
       <c r="T83" s="0" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="U83" s="0" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="V83" s="0" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="W83" s="0" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="X83" s="0">
         <v>5</v>
@@ -10068,25 +10490,25 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C84" s="2">
-        <v>45848</v>
+        <v>45894</v>
       </c>
       <c r="D84" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G84" s="2">
-        <v>45848.4790960417</v>
+        <v>45894.8301493981</v>
       </c>
       <c r="H84" s="0">
         <v>5</v>
@@ -10098,13 +10520,10 @@
         <v>5</v>
       </c>
       <c r="L84" s="0" t="s">
-        <v>829</v>
-      </c>
-      <c r="M84" s="0" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="N84" s="0" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O84" s="0" t="s">
         <v>49</v>
@@ -10113,25 +10532,25 @@
         <v>50</v>
       </c>
       <c r="Q84" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="R84" s="2">
-        <v>45843</v>
+        <v>45890</v>
       </c>
       <c r="S84" s="2">
-        <v>45844</v>
+        <v>45893</v>
       </c>
       <c r="T84" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="U84" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="V84" s="0" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="W84" s="0" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="X84" s="0">
         <v>5</v>
@@ -10157,25 +10576,25 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C85" s="2">
-        <v>45845</v>
+        <v>45889</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>839</v>
+        <v>771</v>
       </c>
       <c r="G85" s="2">
-        <v>45845.9336395949</v>
+        <v>45889.6599939468</v>
       </c>
       <c r="H85" s="0">
         <v>5</v>
@@ -10187,10 +10606,13 @@
         <v>5</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>840</v>
+        <v>842</v>
+      </c>
+      <c r="M85" s="0" t="s">
+        <v>843</v>
       </c>
       <c r="N85" s="0" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="O85" s="0" t="s">
         <v>49</v>
@@ -10199,25 +10621,25 @@
         <v>50</v>
       </c>
       <c r="Q85" s="0" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="R85" s="2">
-        <v>45838</v>
+        <v>45886</v>
       </c>
       <c r="S85" s="2">
-        <v>45839</v>
+        <v>45889</v>
       </c>
       <c r="T85" s="0" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="U85" s="0" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="V85" s="0" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="W85" s="0" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="X85" s="0">
         <v>5</v>
@@ -10235,7 +10657,7 @@
         <v>5</v>
       </c>
       <c r="AD85" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP85" s="0" t="s">
         <v>56</v>
@@ -10243,25 +10665,25 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C86" s="2">
-        <v>45840</v>
+        <v>45888</v>
       </c>
       <c r="D86" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>839</v>
+        <v>771</v>
       </c>
       <c r="G86" s="2">
-        <v>45840.9692126389</v>
+        <v>45888.5413223148</v>
       </c>
       <c r="H86" s="0">
         <v>5</v>
@@ -10272,11 +10694,11 @@
       <c r="J86" s="0">
         <v>5</v>
       </c>
-      <c r="L86" s="0" t="s">
-        <v>849</v>
-      </c>
-      <c r="N86" s="0" t="s">
-        <v>850</v>
+      <c r="L86" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>853</v>
       </c>
       <c r="O86" s="0" t="s">
         <v>49</v>
@@ -10285,25 +10707,25 @@
         <v>50</v>
       </c>
       <c r="Q86" s="0" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="R86" s="2">
-        <v>45836</v>
+        <v>45883</v>
       </c>
       <c r="S86" s="2">
-        <v>45838</v>
+        <v>45886</v>
       </c>
       <c r="T86" s="0" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="U86" s="0" t="s">
-        <v>853</v>
+        <v>472</v>
       </c>
       <c r="V86" s="0" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="W86" s="0" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="X86" s="0">
         <v>5</v>
@@ -10329,25 +10751,25 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C87" s="2">
-        <v>45834</v>
+        <v>45884</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>839</v>
+        <v>771</v>
       </c>
       <c r="G87" s="2">
-        <v>45834.7373021991</v>
+        <v>45884.5080971296</v>
       </c>
       <c r="H87" s="0">
         <v>5</v>
@@ -10359,10 +10781,10 @@
         <v>5</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="N87" s="0" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="O87" s="0" t="s">
         <v>49</v>
@@ -10371,25 +10793,25 @@
         <v>50</v>
       </c>
       <c r="Q87" s="0" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="R87" s="2">
-        <v>45833</v>
+        <v>45880</v>
       </c>
       <c r="S87" s="2">
-        <v>45834</v>
+        <v>45883</v>
       </c>
       <c r="T87" s="0" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="U87" s="0" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="V87" s="0" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="W87" s="0" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="X87" s="0">
         <v>5</v>
@@ -10415,25 +10837,25 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>43</v>
       </c>
       <c r="C88" s="2">
-        <v>45831</v>
+        <v>45884</v>
       </c>
       <c r="D88" s="0" t="s">
         <v>44</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>839</v>
+        <v>771</v>
       </c>
       <c r="G88" s="2">
-        <v>45831.0369623843</v>
+        <v>45884.3282971181</v>
       </c>
       <c r="H88" s="0">
         <v>5</v>
@@ -10445,10 +10867,10 @@
         <v>5</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="N88" s="0" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="O88" s="0" t="s">
         <v>49</v>
@@ -10457,25 +10879,25 @@
         <v>50</v>
       </c>
       <c r="Q88" s="0" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="R88" s="2">
-        <v>45828</v>
+        <v>45876</v>
       </c>
       <c r="S88" s="2">
-        <v>45830</v>
+        <v>45877</v>
       </c>
       <c r="T88" s="0" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="U88" s="0" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="V88" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="W88" s="0" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="X88" s="0">
         <v>5</v>
@@ -10499,8 +10921,1221 @@
         <v>56</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>876</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" s="2">
+        <v>45880</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>877</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45880.7327610417</v>
+      </c>
+      <c r="H89" s="0">
+        <v>5</v>
+      </c>
+      <c r="I89" s="0">
+        <v>5</v>
+      </c>
+      <c r="J89" s="0">
+        <v>5</v>
+      </c>
+      <c r="L89" s="0" t="s">
+        <v>878</v>
+      </c>
+      <c r="N89" s="0" t="s">
+        <v>879</v>
+      </c>
+      <c r="O89" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P89" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q89" s="0" t="s">
+        <v>880</v>
+      </c>
+      <c r="R89" s="2">
+        <v>45877</v>
+      </c>
+      <c r="S89" s="2">
+        <v>45880</v>
+      </c>
+      <c r="T89" s="0" t="s">
+        <v>881</v>
+      </c>
+      <c r="U89" s="0" t="s">
+        <v>882</v>
+      </c>
+      <c r="V89" s="0" t="s">
+        <v>883</v>
+      </c>
+      <c r="W89" s="0" t="s">
+        <v>884</v>
+      </c>
+      <c r="X89" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP89" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C90" s="2">
+        <v>45877</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>886</v>
+      </c>
+      <c r="F90" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45877.4773553819</v>
+      </c>
+      <c r="H90" s="0">
+        <v>5</v>
+      </c>
+      <c r="I90" s="0">
+        <v>5</v>
+      </c>
+      <c r="J90" s="0">
+        <v>5</v>
+      </c>
+      <c r="L90" s="0" t="s">
+        <v>887</v>
+      </c>
+      <c r="N90" s="0" t="s">
+        <v>888</v>
+      </c>
+      <c r="O90" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P90" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q90" s="0" t="s">
+        <v>889</v>
+      </c>
+      <c r="R90" s="2">
+        <v>45873</v>
+      </c>
+      <c r="S90" s="2">
+        <v>45876</v>
+      </c>
+      <c r="T90" s="0" t="s">
+        <v>890</v>
+      </c>
+      <c r="U90" s="0" t="s">
+        <v>891</v>
+      </c>
+      <c r="V90" s="0" t="s">
+        <v>892</v>
+      </c>
+      <c r="W90" s="0" t="s">
+        <v>893</v>
+      </c>
+      <c r="X90" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y90" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA90" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB90" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC90" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD90" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP90" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>894</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91" s="2">
+        <v>45873</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45873.7425913657</v>
+      </c>
+      <c r="H91" s="0">
+        <v>5</v>
+      </c>
+      <c r="I91" s="0">
+        <v>5</v>
+      </c>
+      <c r="J91" s="0">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="N91" s="0" t="s">
+        <v>897</v>
+      </c>
+      <c r="O91" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P91" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q91" s="0" t="s">
+        <v>898</v>
+      </c>
+      <c r="R91" s="2">
+        <v>45871</v>
+      </c>
+      <c r="S91" s="2">
+        <v>45873</v>
+      </c>
+      <c r="T91" s="0" t="s">
+        <v>899</v>
+      </c>
+      <c r="U91" s="0" t="s">
+        <v>900</v>
+      </c>
+      <c r="V91" s="0" t="s">
+        <v>901</v>
+      </c>
+      <c r="W91" s="0" t="s">
+        <v>902</v>
+      </c>
+      <c r="X91" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP91" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>903</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92" s="2">
+        <v>45871</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>904</v>
+      </c>
+      <c r="F92" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45871.6773271875</v>
+      </c>
+      <c r="H92" s="0">
+        <v>5</v>
+      </c>
+      <c r="I92" s="0">
+        <v>5</v>
+      </c>
+      <c r="J92" s="0">
+        <v>5</v>
+      </c>
+      <c r="L92" s="0" t="s">
+        <v>906</v>
+      </c>
+      <c r="N92" s="0" t="s">
+        <v>907</v>
+      </c>
+      <c r="O92" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P92" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q92" s="0" t="s">
+        <v>908</v>
+      </c>
+      <c r="R92" s="2">
+        <v>45867</v>
+      </c>
+      <c r="S92" s="2">
+        <v>45871</v>
+      </c>
+      <c r="T92" s="0" t="s">
+        <v>909</v>
+      </c>
+      <c r="U92" s="0" t="s">
+        <v>910</v>
+      </c>
+      <c r="V92" s="0" t="s">
+        <v>911</v>
+      </c>
+      <c r="W92" s="0" t="s">
+        <v>912</v>
+      </c>
+      <c r="X92" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y92" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA92" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB92" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC92" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD92" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP92" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>913</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C93" s="2">
+        <v>45866</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>914</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45866.5828246181</v>
+      </c>
+      <c r="H93" s="0">
+        <v>5</v>
+      </c>
+      <c r="I93" s="0">
+        <v>5</v>
+      </c>
+      <c r="J93" s="0">
+        <v>5</v>
+      </c>
+      <c r="L93" s="0" t="s">
+        <v>915</v>
+      </c>
+      <c r="M93" s="0" t="s">
+        <v>916</v>
+      </c>
+      <c r="N93" s="0" t="s">
+        <v>917</v>
+      </c>
+      <c r="O93" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P93" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q93" s="0" t="s">
+        <v>918</v>
+      </c>
+      <c r="R93" s="2">
+        <v>45863</v>
+      </c>
+      <c r="S93" s="2">
+        <v>45865</v>
+      </c>
+      <c r="T93" s="0" t="s">
+        <v>919</v>
+      </c>
+      <c r="U93" s="0" t="s">
+        <v>920</v>
+      </c>
+      <c r="V93" s="0" t="s">
+        <v>921</v>
+      </c>
+      <c r="W93" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="X93" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y93" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA93" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB93" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC93" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD93" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP93" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>923</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45865</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45865.9243556134</v>
+      </c>
+      <c r="H94" s="0">
+        <v>5</v>
+      </c>
+      <c r="I94" s="0">
+        <v>5</v>
+      </c>
+      <c r="J94" s="0">
+        <v>5</v>
+      </c>
+      <c r="L94" s="0" t="s">
+        <v>925</v>
+      </c>
+      <c r="N94" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="O94" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P94" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q94" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="R94" s="2">
+        <v>45856</v>
+      </c>
+      <c r="S94" s="2">
+        <v>45863</v>
+      </c>
+      <c r="T94" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="U94" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="V94" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="W94" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="X94" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP94" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>932</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C95" s="2">
+        <v>45856</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>933</v>
+      </c>
+      <c r="F95" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45856.6443881597</v>
+      </c>
+      <c r="H95" s="0">
+        <v>5</v>
+      </c>
+      <c r="I95" s="0">
+        <v>5</v>
+      </c>
+      <c r="J95" s="0">
+        <v>5</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="M95" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="N95" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="O95" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P95" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q95" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="R95" s="2">
+        <v>45852</v>
+      </c>
+      <c r="S95" s="2">
+        <v>45856</v>
+      </c>
+      <c r="T95" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="U95" s="0" t="s">
+        <v>939</v>
+      </c>
+      <c r="V95" s="0" t="s">
+        <v>940</v>
+      </c>
+      <c r="W95" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="X95" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y95" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA95" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB95" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC95" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD95" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP95" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" s="2">
+        <v>45852</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>943</v>
+      </c>
+      <c r="F96" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45852.7965359028</v>
+      </c>
+      <c r="H96" s="0">
+        <v>5</v>
+      </c>
+      <c r="I96" s="0">
+        <v>5</v>
+      </c>
+      <c r="J96" s="0">
+        <v>5</v>
+      </c>
+      <c r="L96" s="0" t="s">
+        <v>944</v>
+      </c>
+      <c r="N96" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="O96" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P96" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q96" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="R96" s="2">
+        <v>45849</v>
+      </c>
+      <c r="S96" s="2">
+        <v>45852</v>
+      </c>
+      <c r="T96" s="0" t="s">
+        <v>947</v>
+      </c>
+      <c r="U96" s="0" t="s">
+        <v>948</v>
+      </c>
+      <c r="V96" s="0" t="s">
+        <v>949</v>
+      </c>
+      <c r="W96" s="0" t="s">
+        <v>950</v>
+      </c>
+      <c r="X96" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y96" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA96" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB96" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC96" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD96" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP96" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>951</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" s="2">
+        <v>45849</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>952</v>
+      </c>
+      <c r="F97" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45849.5684718982</v>
+      </c>
+      <c r="H97" s="0">
+        <v>5</v>
+      </c>
+      <c r="I97" s="0">
+        <v>5</v>
+      </c>
+      <c r="J97" s="0">
+        <v>5</v>
+      </c>
+      <c r="L97" s="0" t="s">
+        <v>953</v>
+      </c>
+      <c r="N97" s="0" t="s">
+        <v>954</v>
+      </c>
+      <c r="O97" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P97" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q97" s="0" t="s">
+        <v>955</v>
+      </c>
+      <c r="R97" s="2">
+        <v>45844</v>
+      </c>
+      <c r="S97" s="2">
+        <v>45849</v>
+      </c>
+      <c r="T97" s="0" t="s">
+        <v>956</v>
+      </c>
+      <c r="U97" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="V97" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="W97" s="0" t="s">
+        <v>959</v>
+      </c>
+      <c r="X97" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y97" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA97" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB97" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC97" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD97" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP97" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" s="2">
+        <v>45848</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45848.4790960417</v>
+      </c>
+      <c r="H98" s="0">
+        <v>5</v>
+      </c>
+      <c r="I98" s="0">
+        <v>5</v>
+      </c>
+      <c r="J98" s="0">
+        <v>5</v>
+      </c>
+      <c r="L98" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="M98" s="0" t="s">
+        <v>963</v>
+      </c>
+      <c r="N98" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="O98" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P98" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q98" s="0" t="s">
+        <v>964</v>
+      </c>
+      <c r="R98" s="2">
+        <v>45843</v>
+      </c>
+      <c r="S98" s="2">
+        <v>45844</v>
+      </c>
+      <c r="T98" s="0" t="s">
+        <v>965</v>
+      </c>
+      <c r="U98" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="V98" s="0" t="s">
+        <v>966</v>
+      </c>
+      <c r="W98" s="0" t="s">
+        <v>967</v>
+      </c>
+      <c r="X98" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y98" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA98" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB98" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC98" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD98" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP98" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>968</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" s="2">
+        <v>45845</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>969</v>
+      </c>
+      <c r="F99" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45845.9336395949</v>
+      </c>
+      <c r="H99" s="0">
+        <v>5</v>
+      </c>
+      <c r="I99" s="0">
+        <v>5</v>
+      </c>
+      <c r="J99" s="0">
+        <v>5</v>
+      </c>
+      <c r="L99" s="0" t="s">
+        <v>971</v>
+      </c>
+      <c r="N99" s="0" t="s">
+        <v>972</v>
+      </c>
+      <c r="O99" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P99" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q99" s="0" t="s">
+        <v>973</v>
+      </c>
+      <c r="R99" s="2">
+        <v>45838</v>
+      </c>
+      <c r="S99" s="2">
+        <v>45839</v>
+      </c>
+      <c r="T99" s="0" t="s">
+        <v>974</v>
+      </c>
+      <c r="U99" s="0" t="s">
+        <v>975</v>
+      </c>
+      <c r="V99" s="0" t="s">
+        <v>976</v>
+      </c>
+      <c r="W99" s="0" t="s">
+        <v>977</v>
+      </c>
+      <c r="X99" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y99" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA99" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB99" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC99" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD99" s="0">
+        <v>4</v>
+      </c>
+      <c r="AP99" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100" s="2">
+        <v>45840</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>979</v>
+      </c>
+      <c r="F100" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45840.9692126389</v>
+      </c>
+      <c r="H100" s="0">
+        <v>5</v>
+      </c>
+      <c r="I100" s="0">
+        <v>5</v>
+      </c>
+      <c r="J100" s="0">
+        <v>5</v>
+      </c>
+      <c r="L100" s="0" t="s">
+        <v>980</v>
+      </c>
+      <c r="N100" s="0" t="s">
+        <v>981</v>
+      </c>
+      <c r="O100" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P100" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q100" s="0" t="s">
+        <v>982</v>
+      </c>
+      <c r="R100" s="2">
+        <v>45836</v>
+      </c>
+      <c r="S100" s="2">
+        <v>45838</v>
+      </c>
+      <c r="T100" s="0" t="s">
+        <v>983</v>
+      </c>
+      <c r="U100" s="0" t="s">
+        <v>984</v>
+      </c>
+      <c r="V100" s="0" t="s">
+        <v>985</v>
+      </c>
+      <c r="W100" s="0" t="s">
+        <v>986</v>
+      </c>
+      <c r="X100" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP100" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>987</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" s="2">
+        <v>45834</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>988</v>
+      </c>
+      <c r="F101" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="G101" s="2">
+        <v>45834.7373021991</v>
+      </c>
+      <c r="H101" s="0">
+        <v>5</v>
+      </c>
+      <c r="I101" s="0">
+        <v>5</v>
+      </c>
+      <c r="J101" s="0">
+        <v>5</v>
+      </c>
+      <c r="L101" s="0" t="s">
+        <v>989</v>
+      </c>
+      <c r="N101" s="0" t="s">
+        <v>990</v>
+      </c>
+      <c r="O101" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P101" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q101" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="R101" s="2">
+        <v>45833</v>
+      </c>
+      <c r="S101" s="2">
+        <v>45834</v>
+      </c>
+      <c r="T101" s="0" t="s">
+        <v>992</v>
+      </c>
+      <c r="U101" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="V101" s="0" t="s">
+        <v>994</v>
+      </c>
+      <c r="W101" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="X101" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP101" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>996</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C102" s="2">
+        <v>45831</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>997</v>
+      </c>
+      <c r="F102" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45831.0369623843</v>
+      </c>
+      <c r="H102" s="0">
+        <v>5</v>
+      </c>
+      <c r="I102" s="0">
+        <v>5</v>
+      </c>
+      <c r="J102" s="0">
+        <v>5</v>
+      </c>
+      <c r="L102" s="0" t="s">
+        <v>998</v>
+      </c>
+      <c r="N102" s="0" t="s">
+        <v>999</v>
+      </c>
+      <c r="O102" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="P102" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q102" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="R102" s="2">
+        <v>45828</v>
+      </c>
+      <c r="S102" s="2">
+        <v>45830</v>
+      </c>
+      <c r="T102" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="U102" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="V102" s="0" t="s">
+        <v>1003</v>
+      </c>
+      <c r="W102" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="X102" s="0">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="0">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="0">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="0">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="0">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="0">
+        <v>5</v>
+      </c>
+      <c r="AP102" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP88"/>
+  <autoFilter ref="A1:AP102"/>
   <headerFooter/>
 </worksheet>
 </file>